--- a/Reference_docs/Ormeco Sensor List_Rev04- commenets by IE.xlsx
+++ b/Reference_docs/Ormeco Sensor List_Rev04- commenets by IE.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://daikai-my.sharepoint.com/personal/quyen_daikai_com/Documents/PROJECTS/1. In Progeress/5. ORMECO-ORMIN/Others/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DAIKAI VR\Desktop\Ormin_Project_V5\Reference_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_AE758EBF6970577B872A64E21A5A1EF44D585751" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9F3468E-3CF9-4510-8AA7-AE0DCCC48E04}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF1B2281-37BB-4B2E-99FB-49C69192E084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rev04" sheetId="1" r:id="rId1"/>
+    <sheet name="Modbus Digital" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -184,7 +185,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4711" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4747" uniqueCount="615">
   <si>
     <t>No.</t>
   </si>
@@ -2558,12 +2559,117 @@
   <si>
     <t>Gen Local Box#4</t>
   </si>
+  <si>
+    <t>Pump 1</t>
+  </si>
+  <si>
+    <t>Pump 2</t>
+  </si>
+  <si>
+    <t>Pump 3</t>
+  </si>
+  <si>
+    <t>Pump 4</t>
+  </si>
+  <si>
+    <t>Pump 5</t>
+  </si>
+  <si>
+    <t>Pump 6</t>
+  </si>
+  <si>
+    <t>Pump 7</t>
+  </si>
+  <si>
+    <t>Pump 8</t>
+  </si>
+  <si>
+    <t>Pump 9</t>
+  </si>
+  <si>
+    <t>Pump 10</t>
+  </si>
+  <si>
+    <t>Pump 11</t>
+  </si>
+  <si>
+    <t>Pump 12</t>
+  </si>
+  <si>
+    <t>LC_D.O.service.tank</t>
+  </si>
+  <si>
+    <t>LC_H.O.settling.tank</t>
+  </si>
+  <si>
+    <t>LH_D.O.service.tank</t>
+  </si>
+  <si>
+    <t>LH_F.O. drain tank</t>
+  </si>
+  <si>
+    <t>LH_H.O.settling.tank</t>
+  </si>
+  <si>
+    <t>LL_D.O.service.tank</t>
+  </si>
+  <si>
+    <t>LL_F.O. drain tank</t>
+  </si>
+  <si>
+    <t>LL_H.O.service.tank</t>
+  </si>
+  <si>
+    <t>LL_H.O.settling.tank</t>
+  </si>
+  <si>
+    <t>LS_Sludge.tank</t>
+  </si>
+  <si>
+    <t>TS_D.O.service.tank</t>
+  </si>
+  <si>
+    <t>TS_F.O. drain tank</t>
+  </si>
+  <si>
+    <t>TS_H.O.purifier.No1</t>
+  </si>
+  <si>
+    <t>TS_H.O.purifier.No2</t>
+  </si>
+  <si>
+    <t>TS_H.O.purifier.No3</t>
+  </si>
+  <si>
+    <t>TS_H.O.settling.tank</t>
+  </si>
+  <si>
+    <t>TS1_H.O.service.tank</t>
+  </si>
+  <si>
+    <t>TS2_H.O.service.tank</t>
+  </si>
+  <si>
+    <t>TSH_D.O.service.tank</t>
+  </si>
+  <si>
+    <t>TSH_F.O. drain tank</t>
+  </si>
+  <si>
+    <t>TSH_H.O.service.tank</t>
+  </si>
+  <si>
+    <t>TSH_H.O.settling.tank</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2612,6 +2718,11 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -3271,53 +3382,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3332,6 +3396,53 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3571,17 +3682,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="42.75" customHeight="1">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="145" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="126" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126" t="s">
+      <c r="B1" s="146" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="126" t="s">
+      <c r="E1" s="146" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -3605,31 +3716,31 @@
       <c r="L1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="127" t="s">
+      <c r="M1" s="147" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="128"/>
+      <c r="N1" s="148"/>
     </row>
     <row r="2" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A2" s="125"/>
-      <c r="B2" s="125"/>
-      <c r="C2" s="125"/>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="129" t="s">
+      <c r="A2" s="139"/>
+      <c r="B2" s="139"/>
+      <c r="C2" s="139"/>
+      <c r="D2" s="139"/>
+      <c r="E2" s="139"/>
+      <c r="F2" s="149" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="130"/>
-      <c r="H2" s="130"/>
-      <c r="I2" s="130"/>
-      <c r="J2" s="128"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="150"/>
+      <c r="I2" s="150"/>
+      <c r="J2" s="148"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
       <c r="N2" s="4"/>
     </row>
     <row r="3" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A3" s="131">
+      <c r="A3" s="143">
         <v>1</v>
       </c>
       <c r="B3" s="7">
@@ -3667,7 +3778,7 @@
       <c r="P3" s="14"/>
     </row>
     <row r="4" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A4" s="132"/>
+      <c r="A4" s="138"/>
       <c r="B4" s="7">
         <v>12</v>
       </c>
@@ -3703,7 +3814,7 @@
       <c r="P4" s="14"/>
     </row>
     <row r="5" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A5" s="132"/>
+      <c r="A5" s="138"/>
       <c r="B5" s="7">
         <v>12</v>
       </c>
@@ -3739,7 +3850,7 @@
       <c r="P5" s="14"/>
     </row>
     <row r="6" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A6" s="125"/>
+      <c r="A6" s="139"/>
       <c r="B6" s="7">
         <v>12</v>
       </c>
@@ -3793,7 +3904,7 @@
       <c r="P7" s="14"/>
     </row>
     <row r="8" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A8" s="131">
+      <c r="A8" s="143">
         <v>2</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -3829,7 +3940,7 @@
       <c r="P8" s="14"/>
     </row>
     <row r="9" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A9" s="132"/>
+      <c r="A9" s="138"/>
       <c r="B9" s="7" t="s">
         <v>25</v>
       </c>
@@ -3863,7 +3974,7 @@
       <c r="P9" s="14"/>
     </row>
     <row r="10" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A10" s="132"/>
+      <c r="A10" s="138"/>
       <c r="B10" s="7" t="s">
         <v>25</v>
       </c>
@@ -3897,7 +4008,7 @@
       <c r="P10" s="14"/>
     </row>
     <row r="11" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A11" s="125"/>
+      <c r="A11" s="139"/>
       <c r="B11" s="7" t="s">
         <v>25</v>
       </c>
@@ -3949,7 +4060,7 @@
       <c r="P12" s="14"/>
     </row>
     <row r="13" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A13" s="131">
+      <c r="A13" s="143">
         <v>3</v>
       </c>
       <c r="B13" s="7" t="s">
@@ -3987,7 +4098,7 @@
       <c r="P13" s="14"/>
     </row>
     <row r="14" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A14" s="132"/>
+      <c r="A14" s="138"/>
       <c r="B14" s="7" t="s">
         <v>28</v>
       </c>
@@ -4023,7 +4134,7 @@
       <c r="P14" s="14"/>
     </row>
     <row r="15" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A15" s="132"/>
+      <c r="A15" s="138"/>
       <c r="B15" s="7" t="s">
         <v>28</v>
       </c>
@@ -4059,7 +4170,7 @@
       <c r="P15" s="14"/>
     </row>
     <row r="16" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A16" s="125"/>
+      <c r="A16" s="139"/>
       <c r="B16" s="7" t="s">
         <v>28</v>
       </c>
@@ -4113,7 +4224,7 @@
       <c r="P17" s="14"/>
     </row>
     <row r="18" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A18" s="131">
+      <c r="A18" s="143">
         <v>4</v>
       </c>
       <c r="B18" s="7" t="s">
@@ -4149,7 +4260,7 @@
       <c r="P18" s="14"/>
     </row>
     <row r="19" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A19" s="132"/>
+      <c r="A19" s="138"/>
       <c r="B19" s="7" t="s">
         <v>32</v>
       </c>
@@ -4183,7 +4294,7 @@
       <c r="P19" s="14"/>
     </row>
     <row r="20" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A20" s="132"/>
+      <c r="A20" s="138"/>
       <c r="B20" s="7" t="s">
         <v>32</v>
       </c>
@@ -4217,7 +4328,7 @@
       <c r="P20" s="14"/>
     </row>
     <row r="21" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A21" s="125"/>
+      <c r="A21" s="139"/>
       <c r="B21" s="7" t="s">
         <v>32</v>
       </c>
@@ -4269,7 +4380,7 @@
       <c r="P22" s="14"/>
     </row>
     <row r="23" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A23" s="131">
+      <c r="A23" s="143">
         <v>5</v>
       </c>
       <c r="B23" s="7" t="s">
@@ -4307,7 +4418,7 @@
       <c r="P23" s="14"/>
     </row>
     <row r="24" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A24" s="132"/>
+      <c r="A24" s="138"/>
       <c r="B24" s="7" t="s">
         <v>35</v>
       </c>
@@ -4343,7 +4454,7 @@
       <c r="P24" s="14"/>
     </row>
     <row r="25" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A25" s="132"/>
+      <c r="A25" s="138"/>
       <c r="B25" s="7" t="s">
         <v>35</v>
       </c>
@@ -4379,7 +4490,7 @@
       <c r="P25" s="14"/>
     </row>
     <row r="26" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A26" s="125"/>
+      <c r="A26" s="139"/>
       <c r="B26" s="7" t="s">
         <v>35</v>
       </c>
@@ -4433,7 +4544,7 @@
       <c r="P27" s="14"/>
     </row>
     <row r="28" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A28" s="131">
+      <c r="A28" s="143">
         <v>6</v>
       </c>
       <c r="B28" s="7" t="s">
@@ -4471,7 +4582,7 @@
       <c r="P28" s="14"/>
     </row>
     <row r="29" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A29" s="132"/>
+      <c r="A29" s="138"/>
       <c r="B29" s="7" t="s">
         <v>38</v>
       </c>
@@ -4507,7 +4618,7 @@
       <c r="P29" s="14"/>
     </row>
     <row r="30" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A30" s="132"/>
+      <c r="A30" s="138"/>
       <c r="B30" s="7" t="s">
         <v>38</v>
       </c>
@@ -4543,7 +4654,7 @@
       <c r="P30" s="14"/>
     </row>
     <row r="31" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A31" s="125"/>
+      <c r="A31" s="139"/>
       <c r="B31" s="7" t="s">
         <v>38</v>
       </c>
@@ -4597,7 +4708,7 @@
       <c r="P32" s="14"/>
     </row>
     <row r="33" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A33" s="131">
+      <c r="A33" s="143">
         <v>7</v>
       </c>
       <c r="B33" s="7" t="s">
@@ -4635,7 +4746,7 @@
       <c r="P33" s="14"/>
     </row>
     <row r="34" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A34" s="132"/>
+      <c r="A34" s="138"/>
       <c r="B34" s="7" t="s">
         <v>41</v>
       </c>
@@ -4671,7 +4782,7 @@
       <c r="P34" s="14"/>
     </row>
     <row r="35" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A35" s="132"/>
+      <c r="A35" s="138"/>
       <c r="B35" s="7" t="s">
         <v>41</v>
       </c>
@@ -4707,7 +4818,7 @@
       <c r="P35" s="14"/>
     </row>
     <row r="36" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A36" s="125"/>
+      <c r="A36" s="139"/>
       <c r="B36" s="7" t="s">
         <v>41</v>
       </c>
@@ -4761,7 +4872,7 @@
       <c r="P37" s="14"/>
     </row>
     <row r="38" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A38" s="131">
+      <c r="A38" s="143">
         <v>8</v>
       </c>
       <c r="B38" s="7" t="s">
@@ -4799,7 +4910,7 @@
       <c r="P38" s="14"/>
     </row>
     <row r="39" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A39" s="132"/>
+      <c r="A39" s="138"/>
       <c r="B39" s="7" t="s">
         <v>44</v>
       </c>
@@ -4835,7 +4946,7 @@
       <c r="P39" s="14"/>
     </row>
     <row r="40" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A40" s="132"/>
+      <c r="A40" s="138"/>
       <c r="B40" s="7" t="s">
         <v>44</v>
       </c>
@@ -4871,7 +4982,7 @@
       <c r="P40" s="14"/>
     </row>
     <row r="41" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A41" s="125"/>
+      <c r="A41" s="139"/>
       <c r="B41" s="7" t="s">
         <v>44</v>
       </c>
@@ -4925,7 +5036,7 @@
       <c r="P42" s="14"/>
     </row>
     <row r="43" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A43" s="131">
+      <c r="A43" s="143">
         <v>9</v>
       </c>
       <c r="B43" s="7"/>
@@ -4957,7 +5068,7 @@
       <c r="P43" s="14"/>
     </row>
     <row r="44" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A44" s="132"/>
+      <c r="A44" s="138"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7" t="s">
         <v>19</v>
@@ -4987,7 +5098,7 @@
       <c r="P44" s="14"/>
     </row>
     <row r="45" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A45" s="132"/>
+      <c r="A45" s="138"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7" t="s">
         <v>21</v>
@@ -5017,7 +5128,7 @@
       <c r="P45" s="14"/>
     </row>
     <row r="46" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A46" s="125"/>
+      <c r="A46" s="139"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7" t="s">
         <v>23</v>
@@ -5065,7 +5176,7 @@
       <c r="P47" s="14"/>
     </row>
     <row r="48" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A48" s="131">
+      <c r="A48" s="143">
         <v>10</v>
       </c>
       <c r="B48" s="7"/>
@@ -5097,7 +5208,7 @@
       <c r="P48" s="14"/>
     </row>
     <row r="49" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A49" s="132"/>
+      <c r="A49" s="138"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7" t="s">
         <v>19</v>
@@ -5127,7 +5238,7 @@
       <c r="P49" s="14"/>
     </row>
     <row r="50" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A50" s="132"/>
+      <c r="A50" s="138"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7" t="s">
         <v>21</v>
@@ -5157,7 +5268,7 @@
       <c r="P50" s="14"/>
     </row>
     <row r="51" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A51" s="125"/>
+      <c r="A51" s="139"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7" t="s">
         <v>23</v>
@@ -5205,7 +5316,7 @@
       <c r="P52" s="14"/>
     </row>
     <row r="53" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A53" s="131">
+      <c r="A53" s="143">
         <v>11</v>
       </c>
       <c r="B53" s="7" t="s">
@@ -5241,7 +5352,7 @@
       <c r="P53" s="14"/>
     </row>
     <row r="54" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A54" s="132"/>
+      <c r="A54" s="138"/>
       <c r="B54" s="7" t="s">
         <v>49</v>
       </c>
@@ -5275,7 +5386,7 @@
       <c r="P54" s="14"/>
     </row>
     <row r="55" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A55" s="132"/>
+      <c r="A55" s="138"/>
       <c r="B55" s="7" t="s">
         <v>49</v>
       </c>
@@ -5309,7 +5420,7 @@
       <c r="P55" s="14"/>
     </row>
     <row r="56" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A56" s="125"/>
+      <c r="A56" s="139"/>
       <c r="B56" s="7" t="s">
         <v>49</v>
       </c>
@@ -5361,7 +5472,7 @@
       <c r="P57" s="14"/>
     </row>
     <row r="58" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A58" s="131">
+      <c r="A58" s="143">
         <v>12</v>
       </c>
       <c r="B58" s="7" t="s">
@@ -5399,7 +5510,7 @@
       <c r="P58" s="14"/>
     </row>
     <row r="59" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A59" s="132"/>
+      <c r="A59" s="138"/>
       <c r="B59" s="7" t="s">
         <v>52</v>
       </c>
@@ -5435,7 +5546,7 @@
       <c r="P59" s="14"/>
     </row>
     <row r="60" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A60" s="132"/>
+      <c r="A60" s="138"/>
       <c r="B60" s="7" t="s">
         <v>52</v>
       </c>
@@ -5471,7 +5582,7 @@
       <c r="P60" s="14"/>
     </row>
     <row r="61" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A61" s="125"/>
+      <c r="A61" s="139"/>
       <c r="B61" s="7" t="s">
         <v>52</v>
       </c>
@@ -5525,7 +5636,7 @@
       <c r="P62" s="14"/>
     </row>
     <row r="63" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A63" s="131">
+      <c r="A63" s="143">
         <v>13</v>
       </c>
       <c r="B63" s="7"/>
@@ -5555,7 +5666,7 @@
       <c r="N63" s="13"/>
     </row>
     <row r="64" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A64" s="132"/>
+      <c r="A64" s="138"/>
       <c r="B64" s="7"/>
       <c r="C64" s="7" t="s">
         <v>19</v>
@@ -5583,7 +5694,7 @@
       <c r="N64" s="13"/>
     </row>
     <row r="65" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A65" s="132"/>
+      <c r="A65" s="138"/>
       <c r="B65" s="7"/>
       <c r="C65" s="7" t="s">
         <v>21</v>
@@ -5611,7 +5722,7 @@
       <c r="N65" s="13"/>
     </row>
     <row r="66" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A66" s="125"/>
+      <c r="A66" s="139"/>
       <c r="B66" s="7"/>
       <c r="C66" s="7" t="s">
         <v>23</v>
@@ -5655,7 +5766,7 @@
       <c r="N67" s="13"/>
     </row>
     <row r="68" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A68" s="131">
+      <c r="A68" s="143">
         <v>14</v>
       </c>
       <c r="B68" s="7"/>
@@ -5685,7 +5796,7 @@
       <c r="N68" s="13"/>
     </row>
     <row r="69" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A69" s="132"/>
+      <c r="A69" s="138"/>
       <c r="B69" s="7"/>
       <c r="C69" s="7" t="s">
         <v>19</v>
@@ -5713,7 +5824,7 @@
       <c r="N69" s="13"/>
     </row>
     <row r="70" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A70" s="132"/>
+      <c r="A70" s="138"/>
       <c r="B70" s="7"/>
       <c r="C70" s="7" t="s">
         <v>21</v>
@@ -5741,7 +5852,7 @@
       <c r="N70" s="13"/>
     </row>
     <row r="71" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A71" s="125"/>
+      <c r="A71" s="139"/>
       <c r="B71" s="7"/>
       <c r="C71" s="7" t="s">
         <v>23</v>
@@ -5785,7 +5896,7 @@
       <c r="N72" s="13"/>
     </row>
     <row r="73" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A73" s="131">
+      <c r="A73" s="143">
         <v>15</v>
       </c>
       <c r="B73" s="7"/>
@@ -5815,7 +5926,7 @@
       <c r="N73" s="13"/>
     </row>
     <row r="74" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A74" s="132"/>
+      <c r="A74" s="138"/>
       <c r="B74" s="7"/>
       <c r="C74" s="7" t="s">
         <v>19</v>
@@ -5843,7 +5954,7 @@
       <c r="N74" s="13"/>
     </row>
     <row r="75" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A75" s="132"/>
+      <c r="A75" s="138"/>
       <c r="B75" s="7"/>
       <c r="C75" s="7" t="s">
         <v>21</v>
@@ -5871,7 +5982,7 @@
       <c r="N75" s="13"/>
     </row>
     <row r="76" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A76" s="125"/>
+      <c r="A76" s="139"/>
       <c r="B76" s="7"/>
       <c r="C76" s="7" t="s">
         <v>23</v>
@@ -5915,7 +6026,7 @@
       <c r="N77" s="13"/>
     </row>
     <row r="78" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A78" s="131">
+      <c r="A78" s="143">
         <v>16</v>
       </c>
       <c r="B78" s="7"/>
@@ -5948,7 +6059,7 @@
       <c r="Q78" s="14"/>
     </row>
     <row r="79" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A79" s="132"/>
+      <c r="A79" s="138"/>
       <c r="B79" s="7"/>
       <c r="C79" s="7" t="s">
         <v>19</v>
@@ -5979,7 +6090,7 @@
       <c r="Q79" s="14"/>
     </row>
     <row r="80" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A80" s="132"/>
+      <c r="A80" s="138"/>
       <c r="B80" s="7"/>
       <c r="C80" s="7" t="s">
         <v>21</v>
@@ -6010,7 +6121,7 @@
       <c r="Q80" s="14"/>
     </row>
     <row r="81" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A81" s="125"/>
+      <c r="A81" s="139"/>
       <c r="B81" s="7"/>
       <c r="C81" s="7" t="s">
         <v>23</v>
@@ -6060,7 +6171,7 @@
       <c r="Q82" s="14"/>
     </row>
     <row r="83" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A83" s="131">
+      <c r="A83" s="143">
         <v>17</v>
       </c>
       <c r="B83" s="7"/>
@@ -6093,7 +6204,7 @@
       <c r="Q83" s="14"/>
     </row>
     <row r="84" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A84" s="132"/>
+      <c r="A84" s="138"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7" t="s">
         <v>19</v>
@@ -6124,7 +6235,7 @@
       <c r="Q84" s="14"/>
     </row>
     <row r="85" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A85" s="132"/>
+      <c r="A85" s="138"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7" t="s">
         <v>21</v>
@@ -6155,7 +6266,7 @@
       <c r="Q85" s="14"/>
     </row>
     <row r="86" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A86" s="125"/>
+      <c r="A86" s="139"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7" t="s">
         <v>23</v>
@@ -6205,7 +6316,7 @@
       <c r="Q87" s="14"/>
     </row>
     <row r="88" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A88" s="131">
+      <c r="A88" s="143">
         <v>18</v>
       </c>
       <c r="B88" s="7" t="s">
@@ -6242,7 +6353,7 @@
       <c r="Q88" s="14"/>
     </row>
     <row r="89" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A89" s="132"/>
+      <c r="A89" s="138"/>
       <c r="B89" s="7" t="s">
         <v>61</v>
       </c>
@@ -6277,7 +6388,7 @@
       <c r="Q89" s="14"/>
     </row>
     <row r="90" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A90" s="132"/>
+      <c r="A90" s="138"/>
       <c r="B90" s="7" t="s">
         <v>61</v>
       </c>
@@ -6312,7 +6423,7 @@
       <c r="Q90" s="14"/>
     </row>
     <row r="91" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A91" s="125"/>
+      <c r="A91" s="139"/>
       <c r="B91" s="7" t="s">
         <v>61</v>
       </c>
@@ -6366,7 +6477,7 @@
       <c r="Q92" s="14"/>
     </row>
     <row r="93" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A93" s="131">
+      <c r="A93" s="143">
         <v>19</v>
       </c>
       <c r="B93" s="7" t="s">
@@ -6403,7 +6514,7 @@
       <c r="Q93" s="14"/>
     </row>
     <row r="94" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A94" s="132"/>
+      <c r="A94" s="138"/>
       <c r="B94" s="7" t="s">
         <v>64</v>
       </c>
@@ -6438,7 +6549,7 @@
       <c r="Q94" s="14"/>
     </row>
     <row r="95" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A95" s="132"/>
+      <c r="A95" s="138"/>
       <c r="B95" s="7" t="s">
         <v>64</v>
       </c>
@@ -6473,7 +6584,7 @@
       <c r="Q95" s="14"/>
     </row>
     <row r="96" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A96" s="125"/>
+      <c r="A96" s="139"/>
       <c r="B96" s="7" t="s">
         <v>64</v>
       </c>
@@ -6527,7 +6638,7 @@
       <c r="Q97" s="14"/>
     </row>
     <row r="98" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A98" s="131">
+      <c r="A98" s="143">
         <v>20</v>
       </c>
       <c r="B98" s="7" t="s">
@@ -6566,7 +6677,7 @@
       <c r="Q98" s="14"/>
     </row>
     <row r="99" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A99" s="132"/>
+      <c r="A99" s="138"/>
       <c r="B99" s="7" t="s">
         <v>67</v>
       </c>
@@ -6603,7 +6714,7 @@
       <c r="Q99" s="14"/>
     </row>
     <row r="100" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A100" s="132"/>
+      <c r="A100" s="138"/>
       <c r="B100" s="7" t="s">
         <v>67</v>
       </c>
@@ -6640,7 +6751,7 @@
       <c r="Q100" s="14"/>
     </row>
     <row r="101" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A101" s="125"/>
+      <c r="A101" s="139"/>
       <c r="B101" s="7" t="s">
         <v>67</v>
       </c>
@@ -6696,7 +6807,7 @@
       <c r="Q102" s="14"/>
     </row>
     <row r="103" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A103" s="131">
+      <c r="A103" s="143">
         <v>21</v>
       </c>
       <c r="B103" s="7" t="s">
@@ -6735,7 +6846,7 @@
       <c r="Q103" s="14"/>
     </row>
     <row r="104" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A104" s="132"/>
+      <c r="A104" s="138"/>
       <c r="B104" s="7" t="s">
         <v>71</v>
       </c>
@@ -6772,7 +6883,7 @@
       <c r="Q104" s="14"/>
     </row>
     <row r="105" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A105" s="132"/>
+      <c r="A105" s="138"/>
       <c r="B105" s="7" t="s">
         <v>71</v>
       </c>
@@ -6809,7 +6920,7 @@
       <c r="Q105" s="14"/>
     </row>
     <row r="106" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A106" s="125"/>
+      <c r="A106" s="139"/>
       <c r="B106" s="7" t="s">
         <v>71</v>
       </c>
@@ -7034,7 +7145,7 @@
       <c r="Q112" s="14"/>
     </row>
     <row r="113" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A113" s="131">
+      <c r="A113" s="143">
         <v>23</v>
       </c>
       <c r="B113" s="7" t="s">
@@ -7073,7 +7184,7 @@
       <c r="Q113" s="14"/>
     </row>
     <row r="114" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A114" s="132"/>
+      <c r="A114" s="138"/>
       <c r="B114" s="7" t="s">
         <v>78</v>
       </c>
@@ -7110,7 +7221,7 @@
       <c r="Q114" s="14"/>
     </row>
     <row r="115" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A115" s="132"/>
+      <c r="A115" s="138"/>
       <c r="B115" s="7" t="s">
         <v>78</v>
       </c>
@@ -7147,7 +7258,7 @@
       <c r="Q115" s="14"/>
     </row>
     <row r="116" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A116" s="125"/>
+      <c r="A116" s="139"/>
       <c r="B116" s="7" t="s">
         <v>78</v>
       </c>
@@ -7203,7 +7314,7 @@
       <c r="Q117" s="14"/>
     </row>
     <row r="118" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A118" s="131">
+      <c r="A118" s="143">
         <v>24</v>
       </c>
       <c r="B118" s="7" t="s">
@@ -7242,7 +7353,7 @@
       <c r="Q118" s="14"/>
     </row>
     <row r="119" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A119" s="132"/>
+      <c r="A119" s="138"/>
       <c r="B119" s="7" t="s">
         <v>82</v>
       </c>
@@ -7279,7 +7390,7 @@
       <c r="Q119" s="14"/>
     </row>
     <row r="120" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A120" s="132"/>
+      <c r="A120" s="138"/>
       <c r="B120" s="7" t="s">
         <v>82</v>
       </c>
@@ -7316,7 +7427,7 @@
       <c r="Q120" s="14"/>
     </row>
     <row r="121" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A121" s="125"/>
+      <c r="A121" s="139"/>
       <c r="B121" s="7" t="s">
         <v>82</v>
       </c>
@@ -7372,7 +7483,7 @@
       <c r="Q122" s="14"/>
     </row>
     <row r="123" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A123" s="131">
+      <c r="A123" s="143">
         <v>25</v>
       </c>
       <c r="B123" s="7" t="s">
@@ -7409,7 +7520,7 @@
       <c r="Q123" s="14"/>
     </row>
     <row r="124" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A124" s="132"/>
+      <c r="A124" s="138"/>
       <c r="B124" s="7" t="s">
         <v>86</v>
       </c>
@@ -7444,7 +7555,7 @@
       <c r="Q124" s="14"/>
     </row>
     <row r="125" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A125" s="132"/>
+      <c r="A125" s="138"/>
       <c r="B125" s="7" t="s">
         <v>86</v>
       </c>
@@ -7479,7 +7590,7 @@
       <c r="Q125" s="14"/>
     </row>
     <row r="126" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A126" s="125"/>
+      <c r="A126" s="139"/>
       <c r="B126" s="7" t="s">
         <v>86</v>
       </c>
@@ -7533,7 +7644,7 @@
       <c r="Q127" s="14"/>
     </row>
     <row r="128" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A128" s="131">
+      <c r="A128" s="143">
         <v>26</v>
       </c>
       <c r="B128" s="7" t="s">
@@ -7570,7 +7681,7 @@
       <c r="Q128" s="14"/>
     </row>
     <row r="129" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A129" s="132"/>
+      <c r="A129" s="138"/>
       <c r="B129" s="7" t="s">
         <v>89</v>
       </c>
@@ -7605,7 +7716,7 @@
       <c r="Q129" s="14"/>
     </row>
     <row r="130" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A130" s="132"/>
+      <c r="A130" s="138"/>
       <c r="B130" s="7" t="s">
         <v>89</v>
       </c>
@@ -7640,7 +7751,7 @@
       <c r="Q130" s="14"/>
     </row>
     <row r="131" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A131" s="125"/>
+      <c r="A131" s="139"/>
       <c r="B131" s="7" t="s">
         <v>89</v>
       </c>
@@ -7694,7 +7805,7 @@
       <c r="Q132" s="14"/>
     </row>
     <row r="133" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A133" s="131">
+      <c r="A133" s="143">
         <v>27</v>
       </c>
       <c r="B133" s="7" t="s">
@@ -7733,7 +7844,7 @@
       <c r="Q133" s="14"/>
     </row>
     <row r="134" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A134" s="132"/>
+      <c r="A134" s="138"/>
       <c r="B134" s="7" t="s">
         <v>92</v>
       </c>
@@ -7770,7 +7881,7 @@
       <c r="Q134" s="14"/>
     </row>
     <row r="135" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A135" s="132"/>
+      <c r="A135" s="138"/>
       <c r="B135" s="7" t="s">
         <v>92</v>
       </c>
@@ -7807,7 +7918,7 @@
       <c r="Q135" s="14"/>
     </row>
     <row r="136" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A136" s="125"/>
+      <c r="A136" s="139"/>
       <c r="B136" s="7" t="s">
         <v>92</v>
       </c>
@@ -7863,7 +7974,7 @@
       <c r="Q137" s="14"/>
     </row>
     <row r="138" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A138" s="131">
+      <c r="A138" s="143">
         <v>28</v>
       </c>
       <c r="B138" s="7" t="s">
@@ -7902,7 +8013,7 @@
       <c r="Q138" s="14"/>
     </row>
     <row r="139" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A139" s="132"/>
+      <c r="A139" s="138"/>
       <c r="B139" s="7" t="s">
         <v>96</v>
       </c>
@@ -7939,7 +8050,7 @@
       <c r="Q139" s="14"/>
     </row>
     <row r="140" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A140" s="132"/>
+      <c r="A140" s="138"/>
       <c r="B140" s="7" t="s">
         <v>96</v>
       </c>
@@ -7976,7 +8087,7 @@
       <c r="Q140" s="14"/>
     </row>
     <row r="141" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A141" s="125"/>
+      <c r="A141" s="139"/>
       <c r="B141" s="7" t="s">
         <v>96</v>
       </c>
@@ -8032,7 +8143,7 @@
       <c r="Q142" s="14"/>
     </row>
     <row r="143" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A143" s="131">
+      <c r="A143" s="143">
         <v>29</v>
       </c>
       <c r="B143" s="7" t="s">
@@ -8069,7 +8180,7 @@
       <c r="Q143" s="14"/>
     </row>
     <row r="144" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A144" s="132"/>
+      <c r="A144" s="138"/>
       <c r="B144" s="7" t="s">
         <v>100</v>
       </c>
@@ -8104,7 +8215,7 @@
       <c r="Q144" s="14"/>
     </row>
     <row r="145" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A145" s="132"/>
+      <c r="A145" s="138"/>
       <c r="B145" s="7" t="s">
         <v>100</v>
       </c>
@@ -8139,7 +8250,7 @@
       <c r="Q145" s="14"/>
     </row>
     <row r="146" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A146" s="125"/>
+      <c r="A146" s="139"/>
       <c r="B146" s="7" t="s">
         <v>100</v>
       </c>
@@ -8193,7 +8304,7 @@
       <c r="Q147" s="14"/>
     </row>
     <row r="148" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A148" s="131">
+      <c r="A148" s="143">
         <v>30</v>
       </c>
       <c r="B148" s="7" t="s">
@@ -8230,7 +8341,7 @@
       <c r="Q148" s="14"/>
     </row>
     <row r="149" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A149" s="132"/>
+      <c r="A149" s="138"/>
       <c r="B149" s="7" t="s">
         <v>103</v>
       </c>
@@ -8265,7 +8376,7 @@
       <c r="Q149" s="14"/>
     </row>
     <row r="150" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A150" s="132"/>
+      <c r="A150" s="138"/>
       <c r="B150" s="7" t="s">
         <v>103</v>
       </c>
@@ -8300,7 +8411,7 @@
       <c r="Q150" s="14"/>
     </row>
     <row r="151" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A151" s="125"/>
+      <c r="A151" s="139"/>
       <c r="B151" s="7" t="s">
         <v>103</v>
       </c>
@@ -8354,7 +8465,7 @@
       <c r="Q152" s="14"/>
     </row>
     <row r="153" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A153" s="131">
+      <c r="A153" s="143">
         <v>31</v>
       </c>
       <c r="B153" s="7" t="s">
@@ -8393,7 +8504,7 @@
       <c r="Q153" s="14"/>
     </row>
     <row r="154" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A154" s="132"/>
+      <c r="A154" s="138"/>
       <c r="B154" s="7" t="s">
         <v>106</v>
       </c>
@@ -8430,7 +8541,7 @@
       <c r="Q154" s="14"/>
     </row>
     <row r="155" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A155" s="132"/>
+      <c r="A155" s="138"/>
       <c r="B155" s="7" t="s">
         <v>106</v>
       </c>
@@ -8467,7 +8578,7 @@
       <c r="Q155" s="14"/>
     </row>
     <row r="156" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A156" s="125"/>
+      <c r="A156" s="139"/>
       <c r="B156" s="7" t="s">
         <v>106</v>
       </c>
@@ -8523,7 +8634,7 @@
       <c r="Q157" s="14"/>
     </row>
     <row r="158" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A158" s="131">
+      <c r="A158" s="143">
         <v>32</v>
       </c>
       <c r="B158" s="7" t="s">
@@ -8562,7 +8673,7 @@
       <c r="Q158" s="14"/>
     </row>
     <row r="159" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A159" s="132"/>
+      <c r="A159" s="138"/>
       <c r="B159" s="7" t="s">
         <v>109</v>
       </c>
@@ -8599,7 +8710,7 @@
       <c r="Q159" s="14"/>
     </row>
     <row r="160" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A160" s="132"/>
+      <c r="A160" s="138"/>
       <c r="B160" s="7" t="s">
         <v>109</v>
       </c>
@@ -8636,7 +8747,7 @@
       <c r="Q160" s="14"/>
     </row>
     <row r="161" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A161" s="125"/>
+      <c r="A161" s="139"/>
       <c r="B161" s="7" t="s">
         <v>109</v>
       </c>
@@ -8692,7 +8803,7 @@
       <c r="Q162" s="14"/>
     </row>
     <row r="163" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A163" s="131">
+      <c r="A163" s="143">
         <v>33</v>
       </c>
       <c r="B163" s="7" t="s">
@@ -8731,7 +8842,7 @@
       <c r="Q163" s="14"/>
     </row>
     <row r="164" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A164" s="132"/>
+      <c r="A164" s="138"/>
       <c r="B164" s="7" t="s">
         <v>114</v>
       </c>
@@ -8768,7 +8879,7 @@
       <c r="Q164" s="14"/>
     </row>
     <row r="165" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A165" s="132"/>
+      <c r="A165" s="138"/>
       <c r="B165" s="7" t="s">
         <v>114</v>
       </c>
@@ -8805,7 +8916,7 @@
       <c r="Q165" s="14"/>
     </row>
     <row r="166" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A166" s="125"/>
+      <c r="A166" s="139"/>
       <c r="B166" s="7" t="s">
         <v>114</v>
       </c>
@@ -8861,7 +8972,7 @@
       <c r="Q167" s="14"/>
     </row>
     <row r="168" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A168" s="131">
+      <c r="A168" s="143">
         <v>34</v>
       </c>
       <c r="B168" s="7" t="s">
@@ -8893,7 +9004,7 @@
       <c r="N168" s="13"/>
     </row>
     <row r="169" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A169" s="132"/>
+      <c r="A169" s="138"/>
       <c r="B169" s="7" t="s">
         <v>117</v>
       </c>
@@ -8923,7 +9034,7 @@
       <c r="N169" s="13"/>
     </row>
     <row r="170" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A170" s="125"/>
+      <c r="A170" s="139"/>
       <c r="B170" s="7" t="s">
         <v>117</v>
       </c>
@@ -8969,7 +9080,7 @@
       <c r="N171" s="13"/>
     </row>
     <row r="172" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A172" s="131">
+      <c r="A172" s="143">
         <v>35</v>
       </c>
       <c r="B172" s="7" t="s">
@@ -9001,7 +9112,7 @@
       <c r="N172" s="13"/>
     </row>
     <row r="173" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A173" s="132"/>
+      <c r="A173" s="138"/>
       <c r="B173" s="7" t="s">
         <v>121</v>
       </c>
@@ -9031,7 +9142,7 @@
       <c r="N173" s="13"/>
     </row>
     <row r="174" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A174" s="125"/>
+      <c r="A174" s="139"/>
       <c r="B174" s="7" t="s">
         <v>121</v>
       </c>
@@ -9077,7 +9188,7 @@
       <c r="N175" s="13"/>
     </row>
     <row r="176" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A176" s="131">
+      <c r="A176" s="143">
         <v>36</v>
       </c>
       <c r="B176" s="7" t="s">
@@ -9111,7 +9222,7 @@
       <c r="N176" s="13"/>
     </row>
     <row r="177" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A177" s="132"/>
+      <c r="A177" s="138"/>
       <c r="B177" s="7" t="s">
         <v>123</v>
       </c>
@@ -9143,7 +9254,7 @@
       <c r="N177" s="13"/>
     </row>
     <row r="178" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A178" s="132"/>
+      <c r="A178" s="138"/>
       <c r="B178" s="7" t="s">
         <v>123</v>
       </c>
@@ -9175,7 +9286,7 @@
       <c r="N178" s="13"/>
     </row>
     <row r="179" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A179" s="125"/>
+      <c r="A179" s="139"/>
       <c r="B179" s="7" t="s">
         <v>123</v>
       </c>
@@ -9223,7 +9334,7 @@
       <c r="N180" s="13"/>
     </row>
     <row r="181" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A181" s="131">
+      <c r="A181" s="143">
         <v>37</v>
       </c>
       <c r="B181" s="7" t="s">
@@ -9257,7 +9368,7 @@
       <c r="N181" s="13"/>
     </row>
     <row r="182" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A182" s="132"/>
+      <c r="A182" s="138"/>
       <c r="B182" s="7" t="s">
         <v>126</v>
       </c>
@@ -9289,7 +9400,7 @@
       <c r="N182" s="13"/>
     </row>
     <row r="183" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A183" s="132"/>
+      <c r="A183" s="138"/>
       <c r="B183" s="7" t="s">
         <v>126</v>
       </c>
@@ -9321,7 +9432,7 @@
       <c r="N183" s="13"/>
     </row>
     <row r="184" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A184" s="125"/>
+      <c r="A184" s="139"/>
       <c r="B184" s="7" t="s">
         <v>126</v>
       </c>
@@ -9369,7 +9480,7 @@
       <c r="N185" s="13"/>
     </row>
     <row r="186" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A186" s="131">
+      <c r="A186" s="143">
         <v>38</v>
       </c>
       <c r="B186" s="7" t="s">
@@ -9405,7 +9516,7 @@
       </c>
     </row>
     <row r="187" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A187" s="132"/>
+      <c r="A187" s="138"/>
       <c r="B187" s="7" t="s">
         <v>128</v>
       </c>
@@ -9439,7 +9550,7 @@
       </c>
     </row>
     <row r="188" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A188" s="132"/>
+      <c r="A188" s="138"/>
       <c r="B188" s="7" t="s">
         <v>128</v>
       </c>
@@ -9473,7 +9584,7 @@
       </c>
     </row>
     <row r="189" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A189" s="125"/>
+      <c r="A189" s="139"/>
       <c r="B189" s="7" t="s">
         <v>128</v>
       </c>
@@ -9523,7 +9634,7 @@
       <c r="N190" s="13"/>
     </row>
     <row r="191" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A191" s="131">
+      <c r="A191" s="143">
         <v>39</v>
       </c>
       <c r="B191" s="7" t="s">
@@ -9559,7 +9670,7 @@
       </c>
     </row>
     <row r="192" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A192" s="132"/>
+      <c r="A192" s="138"/>
       <c r="B192" s="7" t="s">
         <v>131</v>
       </c>
@@ -9593,7 +9704,7 @@
       </c>
     </row>
     <row r="193" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A193" s="132"/>
+      <c r="A193" s="138"/>
       <c r="B193" s="7" t="s">
         <v>131</v>
       </c>
@@ -9627,7 +9738,7 @@
       </c>
     </row>
     <row r="194" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A194" s="125"/>
+      <c r="A194" s="139"/>
       <c r="B194" s="7" t="s">
         <v>131</v>
       </c>
@@ -9677,7 +9788,7 @@
       <c r="N195" s="13"/>
     </row>
     <row r="196" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A196" s="131">
+      <c r="A196" s="143">
         <v>40</v>
       </c>
       <c r="B196" s="7" t="s">
@@ -9713,7 +9824,7 @@
       </c>
     </row>
     <row r="197" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A197" s="132"/>
+      <c r="A197" s="138"/>
       <c r="B197" s="7" t="s">
         <v>132</v>
       </c>
@@ -9747,7 +9858,7 @@
       </c>
     </row>
     <row r="198" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A198" s="132"/>
+      <c r="A198" s="138"/>
       <c r="B198" s="7" t="s">
         <v>132</v>
       </c>
@@ -9781,7 +9892,7 @@
       </c>
     </row>
     <row r="199" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A199" s="125"/>
+      <c r="A199" s="139"/>
       <c r="B199" s="7" t="s">
         <v>132</v>
       </c>
@@ -9831,7 +9942,7 @@
       <c r="N200" s="13"/>
     </row>
     <row r="201" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A201" s="131">
+      <c r="A201" s="143">
         <v>41</v>
       </c>
       <c r="B201" s="7" t="s">
@@ -9867,7 +9978,7 @@
       </c>
     </row>
     <row r="202" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A202" s="132"/>
+      <c r="A202" s="138"/>
       <c r="B202" s="7" t="s">
         <v>135</v>
       </c>
@@ -9901,7 +10012,7 @@
       </c>
     </row>
     <row r="203" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A203" s="132"/>
+      <c r="A203" s="138"/>
       <c r="B203" s="7" t="s">
         <v>135</v>
       </c>
@@ -9935,7 +10046,7 @@
       </c>
     </row>
     <row r="204" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A204" s="125"/>
+      <c r="A204" s="139"/>
       <c r="B204" s="7" t="s">
         <v>135</v>
       </c>
@@ -9985,7 +10096,7 @@
       <c r="N205" s="13"/>
     </row>
     <row r="206" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A206" s="131">
+      <c r="A206" s="143">
         <v>42</v>
       </c>
       <c r="B206" s="7" t="s">
@@ -9994,7 +10105,7 @@
       <c r="C206" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D206" s="150" t="s">
+      <c r="D206" s="129" t="s">
         <v>138</v>
       </c>
       <c r="E206" s="9" t="s">
@@ -10021,7 +10132,7 @@
       </c>
     </row>
     <row r="207" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A207" s="132"/>
+      <c r="A207" s="138"/>
       <c r="B207" s="21" t="s">
         <v>137</v>
       </c>
@@ -10055,7 +10166,7 @@
       </c>
     </row>
     <row r="208" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A208" s="132"/>
+      <c r="A208" s="138"/>
       <c r="B208" s="21" t="s">
         <v>137</v>
       </c>
@@ -10089,7 +10200,7 @@
       </c>
     </row>
     <row r="209" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A209" s="125"/>
+      <c r="A209" s="139"/>
       <c r="B209" s="21" t="s">
         <v>137</v>
       </c>
@@ -10139,7 +10250,7 @@
       <c r="N210" s="13"/>
     </row>
     <row r="211" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A211" s="131">
+      <c r="A211" s="143">
         <v>43</v>
       </c>
       <c r="B211" s="7" t="s">
@@ -10175,7 +10286,7 @@
       </c>
     </row>
     <row r="212" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A212" s="132"/>
+      <c r="A212" s="138"/>
       <c r="B212" s="21" t="s">
         <v>140</v>
       </c>
@@ -10209,7 +10320,7 @@
       </c>
     </row>
     <row r="213" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A213" s="132"/>
+      <c r="A213" s="138"/>
       <c r="B213" s="21" t="s">
         <v>140</v>
       </c>
@@ -10243,7 +10354,7 @@
       </c>
     </row>
     <row r="214" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A214" s="125"/>
+      <c r="A214" s="139"/>
       <c r="B214" s="21" t="s">
         <v>140</v>
       </c>
@@ -10293,7 +10404,7 @@
       <c r="N215" s="13"/>
     </row>
     <row r="216" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A216" s="131">
+      <c r="A216" s="143">
         <v>44</v>
       </c>
       <c r="B216" s="7" t="s">
@@ -10329,7 +10440,7 @@
       </c>
     </row>
     <row r="217" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A217" s="132"/>
+      <c r="A217" s="138"/>
       <c r="B217" s="21" t="s">
         <v>142</v>
       </c>
@@ -10363,7 +10474,7 @@
       </c>
     </row>
     <row r="218" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A218" s="132"/>
+      <c r="A218" s="138"/>
       <c r="B218" s="21" t="s">
         <v>142</v>
       </c>
@@ -10397,7 +10508,7 @@
       </c>
     </row>
     <row r="219" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A219" s="125"/>
+      <c r="A219" s="139"/>
       <c r="B219" s="21" t="s">
         <v>142</v>
       </c>
@@ -10447,7 +10558,7 @@
       <c r="N220" s="13"/>
     </row>
     <row r="221" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A221" s="131">
+      <c r="A221" s="143">
         <v>45</v>
       </c>
       <c r="B221" s="7" t="s">
@@ -10483,7 +10594,7 @@
       </c>
     </row>
     <row r="222" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A222" s="132"/>
+      <c r="A222" s="138"/>
       <c r="B222" s="21" t="s">
         <v>144</v>
       </c>
@@ -10517,7 +10628,7 @@
       </c>
     </row>
     <row r="223" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A223" s="132"/>
+      <c r="A223" s="138"/>
       <c r="B223" s="21" t="s">
         <v>144</v>
       </c>
@@ -10551,7 +10662,7 @@
       </c>
     </row>
     <row r="224" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A224" s="125"/>
+      <c r="A224" s="139"/>
       <c r="B224" s="21" t="s">
         <v>144</v>
       </c>
@@ -10601,7 +10712,7 @@
       <c r="N225" s="13"/>
     </row>
     <row r="226" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A226" s="131">
+      <c r="A226" s="143">
         <v>46</v>
       </c>
       <c r="B226" s="7" t="s">
@@ -10637,7 +10748,7 @@
       </c>
     </row>
     <row r="227" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A227" s="132"/>
+      <c r="A227" s="138"/>
       <c r="B227" s="21" t="s">
         <v>146</v>
       </c>
@@ -10671,7 +10782,7 @@
       </c>
     </row>
     <row r="228" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A228" s="132"/>
+      <c r="A228" s="138"/>
       <c r="B228" s="21" t="s">
         <v>146</v>
       </c>
@@ -10705,7 +10816,7 @@
       </c>
     </row>
     <row r="229" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A229" s="125"/>
+      <c r="A229" s="139"/>
       <c r="B229" s="21" t="s">
         <v>146</v>
       </c>
@@ -10755,7 +10866,7 @@
       <c r="N230" s="13"/>
     </row>
     <row r="231" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A231" s="131">
+      <c r="A231" s="143">
         <v>47</v>
       </c>
       <c r="B231" s="7" t="s">
@@ -10791,7 +10902,7 @@
       </c>
     </row>
     <row r="232" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A232" s="132"/>
+      <c r="A232" s="138"/>
       <c r="B232" s="7" t="s">
         <v>148</v>
       </c>
@@ -10825,7 +10936,7 @@
       </c>
     </row>
     <row r="233" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A233" s="132"/>
+      <c r="A233" s="138"/>
       <c r="B233" s="7" t="s">
         <v>148</v>
       </c>
@@ -10859,7 +10970,7 @@
       </c>
     </row>
     <row r="234" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A234" s="125"/>
+      <c r="A234" s="139"/>
       <c r="B234" s="7" t="s">
         <v>148</v>
       </c>
@@ -10909,7 +11020,7 @@
       <c r="N235" s="13"/>
     </row>
     <row r="236" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A236" s="131">
+      <c r="A236" s="143">
         <v>48</v>
       </c>
       <c r="B236" s="7" t="s">
@@ -10943,7 +11054,7 @@
       <c r="N236" s="13"/>
     </row>
     <row r="237" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A237" s="132"/>
+      <c r="A237" s="138"/>
       <c r="B237" s="21" t="s">
         <v>151</v>
       </c>
@@ -10975,7 +11086,7 @@
       <c r="N237" s="27"/>
     </row>
     <row r="238" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A238" s="132"/>
+      <c r="A238" s="138"/>
       <c r="B238" s="21" t="s">
         <v>151</v>
       </c>
@@ -11007,7 +11118,7 @@
       <c r="N238" s="27"/>
     </row>
     <row r="239" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A239" s="125"/>
+      <c r="A239" s="139"/>
       <c r="B239" s="21" t="s">
         <v>151</v>
       </c>
@@ -11055,7 +11166,7 @@
       <c r="N240" s="13"/>
     </row>
     <row r="241" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A241" s="131">
+      <c r="A241" s="143">
         <v>49</v>
       </c>
       <c r="B241" s="7" t="s">
@@ -11089,7 +11200,7 @@
       <c r="N241" s="13"/>
     </row>
     <row r="242" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A242" s="132"/>
+      <c r="A242" s="138"/>
       <c r="B242" s="21" t="s">
         <v>154</v>
       </c>
@@ -11121,7 +11232,7 @@
       <c r="N242" s="27"/>
     </row>
     <row r="243" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A243" s="132"/>
+      <c r="A243" s="138"/>
       <c r="B243" s="21" t="s">
         <v>154</v>
       </c>
@@ -11153,7 +11264,7 @@
       <c r="N243" s="27"/>
     </row>
     <row r="244" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A244" s="125"/>
+      <c r="A244" s="139"/>
       <c r="B244" s="21" t="s">
         <v>154</v>
       </c>
@@ -11201,7 +11312,7 @@
       <c r="N245" s="13"/>
     </row>
     <row r="246" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A246" s="131">
+      <c r="A246" s="143">
         <v>50</v>
       </c>
       <c r="B246" s="7" t="s">
@@ -11235,7 +11346,7 @@
       <c r="N246" s="13"/>
     </row>
     <row r="247" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A247" s="132"/>
+      <c r="A247" s="138"/>
       <c r="B247" s="21" t="s">
         <v>155</v>
       </c>
@@ -11267,7 +11378,7 @@
       <c r="N247" s="27"/>
     </row>
     <row r="248" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A248" s="132"/>
+      <c r="A248" s="138"/>
       <c r="B248" s="21" t="s">
         <v>155</v>
       </c>
@@ -11299,7 +11410,7 @@
       <c r="N248" s="27"/>
     </row>
     <row r="249" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A249" s="125"/>
+      <c r="A249" s="139"/>
       <c r="B249" s="21" t="s">
         <v>155</v>
       </c>
@@ -11347,7 +11458,7 @@
       <c r="N250" s="13"/>
     </row>
     <row r="251" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A251" s="131">
+      <c r="A251" s="143">
         <v>51</v>
       </c>
       <c r="B251" s="7"/>
@@ -11377,7 +11488,7 @@
       <c r="N251" s="13"/>
     </row>
     <row r="252" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A252" s="132"/>
+      <c r="A252" s="138"/>
       <c r="B252" s="7"/>
       <c r="C252" s="7" t="s">
         <v>19</v>
@@ -11405,7 +11516,7 @@
       <c r="N252" s="13"/>
     </row>
     <row r="253" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A253" s="132"/>
+      <c r="A253" s="138"/>
       <c r="B253" s="7"/>
       <c r="C253" s="7" t="s">
         <v>21</v>
@@ -11433,7 +11544,7 @@
       <c r="N253" s="13"/>
     </row>
     <row r="254" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A254" s="125"/>
+      <c r="A254" s="139"/>
       <c r="B254" s="7"/>
       <c r="C254" s="7" t="s">
         <v>23</v>
@@ -11477,7 +11588,7 @@
       <c r="N255" s="13"/>
     </row>
     <row r="256" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A256" s="131">
+      <c r="A256" s="143">
         <v>52</v>
       </c>
       <c r="B256" s="7"/>
@@ -11507,7 +11618,7 @@
       <c r="N256" s="13"/>
     </row>
     <row r="257" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A257" s="132"/>
+      <c r="A257" s="138"/>
       <c r="B257" s="7"/>
       <c r="C257" s="7" t="s">
         <v>19</v>
@@ -11535,7 +11646,7 @@
       <c r="N257" s="13"/>
     </row>
     <row r="258" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A258" s="132"/>
+      <c r="A258" s="138"/>
       <c r="B258" s="7"/>
       <c r="C258" s="7" t="s">
         <v>21</v>
@@ -11563,7 +11674,7 @@
       <c r="N258" s="13"/>
     </row>
     <row r="259" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A259" s="125"/>
+      <c r="A259" s="139"/>
       <c r="B259" s="7"/>
       <c r="C259" s="7" t="s">
         <v>23</v>
@@ -11607,7 +11718,7 @@
       <c r="N260" s="13"/>
     </row>
     <row r="261" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A261" s="131">
+      <c r="A261" s="143">
         <v>53</v>
       </c>
       <c r="B261" s="7"/>
@@ -11637,7 +11748,7 @@
       <c r="N261" s="13"/>
     </row>
     <row r="262" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A262" s="132"/>
+      <c r="A262" s="138"/>
       <c r="B262" s="7"/>
       <c r="C262" s="7" t="s">
         <v>19</v>
@@ -11665,7 +11776,7 @@
       <c r="N262" s="13"/>
     </row>
     <row r="263" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A263" s="132"/>
+      <c r="A263" s="138"/>
       <c r="B263" s="7"/>
       <c r="C263" s="7" t="s">
         <v>21</v>
@@ -11693,7 +11804,7 @@
       <c r="N263" s="13"/>
     </row>
     <row r="264" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A264" s="125"/>
+      <c r="A264" s="139"/>
       <c r="B264" s="7"/>
       <c r="C264" s="7" t="s">
         <v>23</v>
@@ -11737,7 +11848,7 @@
       <c r="N265" s="13"/>
     </row>
     <row r="266" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A266" s="131">
+      <c r="A266" s="143">
         <v>54</v>
       </c>
       <c r="B266" s="7"/>
@@ -11767,7 +11878,7 @@
       <c r="N266" s="13"/>
     </row>
     <row r="267" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A267" s="132"/>
+      <c r="A267" s="138"/>
       <c r="B267" s="7"/>
       <c r="C267" s="7" t="s">
         <v>19</v>
@@ -11795,7 +11906,7 @@
       <c r="N267" s="13"/>
     </row>
     <row r="268" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A268" s="132"/>
+      <c r="A268" s="138"/>
       <c r="B268" s="7"/>
       <c r="C268" s="7" t="s">
         <v>21</v>
@@ -11823,7 +11934,7 @@
       <c r="N268" s="13"/>
     </row>
     <row r="269" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A269" s="125"/>
+      <c r="A269" s="139"/>
       <c r="B269" s="7"/>
       <c r="C269" s="7" t="s">
         <v>23</v>
@@ -11867,7 +11978,7 @@
       <c r="N270" s="13"/>
     </row>
     <row r="271" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A271" s="131">
+      <c r="A271" s="143">
         <v>55</v>
       </c>
       <c r="B271" s="7"/>
@@ -11897,7 +12008,7 @@
       <c r="N271" s="13"/>
     </row>
     <row r="272" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A272" s="132"/>
+      <c r="A272" s="138"/>
       <c r="B272" s="7"/>
       <c r="C272" s="7" t="s">
         <v>19</v>
@@ -11925,7 +12036,7 @@
       <c r="N272" s="13"/>
     </row>
     <row r="273" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A273" s="132"/>
+      <c r="A273" s="138"/>
       <c r="B273" s="7"/>
       <c r="C273" s="7" t="s">
         <v>21</v>
@@ -11953,7 +12064,7 @@
       <c r="N273" s="13"/>
     </row>
     <row r="274" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A274" s="125"/>
+      <c r="A274" s="139"/>
       <c r="B274" s="7"/>
       <c r="C274" s="7" t="s">
         <v>23</v>
@@ -11997,7 +12108,7 @@
       <c r="N275" s="13"/>
     </row>
     <row r="276" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A276" s="131">
+      <c r="A276" s="143">
         <v>56</v>
       </c>
       <c r="B276" s="7" t="s">
@@ -12031,7 +12142,7 @@
       </c>
     </row>
     <row r="277" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A277" s="132"/>
+      <c r="A277" s="138"/>
       <c r="B277" s="7" t="s">
         <v>162</v>
       </c>
@@ -12063,7 +12174,7 @@
       </c>
     </row>
     <row r="278" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A278" s="132"/>
+      <c r="A278" s="138"/>
       <c r="B278" s="7" t="s">
         <v>162</v>
       </c>
@@ -12095,7 +12206,7 @@
       </c>
     </row>
     <row r="279" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A279" s="125"/>
+      <c r="A279" s="139"/>
       <c r="B279" s="28" t="s">
         <v>162</v>
       </c>
@@ -12175,7 +12286,7 @@
       <c r="N282" s="13"/>
     </row>
     <row r="283" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A283" s="131">
+      <c r="A283" s="143">
         <v>60</v>
       </c>
       <c r="B283" s="8" t="s">
@@ -12209,7 +12320,7 @@
       <c r="N283" s="13"/>
     </row>
     <row r="284" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A284" s="132"/>
+      <c r="A284" s="138"/>
       <c r="B284" s="8" t="s">
         <v>165</v>
       </c>
@@ -12241,7 +12352,7 @@
       <c r="N284" s="13"/>
     </row>
     <row r="285" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A285" s="132"/>
+      <c r="A285" s="138"/>
       <c r="B285" s="8" t="s">
         <v>165</v>
       </c>
@@ -12273,7 +12384,7 @@
       <c r="N285" s="13"/>
     </row>
     <row r="286" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A286" s="125"/>
+      <c r="A286" s="139"/>
       <c r="B286" s="8" t="s">
         <v>165</v>
       </c>
@@ -12321,7 +12432,7 @@
       <c r="N287" s="13"/>
     </row>
     <row r="288" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A288" s="131">
+      <c r="A288" s="143">
         <v>61</v>
       </c>
       <c r="B288" s="19" t="s">
@@ -12355,7 +12466,7 @@
       <c r="N288" s="36"/>
     </row>
     <row r="289" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A289" s="132"/>
+      <c r="A289" s="138"/>
       <c r="B289" s="19" t="s">
         <v>168</v>
       </c>
@@ -12387,7 +12498,7 @@
       <c r="N289" s="36"/>
     </row>
     <row r="290" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A290" s="132"/>
+      <c r="A290" s="138"/>
       <c r="B290" s="19" t="s">
         <v>168</v>
       </c>
@@ -12419,7 +12530,7 @@
       <c r="N290" s="36"/>
     </row>
     <row r="291" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A291" s="125"/>
+      <c r="A291" s="139"/>
       <c r="B291" s="19" t="s">
         <v>168</v>
       </c>
@@ -12467,7 +12578,7 @@
       <c r="N292" s="36"/>
     </row>
     <row r="293" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A293" s="131">
+      <c r="A293" s="143">
         <v>62</v>
       </c>
       <c r="B293" s="19" t="s">
@@ -12501,7 +12612,7 @@
       <c r="N293" s="13"/>
     </row>
     <row r="294" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A294" s="132"/>
+      <c r="A294" s="138"/>
       <c r="B294" s="19" t="s">
         <v>171</v>
       </c>
@@ -12533,7 +12644,7 @@
       <c r="N294" s="13"/>
     </row>
     <row r="295" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A295" s="132"/>
+      <c r="A295" s="138"/>
       <c r="B295" s="19" t="s">
         <v>171</v>
       </c>
@@ -12565,7 +12676,7 @@
       <c r="N295" s="13"/>
     </row>
     <row r="296" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A296" s="125"/>
+      <c r="A296" s="139"/>
       <c r="B296" s="19" t="s">
         <v>171</v>
       </c>
@@ -12613,7 +12724,7 @@
       <c r="N297" s="13"/>
     </row>
     <row r="298" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A298" s="131">
+      <c r="A298" s="143">
         <v>65</v>
       </c>
       <c r="B298" s="37">
@@ -12647,7 +12758,7 @@
       <c r="N298" s="13"/>
     </row>
     <row r="299" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A299" s="132"/>
+      <c r="A299" s="138"/>
       <c r="B299" s="37">
         <v>13</v>
       </c>
@@ -12679,7 +12790,7 @@
       <c r="N299" s="13"/>
     </row>
     <row r="300" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A300" s="132"/>
+      <c r="A300" s="138"/>
       <c r="B300" s="37">
         <v>13</v>
       </c>
@@ -12711,7 +12822,7 @@
       <c r="N300" s="13"/>
     </row>
     <row r="301" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A301" s="125"/>
+      <c r="A301" s="139"/>
       <c r="B301" s="37">
         <v>13</v>
       </c>
@@ -12905,7 +13016,7 @@
       <c r="N307" s="13"/>
     </row>
     <row r="308" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A308" s="131">
+      <c r="A308" s="143">
         <v>67</v>
       </c>
       <c r="B308" s="43" t="s">
@@ -12939,7 +13050,7 @@
       <c r="N308" s="13"/>
     </row>
     <row r="309" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A309" s="132"/>
+      <c r="A309" s="138"/>
       <c r="B309" s="43" t="s">
         <v>180</v>
       </c>
@@ -12971,7 +13082,7 @@
       <c r="N309" s="13"/>
     </row>
     <row r="310" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A310" s="132"/>
+      <c r="A310" s="138"/>
       <c r="B310" s="43" t="s">
         <v>180</v>
       </c>
@@ -13003,7 +13114,7 @@
       <c r="N310" s="13"/>
     </row>
     <row r="311" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A311" s="125"/>
+      <c r="A311" s="139"/>
       <c r="B311" s="43" t="s">
         <v>180</v>
       </c>
@@ -13051,7 +13162,7 @@
       <c r="N312" s="13"/>
     </row>
     <row r="313" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A313" s="131">
+      <c r="A313" s="143">
         <v>68</v>
       </c>
       <c r="B313" s="49" t="s">
@@ -13085,7 +13196,7 @@
       <c r="N313" s="13"/>
     </row>
     <row r="314" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A314" s="132"/>
+      <c r="A314" s="138"/>
       <c r="B314" s="49" t="s">
         <v>183</v>
       </c>
@@ -13117,7 +13228,7 @@
       <c r="N314" s="13"/>
     </row>
     <row r="315" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A315" s="132"/>
+      <c r="A315" s="138"/>
       <c r="B315" s="49" t="s">
         <v>183</v>
       </c>
@@ -13149,7 +13260,7 @@
       <c r="N315" s="13"/>
     </row>
     <row r="316" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A316" s="125"/>
+      <c r="A316" s="139"/>
       <c r="B316" s="49" t="s">
         <v>183</v>
       </c>
@@ -13197,7 +13308,7 @@
       <c r="N317" s="13"/>
     </row>
     <row r="318" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A318" s="131">
+      <c r="A318" s="143">
         <v>69</v>
       </c>
       <c r="B318" s="49" t="s">
@@ -13231,7 +13342,7 @@
       <c r="N318" s="13"/>
     </row>
     <row r="319" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A319" s="132"/>
+      <c r="A319" s="138"/>
       <c r="B319" s="49" t="s">
         <v>186</v>
       </c>
@@ -13263,7 +13374,7 @@
       <c r="N319" s="13"/>
     </row>
     <row r="320" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A320" s="132"/>
+      <c r="A320" s="138"/>
       <c r="B320" s="49" t="s">
         <v>186</v>
       </c>
@@ -13295,7 +13406,7 @@
       <c r="N320" s="13"/>
     </row>
     <row r="321" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A321" s="125"/>
+      <c r="A321" s="139"/>
       <c r="B321" s="49" t="s">
         <v>186</v>
       </c>
@@ -13343,7 +13454,7 @@
       <c r="N322" s="13"/>
     </row>
     <row r="323" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A323" s="131">
+      <c r="A323" s="143">
         <v>70</v>
       </c>
       <c r="B323" s="49" t="s">
@@ -13377,7 +13488,7 @@
       <c r="N323" s="13"/>
     </row>
     <row r="324" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A324" s="132"/>
+      <c r="A324" s="138"/>
       <c r="B324" s="49" t="s">
         <v>188</v>
       </c>
@@ -13409,7 +13520,7 @@
       <c r="N324" s="13"/>
     </row>
     <row r="325" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A325" s="132"/>
+      <c r="A325" s="138"/>
       <c r="B325" s="49" t="s">
         <v>188</v>
       </c>
@@ -13441,7 +13552,7 @@
       <c r="N325" s="13"/>
     </row>
     <row r="326" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A326" s="125"/>
+      <c r="A326" s="139"/>
       <c r="B326" s="49" t="s">
         <v>188</v>
       </c>
@@ -13489,7 +13600,7 @@
       <c r="N327" s="13"/>
     </row>
     <row r="328" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A328" s="131">
+      <c r="A328" s="143">
         <v>71</v>
       </c>
       <c r="B328" s="49" t="s">
@@ -13523,7 +13634,7 @@
       <c r="N328" s="13"/>
     </row>
     <row r="329" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A329" s="132"/>
+      <c r="A329" s="138"/>
       <c r="B329" s="49" t="s">
         <v>190</v>
       </c>
@@ -13555,7 +13666,7 @@
       <c r="N329" s="13"/>
     </row>
     <row r="330" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A330" s="132"/>
+      <c r="A330" s="138"/>
       <c r="B330" s="49" t="s">
         <v>190</v>
       </c>
@@ -13587,7 +13698,7 @@
       <c r="N330" s="13"/>
     </row>
     <row r="331" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A331" s="125"/>
+      <c r="A331" s="139"/>
       <c r="B331" s="49" t="s">
         <v>190</v>
       </c>
@@ -13635,7 +13746,7 @@
       <c r="N332" s="13"/>
     </row>
     <row r="333" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A333" s="131">
+      <c r="A333" s="143">
         <v>72</v>
       </c>
       <c r="B333" s="49" t="s">
@@ -13669,7 +13780,7 @@
       <c r="N333" s="13"/>
     </row>
     <row r="334" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A334" s="132"/>
+      <c r="A334" s="138"/>
       <c r="B334" s="49" t="s">
         <v>193</v>
       </c>
@@ -13701,7 +13812,7 @@
       <c r="N334" s="13"/>
     </row>
     <row r="335" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A335" s="132"/>
+      <c r="A335" s="138"/>
       <c r="B335" s="49" t="s">
         <v>193</v>
       </c>
@@ -13733,7 +13844,7 @@
       <c r="N335" s="13"/>
     </row>
     <row r="336" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A336" s="125"/>
+      <c r="A336" s="139"/>
       <c r="B336" s="49" t="s">
         <v>193</v>
       </c>
@@ -13781,7 +13892,7 @@
       <c r="N337" s="13"/>
     </row>
     <row r="338" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A338" s="131">
+      <c r="A338" s="143">
         <v>73</v>
       </c>
       <c r="B338" s="49" t="s">
@@ -13815,7 +13926,7 @@
       <c r="N338" s="13"/>
     </row>
     <row r="339" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A339" s="132"/>
+      <c r="A339" s="138"/>
       <c r="B339" s="49" t="s">
         <v>196</v>
       </c>
@@ -13847,7 +13958,7 @@
       <c r="N339" s="13"/>
     </row>
     <row r="340" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A340" s="132"/>
+      <c r="A340" s="138"/>
       <c r="B340" s="49" t="s">
         <v>196</v>
       </c>
@@ -13879,7 +13990,7 @@
       <c r="N340" s="13"/>
     </row>
     <row r="341" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A341" s="125"/>
+      <c r="A341" s="139"/>
       <c r="B341" s="49" t="s">
         <v>196</v>
       </c>
@@ -13927,7 +14038,7 @@
       <c r="N342" s="13"/>
     </row>
     <row r="343" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A343" s="131">
+      <c r="A343" s="143">
         <v>74</v>
       </c>
       <c r="B343" s="49" t="s">
@@ -13961,7 +14072,7 @@
       <c r="N343" s="13"/>
     </row>
     <row r="344" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A344" s="132"/>
+      <c r="A344" s="138"/>
       <c r="B344" s="49" t="s">
         <v>198</v>
       </c>
@@ -13993,7 +14104,7 @@
       <c r="N344" s="13"/>
     </row>
     <row r="345" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A345" s="132"/>
+      <c r="A345" s="138"/>
       <c r="B345" s="49" t="s">
         <v>198</v>
       </c>
@@ -14025,7 +14136,7 @@
       <c r="N345" s="13"/>
     </row>
     <row r="346" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A346" s="125"/>
+      <c r="A346" s="139"/>
       <c r="B346" s="49" t="s">
         <v>198</v>
       </c>
@@ -14073,7 +14184,7 @@
       <c r="N347" s="13"/>
     </row>
     <row r="348" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A348" s="131">
+      <c r="A348" s="143">
         <v>75</v>
       </c>
       <c r="B348" s="49" t="s">
@@ -14107,7 +14218,7 @@
       <c r="N348" s="13"/>
     </row>
     <row r="349" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A349" s="132"/>
+      <c r="A349" s="138"/>
       <c r="B349" s="49" t="s">
         <v>201</v>
       </c>
@@ -14139,7 +14250,7 @@
       <c r="N349" s="13"/>
     </row>
     <row r="350" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A350" s="132"/>
+      <c r="A350" s="138"/>
       <c r="B350" s="49" t="s">
         <v>201</v>
       </c>
@@ -14171,7 +14282,7 @@
       <c r="N350" s="13"/>
     </row>
     <row r="351" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A351" s="125"/>
+      <c r="A351" s="139"/>
       <c r="B351" s="49" t="s">
         <v>201</v>
       </c>
@@ -14219,7 +14330,7 @@
       <c r="N352" s="13"/>
     </row>
     <row r="353" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A353" s="131">
+      <c r="A353" s="143">
         <v>76</v>
       </c>
       <c r="B353" s="49" t="s">
@@ -14253,7 +14364,7 @@
       <c r="N353" s="13"/>
     </row>
     <row r="354" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A354" s="132"/>
+      <c r="A354" s="138"/>
       <c r="B354" s="49" t="s">
         <v>202</v>
       </c>
@@ -14285,7 +14396,7 @@
       <c r="N354" s="13"/>
     </row>
     <row r="355" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A355" s="132"/>
+      <c r="A355" s="138"/>
       <c r="B355" s="49" t="s">
         <v>202</v>
       </c>
@@ -14317,7 +14428,7 @@
       <c r="N355" s="13"/>
     </row>
     <row r="356" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A356" s="125"/>
+      <c r="A356" s="139"/>
       <c r="B356" s="49" t="s">
         <v>202</v>
       </c>
@@ -14365,7 +14476,7 @@
       <c r="N357" s="13"/>
     </row>
     <row r="358" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A358" s="133">
+      <c r="A358" s="137">
         <v>77</v>
       </c>
       <c r="B358" s="54" t="s">
@@ -14411,7 +14522,7 @@
       <c r="Z358" s="58"/>
     </row>
     <row r="359" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A359" s="132"/>
+      <c r="A359" s="138"/>
       <c r="B359" s="54" t="s">
         <v>203</v>
       </c>
@@ -14455,7 +14566,7 @@
       <c r="Z359" s="58"/>
     </row>
     <row r="360" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A360" s="132"/>
+      <c r="A360" s="138"/>
       <c r="B360" s="54" t="s">
         <v>203</v>
       </c>
@@ -14499,7 +14610,7 @@
       <c r="Z360" s="58"/>
     </row>
     <row r="361" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A361" s="125"/>
+      <c r="A361" s="139"/>
       <c r="B361" s="54" t="s">
         <v>203</v>
       </c>
@@ -14571,7 +14682,7 @@
       <c r="Z362" s="58"/>
     </row>
     <row r="363" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A363" s="133">
+      <c r="A363" s="137">
         <v>78</v>
       </c>
       <c r="B363" s="54" t="s">
@@ -14617,7 +14728,7 @@
       <c r="Z363" s="58"/>
     </row>
     <row r="364" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A364" s="132"/>
+      <c r="A364" s="138"/>
       <c r="B364" s="54" t="s">
         <v>205</v>
       </c>
@@ -14661,7 +14772,7 @@
       <c r="Z364" s="58"/>
     </row>
     <row r="365" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A365" s="132"/>
+      <c r="A365" s="138"/>
       <c r="B365" s="54" t="s">
         <v>205</v>
       </c>
@@ -14705,7 +14816,7 @@
       <c r="Z365" s="58"/>
     </row>
     <row r="366" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A366" s="125"/>
+      <c r="A366" s="139"/>
       <c r="B366" s="54" t="s">
         <v>205</v>
       </c>
@@ -14777,7 +14888,7 @@
       <c r="Z367" s="58"/>
     </row>
     <row r="368" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A368" s="133">
+      <c r="A368" s="137">
         <v>79</v>
       </c>
       <c r="B368" s="54" t="s">
@@ -14823,7 +14934,7 @@
       <c r="Z368" s="58"/>
     </row>
     <row r="369" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A369" s="132"/>
+      <c r="A369" s="138"/>
       <c r="B369" s="54" t="s">
         <v>206</v>
       </c>
@@ -14867,7 +14978,7 @@
       <c r="Z369" s="58"/>
     </row>
     <row r="370" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A370" s="132"/>
+      <c r="A370" s="138"/>
       <c r="B370" s="54" t="s">
         <v>206</v>
       </c>
@@ -14911,7 +15022,7 @@
       <c r="Z370" s="58"/>
     </row>
     <row r="371" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A371" s="125"/>
+      <c r="A371" s="139"/>
       <c r="B371" s="54" t="s">
         <v>206</v>
       </c>
@@ -14971,7 +15082,7 @@
       <c r="N372" s="13"/>
     </row>
     <row r="373" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A373" s="131">
+      <c r="A373" s="143">
         <v>80</v>
       </c>
       <c r="B373" s="49" t="s">
@@ -15005,7 +15116,7 @@
       <c r="N373" s="13"/>
     </row>
     <row r="374" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A374" s="132"/>
+      <c r="A374" s="138"/>
       <c r="B374" s="49" t="s">
         <v>207</v>
       </c>
@@ -15037,7 +15148,7 @@
       <c r="N374" s="13"/>
     </row>
     <row r="375" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A375" s="132"/>
+      <c r="A375" s="138"/>
       <c r="B375" s="49" t="s">
         <v>207</v>
       </c>
@@ -15069,7 +15180,7 @@
       <c r="N375" s="13"/>
     </row>
     <row r="376" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A376" s="125"/>
+      <c r="A376" s="139"/>
       <c r="B376" s="49" t="s">
         <v>207</v>
       </c>
@@ -15117,7 +15228,7 @@
       <c r="N377" s="13"/>
     </row>
     <row r="378" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A378" s="131">
+      <c r="A378" s="143">
         <v>81</v>
       </c>
       <c r="B378" s="49" t="s">
@@ -15151,7 +15262,7 @@
       <c r="N378" s="13"/>
     </row>
     <row r="379" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A379" s="132"/>
+      <c r="A379" s="138"/>
       <c r="B379" s="49" t="s">
         <v>210</v>
       </c>
@@ -15183,7 +15294,7 @@
       <c r="N379" s="13"/>
     </row>
     <row r="380" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A380" s="132"/>
+      <c r="A380" s="138"/>
       <c r="B380" s="49" t="s">
         <v>210</v>
       </c>
@@ -15215,7 +15326,7 @@
       <c r="N380" s="13"/>
     </row>
     <row r="381" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A381" s="125"/>
+      <c r="A381" s="139"/>
       <c r="B381" s="49" t="s">
         <v>210</v>
       </c>
@@ -15263,7 +15374,7 @@
       <c r="N382" s="13"/>
     </row>
     <row r="383" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A383" s="131">
+      <c r="A383" s="143">
         <v>82</v>
       </c>
       <c r="B383" s="43" t="s">
@@ -15297,7 +15408,7 @@
       <c r="N383" s="13"/>
     </row>
     <row r="384" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A384" s="132"/>
+      <c r="A384" s="138"/>
       <c r="B384" s="43" t="s">
         <v>212</v>
       </c>
@@ -15329,7 +15440,7 @@
       <c r="N384" s="13"/>
     </row>
     <row r="385" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A385" s="132"/>
+      <c r="A385" s="138"/>
       <c r="B385" s="43" t="s">
         <v>212</v>
       </c>
@@ -15361,7 +15472,7 @@
       <c r="N385" s="13"/>
     </row>
     <row r="386" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A386" s="125"/>
+      <c r="A386" s="139"/>
       <c r="B386" s="43" t="s">
         <v>212</v>
       </c>
@@ -15409,7 +15520,7 @@
       <c r="N387" s="13"/>
     </row>
     <row r="388" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A388" s="131">
+      <c r="A388" s="143">
         <v>83</v>
       </c>
       <c r="B388" s="49" t="s">
@@ -15443,7 +15554,7 @@
       <c r="N388" s="13"/>
     </row>
     <row r="389" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A389" s="132"/>
+      <c r="A389" s="138"/>
       <c r="B389" s="49" t="s">
         <v>214</v>
       </c>
@@ -15475,7 +15586,7 @@
       <c r="N389" s="13"/>
     </row>
     <row r="390" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A390" s="132"/>
+      <c r="A390" s="138"/>
       <c r="B390" s="49" t="s">
         <v>214</v>
       </c>
@@ -15507,7 +15618,7 @@
       <c r="N390" s="13"/>
     </row>
     <row r="391" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A391" s="125"/>
+      <c r="A391" s="139"/>
       <c r="B391" s="49" t="s">
         <v>214</v>
       </c>
@@ -15555,7 +15666,7 @@
       <c r="N392" s="13"/>
     </row>
     <row r="393" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A393" s="131">
+      <c r="A393" s="143">
         <v>84</v>
       </c>
       <c r="B393" s="49" t="s">
@@ -15589,7 +15700,7 @@
       <c r="N393" s="13"/>
     </row>
     <row r="394" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A394" s="132"/>
+      <c r="A394" s="138"/>
       <c r="B394" s="49" t="s">
         <v>216</v>
       </c>
@@ -15621,7 +15732,7 @@
       <c r="N394" s="13"/>
     </row>
     <row r="395" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A395" s="132"/>
+      <c r="A395" s="138"/>
       <c r="B395" s="49" t="s">
         <v>216</v>
       </c>
@@ -15653,7 +15764,7 @@
       <c r="N395" s="13"/>
     </row>
     <row r="396" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A396" s="125"/>
+      <c r="A396" s="139"/>
       <c r="B396" s="49" t="s">
         <v>216</v>
       </c>
@@ -15701,7 +15812,7 @@
       <c r="N397" s="13"/>
     </row>
     <row r="398" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A398" s="131">
+      <c r="A398" s="143">
         <v>85</v>
       </c>
       <c r="B398" s="49" t="s">
@@ -15735,7 +15846,7 @@
       <c r="N398" s="13"/>
     </row>
     <row r="399" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A399" s="132"/>
+      <c r="A399" s="138"/>
       <c r="B399" s="49" t="s">
         <v>218</v>
       </c>
@@ -15767,7 +15878,7 @@
       <c r="N399" s="13"/>
     </row>
     <row r="400" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A400" s="132"/>
+      <c r="A400" s="138"/>
       <c r="B400" s="49" t="s">
         <v>218</v>
       </c>
@@ -15799,7 +15910,7 @@
       <c r="N400" s="13"/>
     </row>
     <row r="401" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A401" s="125"/>
+      <c r="A401" s="139"/>
       <c r="B401" s="49" t="s">
         <v>218</v>
       </c>
@@ -15847,7 +15958,7 @@
       <c r="N402" s="13"/>
     </row>
     <row r="403" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A403" s="131">
+      <c r="A403" s="143">
         <v>86</v>
       </c>
       <c r="B403" s="49" t="s">
@@ -15881,7 +15992,7 @@
       <c r="N403" s="13"/>
     </row>
     <row r="404" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A404" s="132"/>
+      <c r="A404" s="138"/>
       <c r="B404" s="49" t="s">
         <v>220</v>
       </c>
@@ -15913,7 +16024,7 @@
       <c r="N404" s="13"/>
     </row>
     <row r="405" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A405" s="132"/>
+      <c r="A405" s="138"/>
       <c r="B405" s="49" t="s">
         <v>220</v>
       </c>
@@ -15945,7 +16056,7 @@
       <c r="N405" s="13"/>
     </row>
     <row r="406" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A406" s="125"/>
+      <c r="A406" s="139"/>
       <c r="B406" s="49" t="s">
         <v>220</v>
       </c>
@@ -15993,7 +16104,7 @@
       <c r="N407" s="13"/>
     </row>
     <row r="408" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A408" s="131">
+      <c r="A408" s="143">
         <v>87</v>
       </c>
       <c r="B408" s="49" t="s">
@@ -16027,7 +16138,7 @@
       <c r="N408" s="13"/>
     </row>
     <row r="409" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A409" s="132"/>
+      <c r="A409" s="138"/>
       <c r="B409" s="49" t="s">
         <v>222</v>
       </c>
@@ -16059,7 +16170,7 @@
       <c r="N409" s="13"/>
     </row>
     <row r="410" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A410" s="132"/>
+      <c r="A410" s="138"/>
       <c r="B410" s="49" t="s">
         <v>222</v>
       </c>
@@ -16091,7 +16202,7 @@
       <c r="N410" s="13"/>
     </row>
     <row r="411" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A411" s="125"/>
+      <c r="A411" s="139"/>
       <c r="B411" s="49" t="s">
         <v>222</v>
       </c>
@@ -16139,7 +16250,7 @@
       <c r="N412" s="13"/>
     </row>
     <row r="413" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A413" s="131">
+      <c r="A413" s="143">
         <v>88</v>
       </c>
       <c r="B413" s="49" t="s">
@@ -16173,7 +16284,7 @@
       <c r="N413" s="13"/>
     </row>
     <row r="414" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A414" s="132"/>
+      <c r="A414" s="138"/>
       <c r="B414" s="49" t="s">
         <v>224</v>
       </c>
@@ -16205,7 +16316,7 @@
       <c r="N414" s="13"/>
     </row>
     <row r="415" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A415" s="132"/>
+      <c r="A415" s="138"/>
       <c r="B415" s="49" t="s">
         <v>224</v>
       </c>
@@ -16237,7 +16348,7 @@
       <c r="N415" s="13"/>
     </row>
     <row r="416" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A416" s="125"/>
+      <c r="A416" s="139"/>
       <c r="B416" s="49" t="s">
         <v>224</v>
       </c>
@@ -16285,19 +16396,19 @@
       <c r="N417" s="13"/>
     </row>
     <row r="418" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A418" s="131">
+      <c r="A418" s="143">
         <v>89</v>
       </c>
       <c r="B418" s="49" t="s">
         <v>226</v>
       </c>
-      <c r="C418" s="145" t="s">
+      <c r="C418" s="124" t="s">
         <v>13</v>
       </c>
-      <c r="D418" s="146" t="s">
+      <c r="D418" s="125" t="s">
         <v>227</v>
       </c>
-      <c r="E418" s="147" t="s">
+      <c r="E418" s="126" t="s">
         <v>228</v>
       </c>
       <c r="F418" s="13" t="s">
@@ -16319,17 +16430,17 @@
       <c r="N418" s="13"/>
     </row>
     <row r="419" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A419" s="132"/>
+      <c r="A419" s="138"/>
       <c r="B419" s="49" t="s">
         <v>226</v>
       </c>
-      <c r="C419" s="145" t="s">
+      <c r="C419" s="124" t="s">
         <v>19</v>
       </c>
-      <c r="D419" s="146" t="s">
+      <c r="D419" s="125" t="s">
         <v>227</v>
       </c>
-      <c r="E419" s="147" t="s">
+      <c r="E419" s="126" t="s">
         <v>228</v>
       </c>
       <c r="F419" s="13" t="s">
@@ -16351,17 +16462,17 @@
       <c r="N419" s="13"/>
     </row>
     <row r="420" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A420" s="132"/>
+      <c r="A420" s="138"/>
       <c r="B420" s="49" t="s">
         <v>226</v>
       </c>
-      <c r="C420" s="145" t="s">
+      <c r="C420" s="124" t="s">
         <v>21</v>
       </c>
-      <c r="D420" s="146" t="s">
+      <c r="D420" s="125" t="s">
         <v>227</v>
       </c>
-      <c r="E420" s="147" t="s">
+      <c r="E420" s="126" t="s">
         <v>228</v>
       </c>
       <c r="F420" s="13" t="s">
@@ -16383,17 +16494,17 @@
       <c r="N420" s="13"/>
     </row>
     <row r="421" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A421" s="125"/>
+      <c r="A421" s="139"/>
       <c r="B421" s="49" t="s">
         <v>226</v>
       </c>
-      <c r="C421" s="145" t="s">
+      <c r="C421" s="124" t="s">
         <v>23</v>
       </c>
-      <c r="D421" s="146" t="s">
+      <c r="D421" s="125" t="s">
         <v>227</v>
       </c>
-      <c r="E421" s="147" t="s">
+      <c r="E421" s="126" t="s">
         <v>228</v>
       </c>
       <c r="F421" s="13" t="s">
@@ -16417,9 +16528,9 @@
     <row r="422" spans="1:14" ht="18.75" customHeight="1">
       <c r="A422" s="15"/>
       <c r="B422" s="49"/>
-      <c r="C422" s="146"/>
-      <c r="D422" s="146"/>
-      <c r="E422" s="147"/>
+      <c r="C422" s="125"/>
+      <c r="D422" s="125"/>
+      <c r="E422" s="126"/>
       <c r="F422" s="13"/>
       <c r="G422" s="51"/>
       <c r="H422" s="52"/>
@@ -16431,19 +16542,19 @@
       <c r="N422" s="13"/>
     </row>
     <row r="423" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A423" s="131">
+      <c r="A423" s="143">
         <v>90</v>
       </c>
       <c r="B423" s="49" t="s">
         <v>229</v>
       </c>
-      <c r="C423" s="145" t="s">
+      <c r="C423" s="124" t="s">
         <v>13</v>
       </c>
-      <c r="D423" s="146" t="s">
+      <c r="D423" s="125" t="s">
         <v>230</v>
       </c>
-      <c r="E423" s="147" t="s">
+      <c r="E423" s="126" t="s">
         <v>231</v>
       </c>
       <c r="F423" s="13" t="s">
@@ -16465,17 +16576,17 @@
       <c r="N423" s="13"/>
     </row>
     <row r="424" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A424" s="132"/>
+      <c r="A424" s="138"/>
       <c r="B424" s="49" t="s">
         <v>229</v>
       </c>
-      <c r="C424" s="145" t="s">
+      <c r="C424" s="124" t="s">
         <v>19</v>
       </c>
-      <c r="D424" s="146" t="s">
+      <c r="D424" s="125" t="s">
         <v>230</v>
       </c>
-      <c r="E424" s="147" t="s">
+      <c r="E424" s="126" t="s">
         <v>231</v>
       </c>
       <c r="F424" s="13" t="s">
@@ -16497,17 +16608,17 @@
       <c r="N424" s="13"/>
     </row>
     <row r="425" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A425" s="132"/>
+      <c r="A425" s="138"/>
       <c r="B425" s="49" t="s">
         <v>229</v>
       </c>
-      <c r="C425" s="145" t="s">
+      <c r="C425" s="124" t="s">
         <v>21</v>
       </c>
-      <c r="D425" s="146" t="s">
+      <c r="D425" s="125" t="s">
         <v>230</v>
       </c>
-      <c r="E425" s="147" t="s">
+      <c r="E425" s="126" t="s">
         <v>231</v>
       </c>
       <c r="F425" s="13" t="s">
@@ -16529,17 +16640,17 @@
       <c r="N425" s="13"/>
     </row>
     <row r="426" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A426" s="125"/>
+      <c r="A426" s="139"/>
       <c r="B426" s="49" t="s">
         <v>229</v>
       </c>
-      <c r="C426" s="145" t="s">
+      <c r="C426" s="124" t="s">
         <v>23</v>
       </c>
-      <c r="D426" s="146" t="s">
+      <c r="D426" s="125" t="s">
         <v>230</v>
       </c>
-      <c r="E426" s="147" t="s">
+      <c r="E426" s="126" t="s">
         <v>231</v>
       </c>
       <c r="F426" s="13" t="s">
@@ -16563,9 +16674,9 @@
     <row r="427" spans="1:14" ht="18.75" customHeight="1">
       <c r="A427" s="15"/>
       <c r="B427" s="49"/>
-      <c r="C427" s="146"/>
-      <c r="D427" s="146"/>
-      <c r="E427" s="147"/>
+      <c r="C427" s="125"/>
+      <c r="D427" s="125"/>
+      <c r="E427" s="126"/>
       <c r="F427" s="13"/>
       <c r="G427" s="51"/>
       <c r="H427" s="52"/>
@@ -16577,19 +16688,19 @@
       <c r="N427" s="13"/>
     </row>
     <row r="428" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A428" s="131">
+      <c r="A428" s="143">
         <v>91</v>
       </c>
       <c r="B428" s="49" t="s">
         <v>232</v>
       </c>
-      <c r="C428" s="145" t="s">
+      <c r="C428" s="124" t="s">
         <v>13</v>
       </c>
-      <c r="D428" s="146" t="s">
+      <c r="D428" s="125" t="s">
         <v>233</v>
       </c>
-      <c r="E428" s="147" t="s">
+      <c r="E428" s="126" t="s">
         <v>228</v>
       </c>
       <c r="F428" s="13" t="s">
@@ -16611,17 +16722,17 @@
       <c r="N428" s="13"/>
     </row>
     <row r="429" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A429" s="132"/>
+      <c r="A429" s="138"/>
       <c r="B429" s="49" t="s">
         <v>232</v>
       </c>
-      <c r="C429" s="145" t="s">
+      <c r="C429" s="124" t="s">
         <v>19</v>
       </c>
-      <c r="D429" s="146" t="s">
+      <c r="D429" s="125" t="s">
         <v>233</v>
       </c>
-      <c r="E429" s="147" t="s">
+      <c r="E429" s="126" t="s">
         <v>228</v>
       </c>
       <c r="F429" s="13" t="s">
@@ -16643,17 +16754,17 @@
       <c r="N429" s="13"/>
     </row>
     <row r="430" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A430" s="132"/>
+      <c r="A430" s="138"/>
       <c r="B430" s="49" t="s">
         <v>232</v>
       </c>
-      <c r="C430" s="145" t="s">
+      <c r="C430" s="124" t="s">
         <v>21</v>
       </c>
-      <c r="D430" s="146" t="s">
+      <c r="D430" s="125" t="s">
         <v>233</v>
       </c>
-      <c r="E430" s="147" t="s">
+      <c r="E430" s="126" t="s">
         <v>228</v>
       </c>
       <c r="F430" s="13" t="s">
@@ -16675,17 +16786,17 @@
       <c r="N430" s="13"/>
     </row>
     <row r="431" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A431" s="125"/>
+      <c r="A431" s="139"/>
       <c r="B431" s="49" t="s">
         <v>232</v>
       </c>
-      <c r="C431" s="145" t="s">
+      <c r="C431" s="124" t="s">
         <v>23</v>
       </c>
-      <c r="D431" s="146" t="s">
+      <c r="D431" s="125" t="s">
         <v>233</v>
       </c>
-      <c r="E431" s="147" t="s">
+      <c r="E431" s="126" t="s">
         <v>228</v>
       </c>
       <c r="F431" s="13" t="s">
@@ -16723,19 +16834,19 @@
       <c r="N432" s="13"/>
     </row>
     <row r="433" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A433" s="131">
+      <c r="A433" s="143">
         <v>92</v>
       </c>
       <c r="B433" s="49" t="s">
         <v>234</v>
       </c>
-      <c r="C433" s="145" t="s">
+      <c r="C433" s="124" t="s">
         <v>13</v>
       </c>
-      <c r="D433" s="146" t="s">
+      <c r="D433" s="125" t="s">
         <v>235</v>
       </c>
-      <c r="E433" s="147" t="s">
+      <c r="E433" s="126" t="s">
         <v>228</v>
       </c>
       <c r="F433" s="13" t="s">
@@ -16757,17 +16868,17 @@
       <c r="N433" s="13"/>
     </row>
     <row r="434" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A434" s="132"/>
+      <c r="A434" s="138"/>
       <c r="B434" s="49" t="s">
         <v>234</v>
       </c>
-      <c r="C434" s="145" t="s">
+      <c r="C434" s="124" t="s">
         <v>19</v>
       </c>
-      <c r="D434" s="146" t="s">
+      <c r="D434" s="125" t="s">
         <v>235</v>
       </c>
-      <c r="E434" s="147" t="s">
+      <c r="E434" s="126" t="s">
         <v>228</v>
       </c>
       <c r="F434" s="13" t="s">
@@ -16789,17 +16900,17 @@
       <c r="N434" s="13"/>
     </row>
     <row r="435" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A435" s="132"/>
+      <c r="A435" s="138"/>
       <c r="B435" s="49" t="s">
         <v>234</v>
       </c>
-      <c r="C435" s="145" t="s">
+      <c r="C435" s="124" t="s">
         <v>21</v>
       </c>
-      <c r="D435" s="146" t="s">
+      <c r="D435" s="125" t="s">
         <v>235</v>
       </c>
-      <c r="E435" s="147" t="s">
+      <c r="E435" s="126" t="s">
         <v>228</v>
       </c>
       <c r="F435" s="13" t="s">
@@ -16821,17 +16932,17 @@
       <c r="N435" s="13"/>
     </row>
     <row r="436" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A436" s="125"/>
+      <c r="A436" s="139"/>
       <c r="B436" s="49" t="s">
         <v>234</v>
       </c>
-      <c r="C436" s="145" t="s">
+      <c r="C436" s="124" t="s">
         <v>23</v>
       </c>
-      <c r="D436" s="146" t="s">
+      <c r="D436" s="125" t="s">
         <v>235</v>
       </c>
-      <c r="E436" s="147" t="s">
+      <c r="E436" s="126" t="s">
         <v>228</v>
       </c>
       <c r="F436" s="13" t="s">
@@ -16855,9 +16966,9 @@
     <row r="437" spans="1:14" ht="18.75" customHeight="1">
       <c r="A437" s="15"/>
       <c r="B437" s="49"/>
-      <c r="C437" s="146"/>
-      <c r="D437" s="146"/>
-      <c r="E437" s="147"/>
+      <c r="C437" s="125"/>
+      <c r="D437" s="125"/>
+      <c r="E437" s="126"/>
       <c r="F437" s="13"/>
       <c r="G437" s="51"/>
       <c r="H437" s="52"/>
@@ -16869,19 +16980,19 @@
       <c r="N437" s="13"/>
     </row>
     <row r="438" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A438" s="131">
+      <c r="A438" s="143">
         <v>93</v>
       </c>
       <c r="B438" s="49" t="s">
         <v>236</v>
       </c>
-      <c r="C438" s="145" t="s">
+      <c r="C438" s="124" t="s">
         <v>13</v>
       </c>
-      <c r="D438" s="146" t="s">
+      <c r="D438" s="125" t="s">
         <v>237</v>
       </c>
-      <c r="E438" s="147" t="s">
+      <c r="E438" s="126" t="s">
         <v>228</v>
       </c>
       <c r="F438" s="13" t="s">
@@ -16903,17 +17014,17 @@
       <c r="N438" s="13"/>
     </row>
     <row r="439" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A439" s="132"/>
+      <c r="A439" s="138"/>
       <c r="B439" s="49" t="s">
         <v>236</v>
       </c>
-      <c r="C439" s="145" t="s">
+      <c r="C439" s="124" t="s">
         <v>19</v>
       </c>
-      <c r="D439" s="146" t="s">
+      <c r="D439" s="125" t="s">
         <v>237</v>
       </c>
-      <c r="E439" s="147" t="s">
+      <c r="E439" s="126" t="s">
         <v>228</v>
       </c>
       <c r="F439" s="13" t="s">
@@ -16935,17 +17046,17 @@
       <c r="N439" s="13"/>
     </row>
     <row r="440" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A440" s="132"/>
+      <c r="A440" s="138"/>
       <c r="B440" s="49" t="s">
         <v>236</v>
       </c>
-      <c r="C440" s="145" t="s">
+      <c r="C440" s="124" t="s">
         <v>21</v>
       </c>
-      <c r="D440" s="146" t="s">
+      <c r="D440" s="125" t="s">
         <v>237</v>
       </c>
-      <c r="E440" s="147" t="s">
+      <c r="E440" s="126" t="s">
         <v>228</v>
       </c>
       <c r="F440" s="13" t="s">
@@ -16967,17 +17078,17 @@
       <c r="N440" s="13"/>
     </row>
     <row r="441" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A441" s="125"/>
+      <c r="A441" s="139"/>
       <c r="B441" s="49" t="s">
         <v>236</v>
       </c>
-      <c r="C441" s="145" t="s">
+      <c r="C441" s="124" t="s">
         <v>23</v>
       </c>
-      <c r="D441" s="146" t="s">
+      <c r="D441" s="125" t="s">
         <v>237</v>
       </c>
-      <c r="E441" s="147" t="s">
+      <c r="E441" s="126" t="s">
         <v>228</v>
       </c>
       <c r="F441" s="13" t="s">
@@ -17001,9 +17112,9 @@
     <row r="442" spans="1:14" ht="18.75" customHeight="1">
       <c r="A442" s="15"/>
       <c r="B442" s="49"/>
-      <c r="C442" s="146"/>
-      <c r="D442" s="146"/>
-      <c r="E442" s="147"/>
+      <c r="C442" s="125"/>
+      <c r="D442" s="125"/>
+      <c r="E442" s="126"/>
       <c r="F442" s="13"/>
       <c r="G442" s="51"/>
       <c r="H442" s="52"/>
@@ -17015,19 +17126,19 @@
       <c r="N442" s="13"/>
     </row>
     <row r="443" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A443" s="131">
+      <c r="A443" s="143">
         <v>94</v>
       </c>
       <c r="B443" s="49" t="s">
         <v>238</v>
       </c>
-      <c r="C443" s="145" t="s">
+      <c r="C443" s="124" t="s">
         <v>13</v>
       </c>
-      <c r="D443" s="146" t="s">
+      <c r="D443" s="125" t="s">
         <v>239</v>
       </c>
-      <c r="E443" s="147" t="s">
+      <c r="E443" s="126" t="s">
         <v>228</v>
       </c>
       <c r="F443" s="13" t="s">
@@ -17049,17 +17160,17 @@
       <c r="N443" s="13"/>
     </row>
     <row r="444" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A444" s="132"/>
+      <c r="A444" s="138"/>
       <c r="B444" s="49" t="s">
         <v>238</v>
       </c>
-      <c r="C444" s="145" t="s">
+      <c r="C444" s="124" t="s">
         <v>19</v>
       </c>
-      <c r="D444" s="146" t="s">
+      <c r="D444" s="125" t="s">
         <v>239</v>
       </c>
-      <c r="E444" s="147" t="s">
+      <c r="E444" s="126" t="s">
         <v>228</v>
       </c>
       <c r="F444" s="13" t="s">
@@ -17081,17 +17192,17 @@
       <c r="N444" s="13"/>
     </row>
     <row r="445" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A445" s="132"/>
+      <c r="A445" s="138"/>
       <c r="B445" s="49" t="s">
         <v>238</v>
       </c>
-      <c r="C445" s="145" t="s">
+      <c r="C445" s="124" t="s">
         <v>21</v>
       </c>
-      <c r="D445" s="146" t="s">
+      <c r="D445" s="125" t="s">
         <v>239</v>
       </c>
-      <c r="E445" s="147" t="s">
+      <c r="E445" s="126" t="s">
         <v>228</v>
       </c>
       <c r="F445" s="13" t="s">
@@ -17113,17 +17224,17 @@
       <c r="N445" s="13"/>
     </row>
     <row r="446" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A446" s="125"/>
+      <c r="A446" s="139"/>
       <c r="B446" s="49" t="s">
         <v>238</v>
       </c>
-      <c r="C446" s="145" t="s">
+      <c r="C446" s="124" t="s">
         <v>23</v>
       </c>
-      <c r="D446" s="146" t="s">
+      <c r="D446" s="125" t="s">
         <v>239</v>
       </c>
-      <c r="E446" s="147" t="s">
+      <c r="E446" s="126" t="s">
         <v>228</v>
       </c>
       <c r="F446" s="13" t="s">
@@ -17161,7 +17272,7 @@
       <c r="N447" s="13"/>
     </row>
     <row r="448" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A448" s="131">
+      <c r="A448" s="143">
         <v>95</v>
       </c>
       <c r="B448" s="49" t="s">
@@ -17195,7 +17306,7 @@
       <c r="N448" s="13"/>
     </row>
     <row r="449" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A449" s="132"/>
+      <c r="A449" s="138"/>
       <c r="B449" s="49" t="s">
         <v>240</v>
       </c>
@@ -17227,7 +17338,7 @@
       <c r="N449" s="13"/>
     </row>
     <row r="450" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A450" s="132"/>
+      <c r="A450" s="138"/>
       <c r="B450" s="49" t="s">
         <v>240</v>
       </c>
@@ -17259,7 +17370,7 @@
       <c r="N450" s="13"/>
     </row>
     <row r="451" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A451" s="125"/>
+      <c r="A451" s="139"/>
       <c r="B451" s="49" t="s">
         <v>240</v>
       </c>
@@ -17307,7 +17418,7 @@
       <c r="N452" s="13"/>
     </row>
     <row r="453" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A453" s="131">
+      <c r="A453" s="143">
         <v>96</v>
       </c>
       <c r="B453" s="49" t="s">
@@ -17341,7 +17452,7 @@
       <c r="N453" s="13"/>
     </row>
     <row r="454" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A454" s="132"/>
+      <c r="A454" s="138"/>
       <c r="B454" s="49" t="s">
         <v>243</v>
       </c>
@@ -17373,7 +17484,7 @@
       <c r="N454" s="13"/>
     </row>
     <row r="455" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A455" s="132"/>
+      <c r="A455" s="138"/>
       <c r="B455" s="49" t="s">
         <v>243</v>
       </c>
@@ -17405,7 +17516,7 @@
       <c r="N455" s="13"/>
     </row>
     <row r="456" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A456" s="125"/>
+      <c r="A456" s="139"/>
       <c r="B456" s="49" t="s">
         <v>243</v>
       </c>
@@ -17453,7 +17564,7 @@
       <c r="N457" s="13"/>
     </row>
     <row r="458" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A458" s="131">
+      <c r="A458" s="143">
         <v>97</v>
       </c>
       <c r="B458" s="49" t="s">
@@ -17487,7 +17598,7 @@
       <c r="N458" s="13"/>
     </row>
     <row r="459" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A459" s="132"/>
+      <c r="A459" s="138"/>
       <c r="B459" s="49" t="s">
         <v>246</v>
       </c>
@@ -17519,7 +17630,7 @@
       <c r="N459" s="13"/>
     </row>
     <row r="460" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A460" s="132"/>
+      <c r="A460" s="138"/>
       <c r="B460" s="49" t="s">
         <v>246</v>
       </c>
@@ -17551,7 +17662,7 @@
       <c r="N460" s="13"/>
     </row>
     <row r="461" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A461" s="125"/>
+      <c r="A461" s="139"/>
       <c r="B461" s="49" t="s">
         <v>246</v>
       </c>
@@ -17599,7 +17710,7 @@
       <c r="N462" s="13"/>
     </row>
     <row r="463" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A463" s="131">
+      <c r="A463" s="143">
         <v>98</v>
       </c>
       <c r="B463" s="49" t="s">
@@ -17633,7 +17744,7 @@
       <c r="N463" s="13"/>
     </row>
     <row r="464" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A464" s="132"/>
+      <c r="A464" s="138"/>
       <c r="B464" s="49" t="s">
         <v>248</v>
       </c>
@@ -17665,7 +17776,7 @@
       <c r="N464" s="13"/>
     </row>
     <row r="465" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A465" s="132"/>
+      <c r="A465" s="138"/>
       <c r="B465" s="49" t="s">
         <v>248</v>
       </c>
@@ -17697,7 +17808,7 @@
       <c r="N465" s="13"/>
     </row>
     <row r="466" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A466" s="125"/>
+      <c r="A466" s="139"/>
       <c r="B466" s="49" t="s">
         <v>248</v>
       </c>
@@ -17745,7 +17856,7 @@
       <c r="N467" s="13"/>
     </row>
     <row r="468" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A468" s="131">
+      <c r="A468" s="143">
         <v>99</v>
       </c>
       <c r="B468" s="49" t="s">
@@ -17779,7 +17890,7 @@
       <c r="N468" s="13"/>
     </row>
     <row r="469" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A469" s="132"/>
+      <c r="A469" s="138"/>
       <c r="B469" s="49" t="s">
         <v>250</v>
       </c>
@@ -17811,7 +17922,7 @@
       <c r="N469" s="13"/>
     </row>
     <row r="470" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A470" s="132"/>
+      <c r="A470" s="138"/>
       <c r="B470" s="49" t="s">
         <v>250</v>
       </c>
@@ -17843,7 +17954,7 @@
       <c r="N470" s="13"/>
     </row>
     <row r="471" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A471" s="125"/>
+      <c r="A471" s="139"/>
       <c r="B471" s="49" t="s">
         <v>250</v>
       </c>
@@ -17891,7 +18002,7 @@
       <c r="N472" s="13"/>
     </row>
     <row r="473" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A473" s="131">
+      <c r="A473" s="143">
         <v>100</v>
       </c>
       <c r="B473" s="63" t="s">
@@ -17925,7 +18036,7 @@
       <c r="N473" s="13"/>
     </row>
     <row r="474" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A474" s="132"/>
+      <c r="A474" s="138"/>
       <c r="B474" s="63" t="s">
         <v>252</v>
       </c>
@@ -17957,7 +18068,7 @@
       <c r="N474" s="13"/>
     </row>
     <row r="475" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A475" s="132"/>
+      <c r="A475" s="138"/>
       <c r="B475" s="63" t="s">
         <v>252</v>
       </c>
@@ -17989,7 +18100,7 @@
       <c r="N475" s="13"/>
     </row>
     <row r="476" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A476" s="125"/>
+      <c r="A476" s="139"/>
       <c r="B476" s="63" t="s">
         <v>252</v>
       </c>
@@ -18037,7 +18148,7 @@
       <c r="N477" s="13"/>
     </row>
     <row r="478" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A478" s="131">
+      <c r="A478" s="143">
         <v>101</v>
       </c>
       <c r="B478" s="49" t="s">
@@ -18073,7 +18184,7 @@
       </c>
     </row>
     <row r="479" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A479" s="132"/>
+      <c r="A479" s="138"/>
       <c r="B479" s="49" t="s">
         <v>255</v>
       </c>
@@ -18107,7 +18218,7 @@
       </c>
     </row>
     <row r="480" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A480" s="132"/>
+      <c r="A480" s="138"/>
       <c r="B480" s="49" t="s">
         <v>255</v>
       </c>
@@ -18141,7 +18252,7 @@
       </c>
     </row>
     <row r="481" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A481" s="125"/>
+      <c r="A481" s="139"/>
       <c r="B481" s="49" t="s">
         <v>255</v>
       </c>
@@ -18191,7 +18302,7 @@
       <c r="N482" s="13"/>
     </row>
     <row r="483" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A483" s="131">
+      <c r="A483" s="143">
         <v>102</v>
       </c>
       <c r="B483" s="49" t="s">
@@ -18225,7 +18336,7 @@
       <c r="N483" s="13"/>
     </row>
     <row r="484" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A484" s="132"/>
+      <c r="A484" s="138"/>
       <c r="B484" s="49" t="s">
         <v>259</v>
       </c>
@@ -18257,7 +18368,7 @@
       <c r="N484" s="13"/>
     </row>
     <row r="485" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A485" s="132"/>
+      <c r="A485" s="138"/>
       <c r="B485" s="49" t="s">
         <v>259</v>
       </c>
@@ -18289,7 +18400,7 @@
       <c r="N485" s="13"/>
     </row>
     <row r="486" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A486" s="125"/>
+      <c r="A486" s="139"/>
       <c r="B486" s="49" t="s">
         <v>259</v>
       </c>
@@ -18337,7 +18448,7 @@
       <c r="N487" s="13"/>
     </row>
     <row r="488" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A488" s="131">
+      <c r="A488" s="143">
         <v>103</v>
       </c>
       <c r="B488" s="49" t="s">
@@ -18371,7 +18482,7 @@
       <c r="N488" s="13"/>
     </row>
     <row r="489" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A489" s="132"/>
+      <c r="A489" s="138"/>
       <c r="B489" s="49" t="s">
         <v>262</v>
       </c>
@@ -18403,7 +18514,7 @@
       <c r="N489" s="13"/>
     </row>
     <row r="490" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A490" s="132"/>
+      <c r="A490" s="138"/>
       <c r="B490" s="49" t="s">
         <v>262</v>
       </c>
@@ -18435,7 +18546,7 @@
       <c r="N490" s="13"/>
     </row>
     <row r="491" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A491" s="125"/>
+      <c r="A491" s="139"/>
       <c r="B491" s="49" t="s">
         <v>262</v>
       </c>
@@ -18483,7 +18594,7 @@
       <c r="N492" s="13"/>
     </row>
     <row r="493" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A493" s="131">
+      <c r="A493" s="143">
         <v>104</v>
       </c>
       <c r="B493" s="49" t="s">
@@ -18517,7 +18628,7 @@
       <c r="N493" s="13"/>
     </row>
     <row r="494" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A494" s="132"/>
+      <c r="A494" s="138"/>
       <c r="B494" s="49" t="s">
         <v>264</v>
       </c>
@@ -18549,7 +18660,7 @@
       <c r="N494" s="13"/>
     </row>
     <row r="495" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A495" s="132"/>
+      <c r="A495" s="138"/>
       <c r="B495" s="49" t="s">
         <v>264</v>
       </c>
@@ -18581,7 +18692,7 @@
       <c r="N495" s="13"/>
     </row>
     <row r="496" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A496" s="125"/>
+      <c r="A496" s="139"/>
       <c r="B496" s="49" t="s">
         <v>264</v>
       </c>
@@ -18629,7 +18740,7 @@
       <c r="N497" s="13"/>
     </row>
     <row r="498" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A498" s="131">
+      <c r="A498" s="143">
         <v>105</v>
       </c>
       <c r="B498" s="49" t="s">
@@ -18663,7 +18774,7 @@
       <c r="N498" s="13"/>
     </row>
     <row r="499" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A499" s="132"/>
+      <c r="A499" s="138"/>
       <c r="B499" s="49" t="s">
         <v>266</v>
       </c>
@@ -18695,7 +18806,7 @@
       <c r="N499" s="13"/>
     </row>
     <row r="500" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A500" s="132"/>
+      <c r="A500" s="138"/>
       <c r="B500" s="49" t="s">
         <v>266</v>
       </c>
@@ -18727,7 +18838,7 @@
       <c r="N500" s="13"/>
     </row>
     <row r="501" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A501" s="125"/>
+      <c r="A501" s="139"/>
       <c r="B501" s="49" t="s">
         <v>266</v>
       </c>
@@ -18775,7 +18886,7 @@
       <c r="N502" s="13"/>
     </row>
     <row r="503" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A503" s="131">
+      <c r="A503" s="143">
         <v>106</v>
       </c>
       <c r="B503" s="49" t="s">
@@ -18809,7 +18920,7 @@
       <c r="N503" s="13"/>
     </row>
     <row r="504" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A504" s="132"/>
+      <c r="A504" s="138"/>
       <c r="B504" s="49" t="s">
         <v>268</v>
       </c>
@@ -18841,7 +18952,7 @@
       <c r="N504" s="13"/>
     </row>
     <row r="505" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A505" s="132"/>
+      <c r="A505" s="138"/>
       <c r="B505" s="49" t="s">
         <v>268</v>
       </c>
@@ -18873,7 +18984,7 @@
       <c r="N505" s="13"/>
     </row>
     <row r="506" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A506" s="125"/>
+      <c r="A506" s="139"/>
       <c r="B506" s="49" t="s">
         <v>268</v>
       </c>
@@ -18921,7 +19032,7 @@
       <c r="N507" s="13"/>
     </row>
     <row r="508" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A508" s="131">
+      <c r="A508" s="143">
         <v>107</v>
       </c>
       <c r="B508" s="49" t="s">
@@ -18955,7 +19066,7 @@
       <c r="N508" s="13"/>
     </row>
     <row r="509" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A509" s="132"/>
+      <c r="A509" s="138"/>
       <c r="B509" s="49" t="s">
         <v>270</v>
       </c>
@@ -18987,7 +19098,7 @@
       <c r="N509" s="13"/>
     </row>
     <row r="510" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A510" s="132"/>
+      <c r="A510" s="138"/>
       <c r="B510" s="49" t="s">
         <v>270</v>
       </c>
@@ -19019,7 +19130,7 @@
       <c r="N510" s="13"/>
     </row>
     <row r="511" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A511" s="125"/>
+      <c r="A511" s="139"/>
       <c r="B511" s="49" t="s">
         <v>270</v>
       </c>
@@ -19067,7 +19178,7 @@
       <c r="N512" s="13"/>
     </row>
     <row r="513" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A513" s="131">
+      <c r="A513" s="143">
         <v>108</v>
       </c>
       <c r="B513" s="69" t="s">
@@ -19101,7 +19212,7 @@
       <c r="N513" s="13"/>
     </row>
     <row r="514" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A514" s="132"/>
+      <c r="A514" s="138"/>
       <c r="B514" s="69" t="s">
         <v>272</v>
       </c>
@@ -19133,7 +19244,7 @@
       <c r="N514" s="13"/>
     </row>
     <row r="515" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A515" s="132"/>
+      <c r="A515" s="138"/>
       <c r="B515" s="69" t="s">
         <v>272</v>
       </c>
@@ -19165,7 +19276,7 @@
       <c r="N515" s="13"/>
     </row>
     <row r="516" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A516" s="125"/>
+      <c r="A516" s="139"/>
       <c r="B516" s="76" t="s">
         <v>272</v>
       </c>
@@ -19213,7 +19324,7 @@
       <c r="N517" s="13"/>
     </row>
     <row r="518" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A518" s="134">
+      <c r="A518" s="130">
         <v>109</v>
       </c>
       <c r="B518" s="83" t="s">
@@ -19249,7 +19360,7 @@
       <c r="N518" s="13"/>
     </row>
     <row r="519" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A519" s="135"/>
+      <c r="A519" s="131"/>
       <c r="B519" s="84" t="s">
         <v>274</v>
       </c>
@@ -19283,7 +19394,7 @@
       <c r="N519" s="27"/>
     </row>
     <row r="520" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A520" s="135"/>
+      <c r="A520" s="131"/>
       <c r="B520" s="84" t="s">
         <v>274</v>
       </c>
@@ -19317,7 +19428,7 @@
       <c r="N520" s="27"/>
     </row>
     <row r="521" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A521" s="136"/>
+      <c r="A521" s="132"/>
       <c r="B521" s="84" t="s">
         <v>274</v>
       </c>
@@ -19413,7 +19524,7 @@
       <c r="N524" s="13"/>
     </row>
     <row r="525" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A525" s="134">
+      <c r="A525" s="130">
         <v>111</v>
       </c>
       <c r="B525" s="19" t="s">
@@ -19447,7 +19558,7 @@
       <c r="N525" s="13"/>
     </row>
     <row r="526" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A526" s="135"/>
+      <c r="A526" s="131"/>
       <c r="B526" s="19" t="s">
         <v>281</v>
       </c>
@@ -19479,7 +19590,7 @@
       <c r="N526" s="13"/>
     </row>
     <row r="527" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A527" s="135"/>
+      <c r="A527" s="131"/>
       <c r="B527" s="19" t="s">
         <v>281</v>
       </c>
@@ -19511,7 +19622,7 @@
       <c r="N527" s="13"/>
     </row>
     <row r="528" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A528" s="136"/>
+      <c r="A528" s="132"/>
       <c r="B528" s="90" t="s">
         <v>281</v>
       </c>
@@ -19559,7 +19670,7 @@
       <c r="N529" s="13"/>
     </row>
     <row r="530" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A530" s="134">
+      <c r="A530" s="130">
         <v>112</v>
       </c>
       <c r="B530" s="13" t="s">
@@ -19593,7 +19704,7 @@
       <c r="N530" s="13"/>
     </row>
     <row r="531" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A531" s="135"/>
+      <c r="A531" s="131"/>
       <c r="B531" s="27" t="s">
         <v>284</v>
       </c>
@@ -19625,7 +19736,7 @@
       <c r="N531" s="27"/>
     </row>
     <row r="532" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A532" s="135"/>
+      <c r="A532" s="131"/>
       <c r="B532" s="27" t="s">
         <v>284</v>
       </c>
@@ -19657,7 +19768,7 @@
       <c r="N532" s="27"/>
     </row>
     <row r="533" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A533" s="136"/>
+      <c r="A533" s="132"/>
       <c r="B533" s="27" t="s">
         <v>284</v>
       </c>
@@ -20077,7 +20188,7 @@
       <c r="N550" s="13"/>
     </row>
     <row r="551" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A551" s="134">
+      <c r="A551" s="130">
         <v>121</v>
       </c>
       <c r="B551" s="13" t="s">
@@ -20111,7 +20222,7 @@
       <c r="N551" s="13"/>
     </row>
     <row r="552" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A552" s="135"/>
+      <c r="A552" s="131"/>
       <c r="B552" s="13" t="s">
         <v>312</v>
       </c>
@@ -20143,7 +20254,7 @@
       <c r="N552" s="13"/>
     </row>
     <row r="553" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A553" s="135"/>
+      <c r="A553" s="131"/>
       <c r="B553" s="13" t="s">
         <v>312</v>
       </c>
@@ -20175,7 +20286,7 @@
       <c r="N553" s="13"/>
     </row>
     <row r="554" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A554" s="135"/>
+      <c r="A554" s="131"/>
       <c r="B554" s="13" t="s">
         <v>312</v>
       </c>
@@ -20207,7 +20318,7 @@
       <c r="N554" s="13"/>
     </row>
     <row r="555" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A555" s="135"/>
+      <c r="A555" s="131"/>
       <c r="B555" s="13" t="s">
         <v>312</v>
       </c>
@@ -20239,7 +20350,7 @@
       <c r="N555" s="13"/>
     </row>
     <row r="556" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A556" s="135"/>
+      <c r="A556" s="131"/>
       <c r="B556" s="13" t="s">
         <v>312</v>
       </c>
@@ -20271,7 +20382,7 @@
       <c r="N556" s="13"/>
     </row>
     <row r="557" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A557" s="135"/>
+      <c r="A557" s="131"/>
       <c r="B557" s="13" t="s">
         <v>312</v>
       </c>
@@ -20303,7 +20414,7 @@
       <c r="N557" s="13"/>
     </row>
     <row r="558" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A558" s="136"/>
+      <c r="A558" s="132"/>
       <c r="B558" s="13" t="s">
         <v>312</v>
       </c>
@@ -20351,7 +20462,7 @@
       <c r="N559" s="13"/>
     </row>
     <row r="560" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A560" s="134">
+      <c r="A560" s="130">
         <v>122</v>
       </c>
       <c r="B560" s="13" t="s">
@@ -20385,7 +20496,7 @@
       <c r="N560" s="13"/>
     </row>
     <row r="561" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A561" s="135"/>
+      <c r="A561" s="131"/>
       <c r="B561" s="13" t="s">
         <v>315</v>
       </c>
@@ -20417,7 +20528,7 @@
       <c r="N561" s="13"/>
     </row>
     <row r="562" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A562" s="135"/>
+      <c r="A562" s="131"/>
       <c r="B562" s="13" t="s">
         <v>315</v>
       </c>
@@ -20449,7 +20560,7 @@
       <c r="N562" s="13"/>
     </row>
     <row r="563" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A563" s="135"/>
+      <c r="A563" s="131"/>
       <c r="B563" s="13" t="s">
         <v>315</v>
       </c>
@@ -20481,7 +20592,7 @@
       <c r="N563" s="13"/>
     </row>
     <row r="564" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A564" s="135"/>
+      <c r="A564" s="131"/>
       <c r="B564" s="13" t="s">
         <v>315</v>
       </c>
@@ -20513,7 +20624,7 @@
       <c r="N564" s="13"/>
     </row>
     <row r="565" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A565" s="135"/>
+      <c r="A565" s="131"/>
       <c r="B565" s="13" t="s">
         <v>315</v>
       </c>
@@ -20545,7 +20656,7 @@
       <c r="N565" s="13"/>
     </row>
     <row r="566" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A566" s="135"/>
+      <c r="A566" s="131"/>
       <c r="B566" s="13" t="s">
         <v>315</v>
       </c>
@@ -20577,7 +20688,7 @@
       <c r="N566" s="13"/>
     </row>
     <row r="567" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A567" s="136"/>
+      <c r="A567" s="132"/>
       <c r="B567" s="13" t="s">
         <v>315</v>
       </c>
@@ -20719,7 +20830,7 @@
       <c r="N572" s="13"/>
     </row>
     <row r="573" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A573" s="134">
+      <c r="A573" s="130">
         <v>125</v>
       </c>
       <c r="B573" s="94" t="s">
@@ -20753,7 +20864,7 @@
       <c r="N573" s="13"/>
     </row>
     <row r="574" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A574" s="135"/>
+      <c r="A574" s="131"/>
       <c r="B574" s="94" t="s">
         <v>323</v>
       </c>
@@ -20785,7 +20896,7 @@
       <c r="N574" s="13"/>
     </row>
     <row r="575" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A575" s="135"/>
+      <c r="A575" s="131"/>
       <c r="B575" s="94" t="s">
         <v>323</v>
       </c>
@@ -20817,7 +20928,7 @@
       <c r="N575" s="13"/>
     </row>
     <row r="576" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A576" s="136"/>
+      <c r="A576" s="132"/>
       <c r="B576" s="94" t="s">
         <v>323</v>
       </c>
@@ -20865,7 +20976,7 @@
       <c r="N577" s="13"/>
     </row>
     <row r="578" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A578" s="134">
+      <c r="A578" s="130">
         <v>126</v>
       </c>
       <c r="B578" s="96" t="s">
@@ -20899,7 +21010,7 @@
       <c r="N578" s="13"/>
     </row>
     <row r="579" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A579" s="135"/>
+      <c r="A579" s="131"/>
       <c r="B579" s="96" t="s">
         <v>325</v>
       </c>
@@ -20931,7 +21042,7 @@
       <c r="N579" s="13"/>
     </row>
     <row r="580" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A580" s="135"/>
+      <c r="A580" s="131"/>
       <c r="B580" s="96" t="s">
         <v>325</v>
       </c>
@@ -20963,7 +21074,7 @@
       <c r="N580" s="13"/>
     </row>
     <row r="581" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A581" s="136"/>
+      <c r="A581" s="132"/>
       <c r="B581" s="96" t="s">
         <v>325</v>
       </c>
@@ -21011,7 +21122,7 @@
       <c r="N582" s="13"/>
     </row>
     <row r="583" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A583" s="134">
+      <c r="A583" s="130">
         <v>127</v>
       </c>
       <c r="B583" s="96" t="s">
@@ -21045,7 +21156,7 @@
       <c r="N583" s="13"/>
     </row>
     <row r="584" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A584" s="135"/>
+      <c r="A584" s="131"/>
       <c r="B584" s="96" t="s">
         <v>327</v>
       </c>
@@ -21077,7 +21188,7 @@
       <c r="N584" s="13"/>
     </row>
     <row r="585" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A585" s="135"/>
+      <c r="A585" s="131"/>
       <c r="B585" s="96" t="s">
         <v>327</v>
       </c>
@@ -21109,7 +21220,7 @@
       <c r="N585" s="13"/>
     </row>
     <row r="586" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A586" s="136"/>
+      <c r="A586" s="132"/>
       <c r="B586" s="96" t="s">
         <v>327</v>
       </c>
@@ -21157,7 +21268,7 @@
       <c r="N587" s="13"/>
     </row>
     <row r="588" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A588" s="134">
+      <c r="A588" s="130">
         <v>128</v>
       </c>
       <c r="B588" s="96" t="s">
@@ -21191,7 +21302,7 @@
       <c r="N588" s="13"/>
     </row>
     <row r="589" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A589" s="135"/>
+      <c r="A589" s="131"/>
       <c r="B589" s="96" t="s">
         <v>329</v>
       </c>
@@ -21223,7 +21334,7 @@
       <c r="N589" s="13"/>
     </row>
     <row r="590" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A590" s="135"/>
+      <c r="A590" s="131"/>
       <c r="B590" s="96" t="s">
         <v>329</v>
       </c>
@@ -21255,7 +21366,7 @@
       <c r="N590" s="13"/>
     </row>
     <row r="591" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A591" s="136"/>
+      <c r="A591" s="132"/>
       <c r="B591" s="96" t="s">
         <v>329</v>
       </c>
@@ -21347,7 +21458,7 @@
       <c r="N594" s="13"/>
     </row>
     <row r="595" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A595" s="134">
+      <c r="A595" s="130">
         <v>130</v>
       </c>
       <c r="B595" s="19" t="s">
@@ -21381,7 +21492,7 @@
       <c r="N595" s="13"/>
     </row>
     <row r="596" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A596" s="135"/>
+      <c r="A596" s="131"/>
       <c r="B596" s="19" t="s">
         <v>333</v>
       </c>
@@ -21413,7 +21524,7 @@
       <c r="N596" s="13"/>
     </row>
     <row r="597" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A597" s="135"/>
+      <c r="A597" s="131"/>
       <c r="B597" s="19" t="s">
         <v>333</v>
       </c>
@@ -21445,7 +21556,7 @@
       <c r="N597" s="13"/>
     </row>
     <row r="598" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A598" s="136"/>
+      <c r="A598" s="132"/>
       <c r="B598" s="19" t="s">
         <v>333</v>
       </c>
@@ -21493,7 +21604,7 @@
       <c r="N599" s="13"/>
     </row>
     <row r="600" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A600" s="134">
+      <c r="A600" s="130">
         <v>131</v>
       </c>
       <c r="B600" s="19" t="s">
@@ -21527,7 +21638,7 @@
       <c r="N600" s="13"/>
     </row>
     <row r="601" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A601" s="135"/>
+      <c r="A601" s="131"/>
       <c r="B601" s="19" t="s">
         <v>336</v>
       </c>
@@ -21559,7 +21670,7 @@
       <c r="N601" s="13"/>
     </row>
     <row r="602" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A602" s="135"/>
+      <c r="A602" s="131"/>
       <c r="B602" s="19" t="s">
         <v>336</v>
       </c>
@@ -21591,7 +21702,7 @@
       <c r="N602" s="13"/>
     </row>
     <row r="603" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A603" s="136"/>
+      <c r="A603" s="132"/>
       <c r="B603" s="19" t="s">
         <v>336</v>
       </c>
@@ -21639,7 +21750,7 @@
       <c r="N604" s="13"/>
     </row>
     <row r="605" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A605" s="134">
+      <c r="A605" s="130">
         <v>132</v>
       </c>
       <c r="B605" s="19" t="s">
@@ -21673,7 +21784,7 @@
       <c r="N605" s="13"/>
     </row>
     <row r="606" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A606" s="135"/>
+      <c r="A606" s="131"/>
       <c r="B606" s="19" t="s">
         <v>338</v>
       </c>
@@ -21705,7 +21816,7 @@
       <c r="N606" s="62"/>
     </row>
     <row r="607" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A607" s="135"/>
+      <c r="A607" s="131"/>
       <c r="B607" s="19" t="s">
         <v>338</v>
       </c>
@@ -21737,7 +21848,7 @@
       <c r="N607" s="62"/>
     </row>
     <row r="608" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A608" s="136"/>
+      <c r="A608" s="132"/>
       <c r="B608" s="19" t="s">
         <v>338</v>
       </c>
@@ -21785,7 +21896,7 @@
       <c r="N609" s="62"/>
     </row>
     <row r="610" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A610" s="134">
+      <c r="A610" s="130">
         <v>133</v>
       </c>
       <c r="B610" s="19" t="s">
@@ -21819,7 +21930,7 @@
       <c r="N610" s="62"/>
     </row>
     <row r="611" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A611" s="135"/>
+      <c r="A611" s="131"/>
       <c r="B611" s="19" t="s">
         <v>340</v>
       </c>
@@ -21851,7 +21962,7 @@
       <c r="N611" s="62"/>
     </row>
     <row r="612" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A612" s="135"/>
+      <c r="A612" s="131"/>
       <c r="B612" s="19" t="s">
         <v>340</v>
       </c>
@@ -21883,7 +21994,7 @@
       <c r="N612" s="62"/>
     </row>
     <row r="613" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A613" s="136"/>
+      <c r="A613" s="132"/>
       <c r="B613" s="19" t="s">
         <v>340</v>
       </c>
@@ -22023,7 +22134,7 @@
       <c r="N618" s="13"/>
     </row>
     <row r="619" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A619" s="134">
+      <c r="A619" s="130">
         <v>136</v>
       </c>
       <c r="B619" s="19" t="s">
@@ -22055,7 +22166,7 @@
       <c r="N619" s="13"/>
     </row>
     <row r="620" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A620" s="135"/>
+      <c r="A620" s="131"/>
       <c r="B620" s="19" t="s">
         <v>346</v>
       </c>
@@ -22085,7 +22196,7 @@
       <c r="N620" s="13"/>
     </row>
     <row r="621" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A621" s="135"/>
+      <c r="A621" s="131"/>
       <c r="B621" s="19" t="s">
         <v>346</v>
       </c>
@@ -22115,7 +22226,7 @@
       <c r="N621" s="13"/>
     </row>
     <row r="622" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A622" s="136"/>
+      <c r="A622" s="132"/>
       <c r="B622" s="19" t="s">
         <v>346</v>
       </c>
@@ -22205,7 +22316,7 @@
       <c r="N625" s="36"/>
     </row>
     <row r="626" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A626" s="138">
+      <c r="A626" s="136">
         <v>140</v>
       </c>
       <c r="B626" s="49"/>
@@ -22237,7 +22348,7 @@
       <c r="N626" s="13"/>
     </row>
     <row r="627" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A627" s="139"/>
+      <c r="A627" s="134"/>
       <c r="B627" s="49"/>
       <c r="C627" s="7" t="s">
         <v>19</v>
@@ -22267,7 +22378,7 @@
       <c r="N627" s="13"/>
     </row>
     <row r="628" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A628" s="139"/>
+      <c r="A628" s="134"/>
       <c r="B628" s="49"/>
       <c r="C628" s="7" t="s">
         <v>21</v>
@@ -22297,7 +22408,7 @@
       <c r="N628" s="13"/>
     </row>
     <row r="629" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A629" s="140"/>
+      <c r="A629" s="135"/>
       <c r="B629" s="49"/>
       <c r="C629" s="7" t="s">
         <v>23</v>
@@ -22375,7 +22486,7 @@
       <c r="N631" s="13"/>
     </row>
     <row r="632" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A632" s="139"/>
+      <c r="A632" s="134"/>
       <c r="B632" s="49"/>
       <c r="C632" s="7" t="s">
         <v>19</v>
@@ -22405,7 +22516,7 @@
       <c r="N632" s="13"/>
     </row>
     <row r="633" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A633" s="139"/>
+      <c r="A633" s="134"/>
       <c r="B633" s="49"/>
       <c r="C633" s="7" t="s">
         <v>21</v>
@@ -22435,7 +22546,7 @@
       <c r="N633" s="13"/>
     </row>
     <row r="634" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A634" s="140"/>
+      <c r="A634" s="135"/>
       <c r="B634" s="49"/>
       <c r="C634" s="7" t="s">
         <v>23</v>
@@ -22523,7 +22634,7 @@
       <c r="Z636" s="109"/>
     </row>
     <row r="637" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A637" s="139"/>
+      <c r="A637" s="134"/>
       <c r="B637" s="104"/>
       <c r="C637" s="28" t="s">
         <v>19</v>
@@ -22563,7 +22674,7 @@
       <c r="Z637" s="109"/>
     </row>
     <row r="638" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A638" s="139"/>
+      <c r="A638" s="134"/>
       <c r="B638" s="104"/>
       <c r="C638" s="28" t="s">
         <v>21</v>
@@ -22603,7 +22714,7 @@
       <c r="Z638" s="109"/>
     </row>
     <row r="639" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A639" s="140"/>
+      <c r="A639" s="135"/>
       <c r="B639" s="104"/>
       <c r="C639" s="28" t="s">
         <v>23</v>
@@ -22659,7 +22770,7 @@
       <c r="N640" s="13"/>
     </row>
     <row r="641" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A641" s="138">
+      <c r="A641" s="136">
         <v>142</v>
       </c>
       <c r="B641" s="49" t="s">
@@ -22691,7 +22802,7 @@
       <c r="N641" s="13"/>
     </row>
     <row r="642" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A642" s="139"/>
+      <c r="A642" s="134"/>
       <c r="B642" s="49"/>
       <c r="C642" s="49"/>
       <c r="D642" s="49"/>
@@ -22717,7 +22828,7 @@
       <c r="N642" s="13"/>
     </row>
     <row r="643" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A643" s="139"/>
+      <c r="A643" s="134"/>
       <c r="B643" s="49"/>
       <c r="C643" s="49"/>
       <c r="D643" s="49"/>
@@ -22743,7 +22854,7 @@
       <c r="N643" s="13"/>
     </row>
     <row r="644" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A644" s="139"/>
+      <c r="A644" s="134"/>
       <c r="B644" s="49" t="s">
         <v>361</v>
       </c>
@@ -22773,7 +22884,7 @@
       <c r="N644" s="13"/>
     </row>
     <row r="645" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A645" s="139"/>
+      <c r="A645" s="134"/>
       <c r="B645" s="49"/>
       <c r="C645" s="49"/>
       <c r="D645" s="49"/>
@@ -22799,7 +22910,7 @@
       <c r="N645" s="13"/>
     </row>
     <row r="646" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A646" s="139"/>
+      <c r="A646" s="134"/>
       <c r="B646" s="49"/>
       <c r="C646" s="49"/>
       <c r="D646" s="49"/>
@@ -22825,7 +22936,7 @@
       <c r="N646" s="13"/>
     </row>
     <row r="647" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A647" s="139"/>
+      <c r="A647" s="134"/>
       <c r="B647" s="49" t="s">
         <v>362</v>
       </c>
@@ -22855,7 +22966,7 @@
       <c r="N647" s="13"/>
     </row>
     <row r="648" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A648" s="139"/>
+      <c r="A648" s="134"/>
       <c r="B648" s="49"/>
       <c r="C648" s="49"/>
       <c r="D648" s="49"/>
@@ -22881,7 +22992,7 @@
       <c r="N648" s="13"/>
     </row>
     <row r="649" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A649" s="139"/>
+      <c r="A649" s="134"/>
       <c r="B649" s="49"/>
       <c r="C649" s="49"/>
       <c r="D649" s="49"/>
@@ -22907,7 +23018,7 @@
       <c r="N649" s="13"/>
     </row>
     <row r="650" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A650" s="139"/>
+      <c r="A650" s="134"/>
       <c r="B650" s="49" t="s">
         <v>363</v>
       </c>
@@ -22937,7 +23048,7 @@
       <c r="N650" s="13"/>
     </row>
     <row r="651" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A651" s="139"/>
+      <c r="A651" s="134"/>
       <c r="B651" s="49"/>
       <c r="C651" s="49"/>
       <c r="D651" s="49"/>
@@ -22963,7 +23074,7 @@
       <c r="N651" s="13"/>
     </row>
     <row r="652" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A652" s="140"/>
+      <c r="A652" s="135"/>
       <c r="B652" s="49"/>
       <c r="C652" s="49"/>
       <c r="D652" s="49"/>
@@ -23005,7 +23116,7 @@
       <c r="N653" s="13"/>
     </row>
     <row r="654" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A654" s="138">
+      <c r="A654" s="136">
         <v>143</v>
       </c>
       <c r="B654" s="49"/>
@@ -23037,7 +23148,7 @@
       <c r="N654" s="13"/>
     </row>
     <row r="655" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A655" s="139"/>
+      <c r="A655" s="134"/>
       <c r="B655" s="49"/>
       <c r="C655" s="7" t="s">
         <v>19</v>
@@ -23067,7 +23178,7 @@
       <c r="N655" s="13"/>
     </row>
     <row r="656" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A656" s="139"/>
+      <c r="A656" s="134"/>
       <c r="B656" s="49"/>
       <c r="C656" s="7" t="s">
         <v>21</v>
@@ -23097,7 +23208,7 @@
       <c r="N656" s="13"/>
     </row>
     <row r="657" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A657" s="140"/>
+      <c r="A657" s="135"/>
       <c r="B657" s="49"/>
       <c r="C657" s="7" t="s">
         <v>23</v>
@@ -23143,7 +23254,7 @@
       <c r="N658" s="13"/>
     </row>
     <row r="659" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A659" s="138">
+      <c r="A659" s="136">
         <v>144</v>
       </c>
       <c r="B659" s="49"/>
@@ -23175,7 +23286,7 @@
       <c r="N659" s="13"/>
     </row>
     <row r="660" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A660" s="139"/>
+      <c r="A660" s="134"/>
       <c r="B660" s="49"/>
       <c r="C660" s="7" t="s">
         <v>19</v>
@@ -23205,7 +23316,7 @@
       <c r="N660" s="13"/>
     </row>
     <row r="661" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A661" s="139"/>
+      <c r="A661" s="134"/>
       <c r="B661" s="49"/>
       <c r="C661" s="7" t="s">
         <v>21</v>
@@ -23235,7 +23346,7 @@
       <c r="N661" s="13"/>
     </row>
     <row r="662" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A662" s="140"/>
+      <c r="A662" s="135"/>
       <c r="B662" s="49"/>
       <c r="C662" s="7" t="s">
         <v>23</v>
@@ -23281,7 +23392,7 @@
       <c r="N663" s="13"/>
     </row>
     <row r="664" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A664" s="143">
+      <c r="A664" s="133">
         <v>145</v>
       </c>
       <c r="B664" s="54"/>
@@ -23325,7 +23436,7 @@
       <c r="Z664" s="58"/>
     </row>
     <row r="665" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A665" s="139"/>
+      <c r="A665" s="134"/>
       <c r="B665" s="54"/>
       <c r="C665" s="21" t="s">
         <v>19</v>
@@ -23367,7 +23478,7 @@
       <c r="Z665" s="58"/>
     </row>
     <row r="666" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A666" s="139"/>
+      <c r="A666" s="134"/>
       <c r="B666" s="54"/>
       <c r="C666" s="21" t="s">
         <v>21</v>
@@ -23409,7 +23520,7 @@
       <c r="Z666" s="58"/>
     </row>
     <row r="667" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A667" s="140"/>
+      <c r="A667" s="135"/>
       <c r="B667" s="54"/>
       <c r="C667" s="21" t="s">
         <v>23</v>
@@ -23467,7 +23578,7 @@
       <c r="N668" s="13"/>
     </row>
     <row r="669" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A669" s="138">
+      <c r="A669" s="136">
         <v>146</v>
       </c>
       <c r="B669" s="49"/>
@@ -23499,7 +23610,7 @@
       <c r="N669" s="13"/>
     </row>
     <row r="670" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A670" s="139"/>
+      <c r="A670" s="134"/>
       <c r="B670" s="63"/>
       <c r="C670" s="7" t="s">
         <v>19</v>
@@ -23529,7 +23640,7 @@
       <c r="N670" s="13"/>
     </row>
     <row r="671" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A671" s="139"/>
+      <c r="A671" s="134"/>
       <c r="B671" s="63"/>
       <c r="C671" s="7" t="s">
         <v>21</v>
@@ -23559,7 +23670,7 @@
       <c r="N671" s="13"/>
     </row>
     <row r="672" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A672" s="140"/>
+      <c r="A672" s="135"/>
       <c r="B672" s="63"/>
       <c r="C672" s="7" t="s">
         <v>23</v>
@@ -23605,7 +23716,7 @@
       <c r="N673" s="13"/>
     </row>
     <row r="674" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A674" s="138">
+      <c r="A674" s="136">
         <v>147</v>
       </c>
       <c r="B674" s="66"/>
@@ -23637,7 +23748,7 @@
       <c r="N674" s="13"/>
     </row>
     <row r="675" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A675" s="139"/>
+      <c r="A675" s="134"/>
       <c r="B675" s="66"/>
       <c r="C675" s="7" t="s">
         <v>19</v>
@@ -23667,7 +23778,7 @@
       <c r="N675" s="13"/>
     </row>
     <row r="676" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A676" s="139"/>
+      <c r="A676" s="134"/>
       <c r="B676" s="66"/>
       <c r="C676" s="7" t="s">
         <v>21</v>
@@ -23697,7 +23808,7 @@
       <c r="N676" s="13"/>
     </row>
     <row r="677" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A677" s="140"/>
+      <c r="A677" s="135"/>
       <c r="B677" s="66"/>
       <c r="C677" s="7" t="s">
         <v>23</v>
@@ -23743,7 +23854,7 @@
       <c r="N678" s="13"/>
     </row>
     <row r="679" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A679" s="143">
+      <c r="A679" s="133">
         <v>148</v>
       </c>
       <c r="B679" s="57"/>
@@ -23787,7 +23898,7 @@
       <c r="Z679" s="58"/>
     </row>
     <row r="680" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A680" s="139"/>
+      <c r="A680" s="134"/>
       <c r="B680" s="57"/>
       <c r="C680" s="21" t="s">
         <v>19</v>
@@ -23829,7 +23940,7 @@
       <c r="Z680" s="58"/>
     </row>
     <row r="681" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A681" s="139"/>
+      <c r="A681" s="134"/>
       <c r="B681" s="57"/>
       <c r="C681" s="21" t="s">
         <v>21</v>
@@ -23871,7 +23982,7 @@
       <c r="Z681" s="58"/>
     </row>
     <row r="682" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A682" s="140"/>
+      <c r="A682" s="135"/>
       <c r="B682" s="57"/>
       <c r="C682" s="21" t="s">
         <v>23</v>
@@ -23929,7 +24040,7 @@
       <c r="N683" s="13"/>
     </row>
     <row r="684" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A684" s="138">
+      <c r="A684" s="136">
         <v>149</v>
       </c>
       <c r="B684" s="57"/>
@@ -23961,7 +24072,7 @@
       <c r="N684" s="27"/>
     </row>
     <row r="685" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A685" s="139"/>
+      <c r="A685" s="134"/>
       <c r="B685" s="112"/>
       <c r="C685" s="21" t="s">
         <v>19</v>
@@ -23991,7 +24102,7 @@
       <c r="N685" s="27"/>
     </row>
     <row r="686" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A686" s="139"/>
+      <c r="A686" s="134"/>
       <c r="B686" s="112"/>
       <c r="C686" s="21" t="s">
         <v>21</v>
@@ -24021,7 +24132,7 @@
       <c r="N686" s="27"/>
     </row>
     <row r="687" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A687" s="140"/>
+      <c r="A687" s="135"/>
       <c r="B687" s="112"/>
       <c r="C687" s="21" t="s">
         <v>23</v>
@@ -24067,7 +24178,7 @@
       <c r="N688" s="13"/>
     </row>
     <row r="689" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A689" s="133">
+      <c r="A689" s="137">
         <v>150</v>
       </c>
       <c r="B689" s="27"/>
@@ -24111,7 +24222,7 @@
       <c r="Z689" s="58"/>
     </row>
     <row r="690" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A690" s="132"/>
+      <c r="A690" s="138"/>
       <c r="B690" s="27"/>
       <c r="C690" s="21" t="s">
         <v>19</v>
@@ -24153,7 +24264,7 @@
       <c r="Z690" s="58"/>
     </row>
     <row r="691" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A691" s="132"/>
+      <c r="A691" s="138"/>
       <c r="B691" s="27"/>
       <c r="C691" s="21" t="s">
         <v>21</v>
@@ -24195,7 +24306,7 @@
       <c r="Z691" s="58"/>
     </row>
     <row r="692" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A692" s="125"/>
+      <c r="A692" s="139"/>
       <c r="B692" s="27"/>
       <c r="C692" s="21" t="s">
         <v>23</v>
@@ -24253,7 +24364,7 @@
       <c r="N693" s="13"/>
     </row>
     <row r="694" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A694" s="144">
+      <c r="A694" s="140">
         <v>151</v>
       </c>
       <c r="B694" s="115"/>
@@ -24297,7 +24408,7 @@
       <c r="Z694" s="58"/>
     </row>
     <row r="695" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A695" s="135"/>
+      <c r="A695" s="131"/>
       <c r="B695" s="115"/>
       <c r="C695" s="21" t="s">
         <v>19</v>
@@ -24339,7 +24450,7 @@
       <c r="Z695" s="58"/>
     </row>
     <row r="696" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A696" s="135"/>
+      <c r="A696" s="131"/>
       <c r="B696" s="115"/>
       <c r="C696" s="21" t="s">
         <v>21</v>
@@ -24381,7 +24492,7 @@
       <c r="Z696" s="58"/>
     </row>
     <row r="697" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A697" s="136"/>
+      <c r="A697" s="132"/>
       <c r="B697" s="115"/>
       <c r="C697" s="21" t="s">
         <v>23</v>
@@ -24439,7 +24550,7 @@
       <c r="N698" s="13"/>
     </row>
     <row r="699" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A699" s="134">
+      <c r="A699" s="130">
         <v>152</v>
       </c>
       <c r="B699" s="27"/>
@@ -24469,7 +24580,7 @@
       <c r="N699" s="27"/>
     </row>
     <row r="700" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A700" s="135"/>
+      <c r="A700" s="131"/>
       <c r="B700" s="27"/>
       <c r="C700" s="21" t="s">
         <v>19</v>
@@ -24497,7 +24608,7 @@
       <c r="N700" s="27"/>
     </row>
     <row r="701" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A701" s="135"/>
+      <c r="A701" s="131"/>
       <c r="B701" s="27"/>
       <c r="C701" s="21" t="s">
         <v>21</v>
@@ -24525,7 +24636,7 @@
       <c r="N701" s="27"/>
     </row>
     <row r="702" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A702" s="136"/>
+      <c r="A702" s="132"/>
       <c r="B702" s="27"/>
       <c r="C702" s="21" t="s">
         <v>23</v>
@@ -24569,7 +24680,7 @@
       <c r="N703" s="13"/>
     </row>
     <row r="704" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A704" s="134">
+      <c r="A704" s="130">
         <v>153</v>
       </c>
       <c r="B704" s="27"/>
@@ -24599,7 +24710,7 @@
       <c r="N704" s="27"/>
     </row>
     <row r="705" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A705" s="135"/>
+      <c r="A705" s="131"/>
       <c r="B705" s="27"/>
       <c r="C705" s="21" t="s">
         <v>19</v>
@@ -24627,7 +24738,7 @@
       <c r="N705" s="27"/>
     </row>
     <row r="706" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A706" s="135"/>
+      <c r="A706" s="131"/>
       <c r="B706" s="27"/>
       <c r="C706" s="21" t="s">
         <v>21</v>
@@ -24655,7 +24766,7 @@
       <c r="N706" s="27"/>
     </row>
     <row r="707" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A707" s="136"/>
+      <c r="A707" s="132"/>
       <c r="B707" s="27"/>
       <c r="C707" s="21" t="s">
         <v>23</v>
@@ -24699,7 +24810,7 @@
       <c r="N708" s="13"/>
     </row>
     <row r="709" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A709" s="134">
+      <c r="A709" s="130">
         <v>154</v>
       </c>
       <c r="B709" s="13"/>
@@ -24729,7 +24840,7 @@
       <c r="N709" s="13"/>
     </row>
     <row r="710" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A710" s="135"/>
+      <c r="A710" s="131"/>
       <c r="B710" s="13"/>
       <c r="C710" s="7" t="s">
         <v>19</v>
@@ -24757,7 +24868,7 @@
       <c r="N710" s="13"/>
     </row>
     <row r="711" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A711" s="135"/>
+      <c r="A711" s="131"/>
       <c r="B711" s="13"/>
       <c r="C711" s="7" t="s">
         <v>21</v>
@@ -24785,7 +24896,7 @@
       <c r="N711" s="13"/>
     </row>
     <row r="712" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A712" s="136"/>
+      <c r="A712" s="132"/>
       <c r="B712" s="13"/>
       <c r="C712" s="7" t="s">
         <v>23</v>
@@ -24829,7 +24940,7 @@
       <c r="N713" s="13"/>
     </row>
     <row r="714" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A714" s="134">
+      <c r="A714" s="130">
         <v>155</v>
       </c>
       <c r="B714" s="13" t="s">
@@ -24859,7 +24970,7 @@
       <c r="N714" s="13"/>
     </row>
     <row r="715" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A715" s="135"/>
+      <c r="A715" s="131"/>
       <c r="B715" s="13"/>
       <c r="C715" s="13"/>
       <c r="D715" s="13"/>
@@ -24883,7 +24994,7 @@
       <c r="N715" s="13"/>
     </row>
     <row r="716" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A716" s="135"/>
+      <c r="A716" s="131"/>
       <c r="B716" s="13"/>
       <c r="C716" s="13"/>
       <c r="D716" s="13"/>
@@ -24907,7 +25018,7 @@
       <c r="N716" s="13"/>
     </row>
     <row r="717" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A717" s="135"/>
+      <c r="A717" s="131"/>
       <c r="B717" s="13"/>
       <c r="C717" s="13"/>
       <c r="D717" s="13"/>
@@ -24931,7 +25042,7 @@
       <c r="N717" s="13"/>
     </row>
     <row r="718" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A718" s="135"/>
+      <c r="A718" s="131"/>
       <c r="B718" s="13"/>
       <c r="C718" s="13"/>
       <c r="D718" s="13" t="s">
@@ -24957,7 +25068,7 @@
       <c r="N718" s="13"/>
     </row>
     <row r="719" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A719" s="135"/>
+      <c r="A719" s="131"/>
       <c r="B719" s="13"/>
       <c r="C719" s="13"/>
       <c r="D719" s="13"/>
@@ -24981,7 +25092,7 @@
       <c r="N719" s="13"/>
     </row>
     <row r="720" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A720" s="135"/>
+      <c r="A720" s="131"/>
       <c r="B720" s="13"/>
       <c r="C720" s="13"/>
       <c r="D720" s="13"/>
@@ -25005,7 +25116,7 @@
       <c r="N720" s="13"/>
     </row>
     <row r="721" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A721" s="135"/>
+      <c r="A721" s="131"/>
       <c r="B721" s="13"/>
       <c r="C721" s="13"/>
       <c r="D721" s="13"/>
@@ -25029,7 +25140,7 @@
       <c r="N721" s="13"/>
     </row>
     <row r="722" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A722" s="135"/>
+      <c r="A722" s="131"/>
       <c r="B722" s="13"/>
       <c r="C722" s="13"/>
       <c r="D722" s="13" t="s">
@@ -25055,7 +25166,7 @@
       <c r="N722" s="13"/>
     </row>
     <row r="723" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A723" s="135"/>
+      <c r="A723" s="131"/>
       <c r="B723" s="13"/>
       <c r="C723" s="13"/>
       <c r="D723" s="13"/>
@@ -25079,7 +25190,7 @@
       <c r="N723" s="13"/>
     </row>
     <row r="724" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A724" s="135"/>
+      <c r="A724" s="131"/>
       <c r="B724" s="13"/>
       <c r="C724" s="13"/>
       <c r="D724" s="13"/>
@@ -25103,7 +25214,7 @@
       <c r="N724" s="13"/>
     </row>
     <row r="725" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A725" s="135"/>
+      <c r="A725" s="131"/>
       <c r="B725" s="13"/>
       <c r="C725" s="13"/>
       <c r="D725" s="13"/>
@@ -25127,7 +25238,7 @@
       <c r="N725" s="13"/>
     </row>
     <row r="726" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A726" s="135"/>
+      <c r="A726" s="131"/>
       <c r="B726" s="13"/>
       <c r="C726" s="13"/>
       <c r="D726" s="13" t="s">
@@ -25153,7 +25264,7 @@
       <c r="N726" s="13"/>
     </row>
     <row r="727" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A727" s="135"/>
+      <c r="A727" s="131"/>
       <c r="B727" s="13"/>
       <c r="C727" s="13"/>
       <c r="D727" s="13"/>
@@ -25177,7 +25288,7 @@
       <c r="N727" s="13"/>
     </row>
     <row r="728" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A728" s="135"/>
+      <c r="A728" s="131"/>
       <c r="B728" s="13"/>
       <c r="C728" s="13"/>
       <c r="D728" s="13"/>
@@ -25201,7 +25312,7 @@
       <c r="N728" s="13"/>
     </row>
     <row r="729" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A729" s="136"/>
+      <c r="A729" s="132"/>
       <c r="B729" s="13"/>
       <c r="C729" s="13"/>
       <c r="D729" s="13"/>
@@ -25241,7 +25352,7 @@
       <c r="N730" s="13"/>
     </row>
     <row r="731" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A731" s="134">
+      <c r="A731" s="130">
         <v>156</v>
       </c>
       <c r="B731" s="13" t="s">
@@ -25271,7 +25382,7 @@
       <c r="N731" s="13"/>
     </row>
     <row r="732" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A732" s="135"/>
+      <c r="A732" s="131"/>
       <c r="B732" s="13"/>
       <c r="C732" s="13"/>
       <c r="D732" s="13"/>
@@ -25295,7 +25406,7 @@
       <c r="N732" s="13"/>
     </row>
     <row r="733" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A733" s="135"/>
+      <c r="A733" s="131"/>
       <c r="B733" s="13"/>
       <c r="C733" s="13"/>
       <c r="D733" s="13"/>
@@ -25319,7 +25430,7 @@
       <c r="N733" s="13"/>
     </row>
     <row r="734" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A734" s="135"/>
+      <c r="A734" s="131"/>
       <c r="B734" s="13"/>
       <c r="C734" s="13"/>
       <c r="D734" s="13"/>
@@ -25343,7 +25454,7 @@
       <c r="N734" s="13"/>
     </row>
     <row r="735" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A735" s="135"/>
+      <c r="A735" s="131"/>
       <c r="B735" s="13"/>
       <c r="C735" s="13"/>
       <c r="D735" s="13"/>
@@ -25367,7 +25478,7 @@
       <c r="N735" s="13"/>
     </row>
     <row r="736" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A736" s="135"/>
+      <c r="A736" s="131"/>
       <c r="B736" s="13"/>
       <c r="C736" s="13"/>
       <c r="D736" s="13"/>
@@ -25391,7 +25502,7 @@
       <c r="N736" s="13"/>
     </row>
     <row r="737" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A737" s="135"/>
+      <c r="A737" s="131"/>
       <c r="B737" s="13"/>
       <c r="C737" s="13"/>
       <c r="D737" s="13"/>
@@ -25415,7 +25526,7 @@
       <c r="N737" s="13"/>
     </row>
     <row r="738" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A738" s="135"/>
+      <c r="A738" s="131"/>
       <c r="B738" s="13"/>
       <c r="C738" s="13"/>
       <c r="D738" s="13" t="s">
@@ -25441,7 +25552,7 @@
       <c r="N738" s="13"/>
     </row>
     <row r="739" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A739" s="135"/>
+      <c r="A739" s="131"/>
       <c r="B739" s="13"/>
       <c r="C739" s="13"/>
       <c r="D739" s="13"/>
@@ -25465,7 +25576,7 @@
       <c r="N739" s="13"/>
     </row>
     <row r="740" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A740" s="135"/>
+      <c r="A740" s="131"/>
       <c r="B740" s="13"/>
       <c r="C740" s="13"/>
       <c r="D740" s="13"/>
@@ -25489,7 +25600,7 @@
       <c r="N740" s="13"/>
     </row>
     <row r="741" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A741" s="135"/>
+      <c r="A741" s="131"/>
       <c r="B741" s="13"/>
       <c r="C741" s="13"/>
       <c r="D741" s="13"/>
@@ -25513,7 +25624,7 @@
       <c r="N741" s="13"/>
     </row>
     <row r="742" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A742" s="135"/>
+      <c r="A742" s="131"/>
       <c r="B742" s="13"/>
       <c r="C742" s="13"/>
       <c r="D742" s="13"/>
@@ -25537,7 +25648,7 @@
       <c r="N742" s="13"/>
     </row>
     <row r="743" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A743" s="135"/>
+      <c r="A743" s="131"/>
       <c r="B743" s="13"/>
       <c r="C743" s="13"/>
       <c r="D743" s="13"/>
@@ -25561,7 +25672,7 @@
       <c r="N743" s="13"/>
     </row>
     <row r="744" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A744" s="135"/>
+      <c r="A744" s="131"/>
       <c r="B744" s="13"/>
       <c r="C744" s="13"/>
       <c r="D744" s="13"/>
@@ -25585,7 +25696,7 @@
       <c r="N744" s="13"/>
     </row>
     <row r="745" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A745" s="135"/>
+      <c r="A745" s="131"/>
       <c r="B745" s="13"/>
       <c r="C745" s="13"/>
       <c r="D745" s="13" t="s">
@@ -25611,7 +25722,7 @@
       <c r="N745" s="13"/>
     </row>
     <row r="746" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A746" s="135"/>
+      <c r="A746" s="131"/>
       <c r="B746" s="13"/>
       <c r="C746" s="13"/>
       <c r="D746" s="13"/>
@@ -25635,7 +25746,7 @@
       <c r="N746" s="13"/>
     </row>
     <row r="747" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A747" s="135"/>
+      <c r="A747" s="131"/>
       <c r="B747" s="13"/>
       <c r="C747" s="13"/>
       <c r="D747" s="13"/>
@@ -25659,7 +25770,7 @@
       <c r="N747" s="13"/>
     </row>
     <row r="748" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A748" s="135"/>
+      <c r="A748" s="131"/>
       <c r="B748" s="13"/>
       <c r="C748" s="13"/>
       <c r="D748" s="13"/>
@@ -25683,7 +25794,7 @@
       <c r="N748" s="13"/>
     </row>
     <row r="749" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A749" s="135"/>
+      <c r="A749" s="131"/>
       <c r="B749" s="13"/>
       <c r="C749" s="13"/>
       <c r="D749" s="13"/>
@@ -25707,7 +25818,7 @@
       <c r="N749" s="13"/>
     </row>
     <row r="750" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A750" s="135"/>
+      <c r="A750" s="131"/>
       <c r="B750" s="13"/>
       <c r="C750" s="13"/>
       <c r="D750" s="13"/>
@@ -25731,7 +25842,7 @@
       <c r="N750" s="13"/>
     </row>
     <row r="751" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A751" s="135"/>
+      <c r="A751" s="131"/>
       <c r="B751" s="13"/>
       <c r="C751" s="13"/>
       <c r="D751" s="13"/>
@@ -25755,7 +25866,7 @@
       <c r="N751" s="13"/>
     </row>
     <row r="752" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A752" s="135"/>
+      <c r="A752" s="131"/>
       <c r="B752" s="13"/>
       <c r="C752" s="13"/>
       <c r="D752" s="13" t="s">
@@ -25781,7 +25892,7 @@
       <c r="N752" s="13"/>
     </row>
     <row r="753" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A753" s="135"/>
+      <c r="A753" s="131"/>
       <c r="B753" s="13"/>
       <c r="C753" s="13"/>
       <c r="D753" s="13"/>
@@ -25805,7 +25916,7 @@
       <c r="N753" s="13"/>
     </row>
     <row r="754" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A754" s="135"/>
+      <c r="A754" s="131"/>
       <c r="B754" s="13"/>
       <c r="C754" s="13"/>
       <c r="D754" s="13"/>
@@ -25829,7 +25940,7 @@
       <c r="N754" s="13"/>
     </row>
     <row r="755" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A755" s="135"/>
+      <c r="A755" s="131"/>
       <c r="B755" s="13"/>
       <c r="C755" s="13"/>
       <c r="D755" s="13"/>
@@ -25853,7 +25964,7 @@
       <c r="N755" s="13"/>
     </row>
     <row r="756" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A756" s="135"/>
+      <c r="A756" s="131"/>
       <c r="B756" s="13"/>
       <c r="C756" s="13"/>
       <c r="D756" s="13"/>
@@ -25877,7 +25988,7 @@
       <c r="N756" s="13"/>
     </row>
     <row r="757" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A757" s="135"/>
+      <c r="A757" s="131"/>
       <c r="B757" s="13"/>
       <c r="C757" s="13"/>
       <c r="D757" s="13"/>
@@ -25901,7 +26012,7 @@
       <c r="N757" s="13"/>
     </row>
     <row r="758" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A758" s="136"/>
+      <c r="A758" s="132"/>
       <c r="B758" s="13"/>
       <c r="C758" s="13"/>
       <c r="D758" s="13"/>
@@ -25941,7 +26052,7 @@
       <c r="N759" s="13"/>
     </row>
     <row r="760" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A760" s="134">
+      <c r="A760" s="130">
         <v>157</v>
       </c>
       <c r="B760" s="13" t="s">
@@ -25971,7 +26082,7 @@
       <c r="N760" s="13"/>
     </row>
     <row r="761" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A761" s="135"/>
+      <c r="A761" s="131"/>
       <c r="B761" s="13"/>
       <c r="C761" s="13"/>
       <c r="D761" s="13"/>
@@ -25995,7 +26106,7 @@
       <c r="N761" s="13"/>
     </row>
     <row r="762" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A762" s="135"/>
+      <c r="A762" s="131"/>
       <c r="B762" s="13"/>
       <c r="C762" s="13"/>
       <c r="D762" s="13"/>
@@ -26019,7 +26130,7 @@
       <c r="N762" s="13"/>
     </row>
     <row r="763" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A763" s="135"/>
+      <c r="A763" s="131"/>
       <c r="B763" s="13"/>
       <c r="C763" s="13"/>
       <c r="D763" s="13"/>
@@ -26043,7 +26154,7 @@
       <c r="N763" s="13"/>
     </row>
     <row r="764" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A764" s="135"/>
+      <c r="A764" s="131"/>
       <c r="B764" s="13"/>
       <c r="C764" s="13"/>
       <c r="D764" s="13"/>
@@ -26067,7 +26178,7 @@
       <c r="N764" s="13"/>
     </row>
     <row r="765" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A765" s="135"/>
+      <c r="A765" s="131"/>
       <c r="B765" s="13"/>
       <c r="C765" s="13"/>
       <c r="D765" s="13" t="s">
@@ -26093,7 +26204,7 @@
       <c r="N765" s="13"/>
     </row>
     <row r="766" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A766" s="135"/>
+      <c r="A766" s="131"/>
       <c r="B766" s="13"/>
       <c r="C766" s="13"/>
       <c r="D766" s="13"/>
@@ -26117,7 +26228,7 @@
       <c r="N766" s="13"/>
     </row>
     <row r="767" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A767" s="135"/>
+      <c r="A767" s="131"/>
       <c r="B767" s="13"/>
       <c r="C767" s="13"/>
       <c r="D767" s="13"/>
@@ -26141,7 +26252,7 @@
       <c r="N767" s="13"/>
     </row>
     <row r="768" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A768" s="135"/>
+      <c r="A768" s="131"/>
       <c r="B768" s="13"/>
       <c r="C768" s="13"/>
       <c r="D768" s="13"/>
@@ -26165,7 +26276,7 @@
       <c r="N768" s="13"/>
     </row>
     <row r="769" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A769" s="136"/>
+      <c r="A769" s="132"/>
       <c r="B769" s="13"/>
       <c r="C769" s="13"/>
       <c r="D769" s="13"/>
@@ -26205,7 +26316,7 @@
       <c r="N770" s="13"/>
     </row>
     <row r="771" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A771" s="134">
+      <c r="A771" s="130">
         <v>158</v>
       </c>
       <c r="B771" s="13" t="s">
@@ -26235,7 +26346,7 @@
       <c r="N771" s="13"/>
     </row>
     <row r="772" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A772" s="135"/>
+      <c r="A772" s="131"/>
       <c r="B772" s="13"/>
       <c r="C772" s="13"/>
       <c r="D772" s="13"/>
@@ -26259,7 +26370,7 @@
       <c r="N772" s="13"/>
     </row>
     <row r="773" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A773" s="135"/>
+      <c r="A773" s="131"/>
       <c r="B773" s="13"/>
       <c r="C773" s="13"/>
       <c r="D773" s="13"/>
@@ -26283,7 +26394,7 @@
       <c r="N773" s="13"/>
     </row>
     <row r="774" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A774" s="135"/>
+      <c r="A774" s="131"/>
       <c r="B774" s="13"/>
       <c r="C774" s="13"/>
       <c r="D774" s="13"/>
@@ -26307,7 +26418,7 @@
       <c r="N774" s="13"/>
     </row>
     <row r="775" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A775" s="135"/>
+      <c r="A775" s="131"/>
       <c r="B775" s="13"/>
       <c r="C775" s="13"/>
       <c r="D775" s="13"/>
@@ -26331,7 +26442,7 @@
       <c r="N775" s="13"/>
     </row>
     <row r="776" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A776" s="135"/>
+      <c r="A776" s="131"/>
       <c r="B776" s="13"/>
       <c r="C776" s="13"/>
       <c r="D776" s="13" t="s">
@@ -26357,7 +26468,7 @@
       <c r="N776" s="13"/>
     </row>
     <row r="777" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A777" s="135"/>
+      <c r="A777" s="131"/>
       <c r="B777" s="13"/>
       <c r="C777" s="13"/>
       <c r="D777" s="13"/>
@@ -26381,7 +26492,7 @@
       <c r="N777" s="13"/>
     </row>
     <row r="778" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A778" s="135"/>
+      <c r="A778" s="131"/>
       <c r="B778" s="13"/>
       <c r="C778" s="13"/>
       <c r="D778" s="13"/>
@@ -26405,7 +26516,7 @@
       <c r="N778" s="13"/>
     </row>
     <row r="779" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A779" s="135"/>
+      <c r="A779" s="131"/>
       <c r="B779" s="13"/>
       <c r="C779" s="13"/>
       <c r="D779" s="13"/>
@@ -26429,7 +26540,7 @@
       <c r="N779" s="13"/>
     </row>
     <row r="780" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A780" s="135"/>
+      <c r="A780" s="131"/>
       <c r="B780" s="13"/>
       <c r="C780" s="13"/>
       <c r="D780" s="13"/>
@@ -26453,7 +26564,7 @@
       <c r="N780" s="13"/>
     </row>
     <row r="781" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A781" s="135"/>
+      <c r="A781" s="131"/>
       <c r="B781" s="13"/>
       <c r="C781" s="13"/>
       <c r="D781" s="13" t="s">
@@ -26479,7 +26590,7 @@
       <c r="N781" s="13"/>
     </row>
     <row r="782" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A782" s="135"/>
+      <c r="A782" s="131"/>
       <c r="B782" s="13"/>
       <c r="C782" s="13"/>
       <c r="D782" s="13"/>
@@ -26503,7 +26614,7 @@
       <c r="N782" s="13"/>
     </row>
     <row r="783" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A783" s="135"/>
+      <c r="A783" s="131"/>
       <c r="B783" s="13"/>
       <c r="C783" s="13"/>
       <c r="D783" s="13"/>
@@ -26527,7 +26638,7 @@
       <c r="N783" s="13"/>
     </row>
     <row r="784" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A784" s="135"/>
+      <c r="A784" s="131"/>
       <c r="B784" s="13"/>
       <c r="C784" s="13"/>
       <c r="D784" s="13"/>
@@ -26551,7 +26662,7 @@
       <c r="N784" s="13"/>
     </row>
     <row r="785" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A785" s="135"/>
+      <c r="A785" s="131"/>
       <c r="B785" s="13"/>
       <c r="C785" s="13"/>
       <c r="D785" s="13"/>
@@ -26575,7 +26686,7 @@
       <c r="N785" s="13"/>
     </row>
     <row r="786" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A786" s="135"/>
+      <c r="A786" s="131"/>
       <c r="B786" s="13"/>
       <c r="C786" s="13"/>
       <c r="D786" s="13" t="s">
@@ -26601,7 +26712,7 @@
       <c r="N786" s="13"/>
     </row>
     <row r="787" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A787" s="135"/>
+      <c r="A787" s="131"/>
       <c r="B787" s="13"/>
       <c r="C787" s="13"/>
       <c r="D787" s="13"/>
@@ -26625,7 +26736,7 @@
       <c r="N787" s="13"/>
     </row>
     <row r="788" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A788" s="135"/>
+      <c r="A788" s="131"/>
       <c r="B788" s="13"/>
       <c r="C788" s="13"/>
       <c r="D788" s="13"/>
@@ -26649,7 +26760,7 @@
       <c r="N788" s="13"/>
     </row>
     <row r="789" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A789" s="135"/>
+      <c r="A789" s="131"/>
       <c r="B789" s="13"/>
       <c r="C789" s="13"/>
       <c r="D789" s="13"/>
@@ -26673,7 +26784,7 @@
       <c r="N789" s="13"/>
     </row>
     <row r="790" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A790" s="136"/>
+      <c r="A790" s="132"/>
       <c r="B790" s="13"/>
       <c r="C790" s="13"/>
       <c r="D790" s="13"/>
@@ -26713,7 +26824,7 @@
       <c r="N791" s="13"/>
     </row>
     <row r="792" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A792" s="134">
+      <c r="A792" s="130">
         <v>159</v>
       </c>
       <c r="B792" s="13" t="s">
@@ -26743,7 +26854,7 @@
       <c r="N792" s="13"/>
     </row>
     <row r="793" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A793" s="135"/>
+      <c r="A793" s="131"/>
       <c r="B793" s="13"/>
       <c r="C793" s="13"/>
       <c r="D793" s="13"/>
@@ -26767,7 +26878,7 @@
       <c r="N793" s="13"/>
     </row>
     <row r="794" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A794" s="135"/>
+      <c r="A794" s="131"/>
       <c r="B794" s="13"/>
       <c r="C794" s="13"/>
       <c r="D794" s="13"/>
@@ -26791,7 +26902,7 @@
       <c r="N794" s="13"/>
     </row>
     <row r="795" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A795" s="135"/>
+      <c r="A795" s="131"/>
       <c r="B795" s="13"/>
       <c r="C795" s="13"/>
       <c r="D795" s="13"/>
@@ -26815,7 +26926,7 @@
       <c r="N795" s="13"/>
     </row>
     <row r="796" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A796" s="135"/>
+      <c r="A796" s="131"/>
       <c r="B796" s="13"/>
       <c r="C796" s="13"/>
       <c r="D796" s="13"/>
@@ -26839,7 +26950,7 @@
       <c r="N796" s="13"/>
     </row>
     <row r="797" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A797" s="135"/>
+      <c r="A797" s="131"/>
       <c r="B797" s="13"/>
       <c r="C797" s="13"/>
       <c r="D797" s="13" t="s">
@@ -26865,7 +26976,7 @@
       <c r="N797" s="13"/>
     </row>
     <row r="798" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A798" s="135"/>
+      <c r="A798" s="131"/>
       <c r="B798" s="13"/>
       <c r="C798" s="13"/>
       <c r="D798" s="13"/>
@@ -26889,7 +27000,7 @@
       <c r="N798" s="13"/>
     </row>
     <row r="799" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A799" s="135"/>
+      <c r="A799" s="131"/>
       <c r="B799" s="13"/>
       <c r="C799" s="13"/>
       <c r="D799" s="13"/>
@@ -26913,7 +27024,7 @@
       <c r="N799" s="13"/>
     </row>
     <row r="800" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A800" s="135"/>
+      <c r="A800" s="131"/>
       <c r="B800" s="13"/>
       <c r="C800" s="13"/>
       <c r="D800" s="13"/>
@@ -26937,7 +27048,7 @@
       <c r="N800" s="13"/>
     </row>
     <row r="801" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A801" s="136"/>
+      <c r="A801" s="132"/>
       <c r="B801" s="13"/>
       <c r="C801" s="13"/>
       <c r="D801" s="13"/>
@@ -26977,7 +27088,7 @@
       <c r="N802" s="13"/>
     </row>
     <row r="803" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A803" s="134">
+      <c r="A803" s="130">
         <v>160</v>
       </c>
       <c r="B803" s="13" t="s">
@@ -27007,7 +27118,7 @@
       <c r="N803" s="13"/>
     </row>
     <row r="804" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A804" s="135"/>
+      <c r="A804" s="131"/>
       <c r="B804" s="13"/>
       <c r="C804" s="13"/>
       <c r="D804" s="13"/>
@@ -27031,7 +27142,7 @@
       <c r="N804" s="13"/>
     </row>
     <row r="805" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A805" s="135"/>
+      <c r="A805" s="131"/>
       <c r="B805" s="13"/>
       <c r="C805" s="13"/>
       <c r="D805" s="13"/>
@@ -27055,7 +27166,7 @@
       <c r="N805" s="13"/>
     </row>
     <row r="806" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A806" s="135"/>
+      <c r="A806" s="131"/>
       <c r="B806" s="13"/>
       <c r="C806" s="13"/>
       <c r="D806" s="13"/>
@@ -27079,7 +27190,7 @@
       <c r="N806" s="13"/>
     </row>
     <row r="807" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A807" s="135"/>
+      <c r="A807" s="131"/>
       <c r="B807" s="13"/>
       <c r="C807" s="13"/>
       <c r="D807" s="13"/>
@@ -27103,7 +27214,7 @@
       <c r="N807" s="13"/>
     </row>
     <row r="808" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A808" s="135"/>
+      <c r="A808" s="131"/>
       <c r="B808" s="13"/>
       <c r="C808" s="13"/>
       <c r="D808" s="13" t="s">
@@ -27129,7 +27240,7 @@
       <c r="N808" s="13"/>
     </row>
     <row r="809" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A809" s="135"/>
+      <c r="A809" s="131"/>
       <c r="B809" s="13"/>
       <c r="C809" s="13"/>
       <c r="D809" s="13"/>
@@ -27153,7 +27264,7 @@
       <c r="N809" s="13"/>
     </row>
     <row r="810" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A810" s="135"/>
+      <c r="A810" s="131"/>
       <c r="B810" s="13"/>
       <c r="C810" s="13"/>
       <c r="D810" s="13"/>
@@ -27177,7 +27288,7 @@
       <c r="N810" s="13"/>
     </row>
     <row r="811" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A811" s="135"/>
+      <c r="A811" s="131"/>
       <c r="B811" s="13"/>
       <c r="C811" s="13"/>
       <c r="D811" s="13"/>
@@ -27201,7 +27312,7 @@
       <c r="N811" s="13"/>
     </row>
     <row r="812" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A812" s="136"/>
+      <c r="A812" s="132"/>
       <c r="B812" s="13"/>
       <c r="C812" s="13"/>
       <c r="D812" s="13"/>
@@ -27241,7 +27352,7 @@
       <c r="N813" s="13"/>
     </row>
     <row r="814" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A814" s="134">
+      <c r="A814" s="130">
         <v>161</v>
       </c>
       <c r="B814" s="13" t="s">
@@ -27271,7 +27382,7 @@
       <c r="N814" s="13"/>
     </row>
     <row r="815" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A815" s="135"/>
+      <c r="A815" s="131"/>
       <c r="B815" s="13"/>
       <c r="C815" s="13"/>
       <c r="D815" s="13"/>
@@ -27295,7 +27406,7 @@
       <c r="N815" s="13"/>
     </row>
     <row r="816" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A816" s="135"/>
+      <c r="A816" s="131"/>
       <c r="B816" s="13"/>
       <c r="C816" s="13"/>
       <c r="D816" s="13"/>
@@ -27319,7 +27430,7 @@
       <c r="N816" s="13"/>
     </row>
     <row r="817" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A817" s="135"/>
+      <c r="A817" s="131"/>
       <c r="B817" s="13"/>
       <c r="C817" s="13"/>
       <c r="D817" s="13"/>
@@ -27343,7 +27454,7 @@
       <c r="N817" s="13"/>
     </row>
     <row r="818" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A818" s="135"/>
+      <c r="A818" s="131"/>
       <c r="B818" s="13"/>
       <c r="C818" s="13"/>
       <c r="D818" s="13"/>
@@ -27367,7 +27478,7 @@
       <c r="N818" s="13"/>
     </row>
     <row r="819" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A819" s="135"/>
+      <c r="A819" s="131"/>
       <c r="B819" s="13"/>
       <c r="C819" s="13"/>
       <c r="D819" s="13" t="s">
@@ -27393,7 +27504,7 @@
       <c r="N819" s="13"/>
     </row>
     <row r="820" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A820" s="135"/>
+      <c r="A820" s="131"/>
       <c r="B820" s="13"/>
       <c r="C820" s="13"/>
       <c r="D820" s="13"/>
@@ -27417,7 +27528,7 @@
       <c r="N820" s="13"/>
     </row>
     <row r="821" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A821" s="135"/>
+      <c r="A821" s="131"/>
       <c r="B821" s="13"/>
       <c r="C821" s="13"/>
       <c r="D821" s="13"/>
@@ -27441,7 +27552,7 @@
       <c r="N821" s="13"/>
     </row>
     <row r="822" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A822" s="135"/>
+      <c r="A822" s="131"/>
       <c r="B822" s="13"/>
       <c r="C822" s="13"/>
       <c r="D822" s="13"/>
@@ -27465,7 +27576,7 @@
       <c r="N822" s="13"/>
     </row>
     <row r="823" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A823" s="136"/>
+      <c r="A823" s="132"/>
       <c r="B823" s="13"/>
       <c r="C823" s="13"/>
       <c r="D823" s="13"/>
@@ -27505,7 +27616,7 @@
       <c r="N824" s="13"/>
     </row>
     <row r="825" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A825" s="134">
+      <c r="A825" s="130">
         <v>162</v>
       </c>
       <c r="B825" s="13" t="s">
@@ -27535,7 +27646,7 @@
       <c r="N825" s="13"/>
     </row>
     <row r="826" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A826" s="135"/>
+      <c r="A826" s="131"/>
       <c r="B826" s="13"/>
       <c r="C826" s="13"/>
       <c r="D826" s="13"/>
@@ -27559,7 +27670,7 @@
       <c r="N826" s="13"/>
     </row>
     <row r="827" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A827" s="135"/>
+      <c r="A827" s="131"/>
       <c r="B827" s="13"/>
       <c r="C827" s="13"/>
       <c r="D827" s="13"/>
@@ -27583,7 +27694,7 @@
       <c r="N827" s="13"/>
     </row>
     <row r="828" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A828" s="135"/>
+      <c r="A828" s="131"/>
       <c r="B828" s="13"/>
       <c r="C828" s="13"/>
       <c r="D828" s="13"/>
@@ -27607,7 +27718,7 @@
       <c r="N828" s="13"/>
     </row>
     <row r="829" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A829" s="135"/>
+      <c r="A829" s="131"/>
       <c r="B829" s="13"/>
       <c r="C829" s="13"/>
       <c r="D829" s="13"/>
@@ -27631,7 +27742,7 @@
       <c r="N829" s="13"/>
     </row>
     <row r="830" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A830" s="135"/>
+      <c r="A830" s="131"/>
       <c r="B830" s="13"/>
       <c r="C830" s="13"/>
       <c r="D830" s="13" t="s">
@@ -27657,7 +27768,7 @@
       <c r="N830" s="13"/>
     </row>
     <row r="831" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A831" s="135"/>
+      <c r="A831" s="131"/>
       <c r="B831" s="13"/>
       <c r="C831" s="13"/>
       <c r="D831" s="13"/>
@@ -27681,7 +27792,7 @@
       <c r="N831" s="13"/>
     </row>
     <row r="832" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A832" s="135"/>
+      <c r="A832" s="131"/>
       <c r="B832" s="13"/>
       <c r="C832" s="13"/>
       <c r="D832" s="13"/>
@@ -27705,7 +27816,7 @@
       <c r="N832" s="13"/>
     </row>
     <row r="833" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A833" s="135"/>
+      <c r="A833" s="131"/>
       <c r="B833" s="13"/>
       <c r="C833" s="13"/>
       <c r="D833" s="13"/>
@@ -27729,7 +27840,7 @@
       <c r="N833" s="13"/>
     </row>
     <row r="834" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A834" s="136"/>
+      <c r="A834" s="132"/>
       <c r="B834" s="13"/>
       <c r="C834" s="13"/>
       <c r="D834" s="13"/>
@@ -27769,7 +27880,7 @@
       <c r="N835" s="13"/>
     </row>
     <row r="836" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A836" s="134">
+      <c r="A836" s="130">
         <v>163</v>
       </c>
       <c r="B836" s="13" t="s">
@@ -27799,7 +27910,7 @@
       <c r="N836" s="13"/>
     </row>
     <row r="837" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A837" s="135"/>
+      <c r="A837" s="131"/>
       <c r="B837" s="13"/>
       <c r="C837" s="13"/>
       <c r="D837" s="13"/>
@@ -27823,7 +27934,7 @@
       <c r="N837" s="13"/>
     </row>
     <row r="838" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A838" s="135"/>
+      <c r="A838" s="131"/>
       <c r="B838" s="13"/>
       <c r="C838" s="13"/>
       <c r="D838" s="13"/>
@@ -27847,7 +27958,7 @@
       <c r="N838" s="13"/>
     </row>
     <row r="839" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A839" s="135"/>
+      <c r="A839" s="131"/>
       <c r="B839" s="13"/>
       <c r="C839" s="13"/>
       <c r="D839" s="13"/>
@@ -27871,7 +27982,7 @@
       <c r="N839" s="13"/>
     </row>
     <row r="840" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A840" s="135"/>
+      <c r="A840" s="131"/>
       <c r="B840" s="13"/>
       <c r="C840" s="13"/>
       <c r="D840" s="13"/>
@@ -27895,7 +28006,7 @@
       <c r="N840" s="13"/>
     </row>
     <row r="841" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A841" s="135"/>
+      <c r="A841" s="131"/>
       <c r="B841" s="13"/>
       <c r="C841" s="13"/>
       <c r="D841" s="13" t="s">
@@ -27921,7 +28032,7 @@
       <c r="N841" s="13"/>
     </row>
     <row r="842" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A842" s="135"/>
+      <c r="A842" s="131"/>
       <c r="B842" s="13"/>
       <c r="C842" s="13"/>
       <c r="D842" s="13"/>
@@ -27945,7 +28056,7 @@
       <c r="N842" s="13"/>
     </row>
     <row r="843" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A843" s="135"/>
+      <c r="A843" s="131"/>
       <c r="B843" s="13"/>
       <c r="C843" s="13"/>
       <c r="D843" s="13"/>
@@ -27969,7 +28080,7 @@
       <c r="N843" s="13"/>
     </row>
     <row r="844" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A844" s="135"/>
+      <c r="A844" s="131"/>
       <c r="B844" s="13"/>
       <c r="C844" s="13"/>
       <c r="D844" s="13"/>
@@ -27993,7 +28104,7 @@
       <c r="N844" s="13"/>
     </row>
     <row r="845" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A845" s="136"/>
+      <c r="A845" s="132"/>
       <c r="B845" s="13"/>
       <c r="C845" s="13"/>
       <c r="D845" s="13"/>
@@ -28033,7 +28144,7 @@
       <c r="N846" s="13"/>
     </row>
     <row r="847" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A847" s="134">
+      <c r="A847" s="130">
         <v>164</v>
       </c>
       <c r="B847" s="13" t="s">
@@ -28063,7 +28174,7 @@
       <c r="N847" s="13"/>
     </row>
     <row r="848" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A848" s="135"/>
+      <c r="A848" s="131"/>
       <c r="B848" s="13"/>
       <c r="C848" s="13"/>
       <c r="D848" s="13"/>
@@ -28087,7 +28198,7 @@
       <c r="N848" s="13"/>
     </row>
     <row r="849" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A849" s="135"/>
+      <c r="A849" s="131"/>
       <c r="B849" s="13"/>
       <c r="C849" s="13"/>
       <c r="D849" s="13"/>
@@ -28111,7 +28222,7 @@
       <c r="N849" s="13"/>
     </row>
     <row r="850" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A850" s="135"/>
+      <c r="A850" s="131"/>
       <c r="B850" s="13"/>
       <c r="C850" s="13"/>
       <c r="D850" s="13"/>
@@ -28135,7 +28246,7 @@
       <c r="N850" s="13"/>
     </row>
     <row r="851" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A851" s="135"/>
+      <c r="A851" s="131"/>
       <c r="B851" s="13"/>
       <c r="C851" s="13"/>
       <c r="D851" s="13"/>
@@ -28159,7 +28270,7 @@
       <c r="N851" s="13"/>
     </row>
     <row r="852" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A852" s="135"/>
+      <c r="A852" s="131"/>
       <c r="B852" s="13"/>
       <c r="C852" s="13"/>
       <c r="D852" s="13" t="s">
@@ -28185,7 +28296,7 @@
       <c r="N852" s="13"/>
     </row>
     <row r="853" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A853" s="135"/>
+      <c r="A853" s="131"/>
       <c r="B853" s="13"/>
       <c r="C853" s="13"/>
       <c r="D853" s="13"/>
@@ -28209,7 +28320,7 @@
       <c r="N853" s="13"/>
     </row>
     <row r="854" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A854" s="135"/>
+      <c r="A854" s="131"/>
       <c r="B854" s="13"/>
       <c r="C854" s="13"/>
       <c r="D854" s="13"/>
@@ -28233,7 +28344,7 @@
       <c r="N854" s="13"/>
     </row>
     <row r="855" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A855" s="135"/>
+      <c r="A855" s="131"/>
       <c r="B855" s="13"/>
       <c r="C855" s="13"/>
       <c r="D855" s="13"/>
@@ -28257,7 +28368,7 @@
       <c r="N855" s="13"/>
     </row>
     <row r="856" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A856" s="136"/>
+      <c r="A856" s="132"/>
       <c r="B856" s="13"/>
       <c r="C856" s="13"/>
       <c r="D856" s="13"/>
@@ -28297,7 +28408,7 @@
       <c r="N857" s="13"/>
     </row>
     <row r="858" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A858" s="134">
+      <c r="A858" s="130">
         <v>165</v>
       </c>
       <c r="B858" s="13" t="s">
@@ -28327,7 +28438,7 @@
       <c r="N858" s="13"/>
     </row>
     <row r="859" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A859" s="135"/>
+      <c r="A859" s="131"/>
       <c r="B859" s="13"/>
       <c r="C859" s="13"/>
       <c r="D859" s="13"/>
@@ -28351,7 +28462,7 @@
       <c r="N859" s="13"/>
     </row>
     <row r="860" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A860" s="135"/>
+      <c r="A860" s="131"/>
       <c r="B860" s="13"/>
       <c r="C860" s="13"/>
       <c r="D860" s="13" t="s">
@@ -28377,7 +28488,7 @@
       <c r="N860" s="13"/>
     </row>
     <row r="861" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A861" s="135"/>
+      <c r="A861" s="131"/>
       <c r="B861" s="13"/>
       <c r="C861" s="13"/>
       <c r="D861" s="13"/>
@@ -28401,7 +28512,7 @@
       <c r="N861" s="13"/>
     </row>
     <row r="862" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A862" s="135"/>
+      <c r="A862" s="131"/>
       <c r="B862" s="13"/>
       <c r="C862" s="13"/>
       <c r="D862" s="13" t="s">
@@ -28427,7 +28538,7 @@
       <c r="N862" s="13"/>
     </row>
     <row r="863" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A863" s="135"/>
+      <c r="A863" s="131"/>
       <c r="B863" s="13"/>
       <c r="C863" s="13"/>
       <c r="D863" s="13"/>
@@ -28451,7 +28562,7 @@
       <c r="N863" s="13"/>
     </row>
     <row r="864" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A864" s="135"/>
+      <c r="A864" s="131"/>
       <c r="B864" s="13"/>
       <c r="C864" s="13"/>
       <c r="D864" s="13" t="s">
@@ -28477,7 +28588,7 @@
       <c r="N864" s="13"/>
     </row>
     <row r="865" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A865" s="135"/>
+      <c r="A865" s="131"/>
       <c r="B865" s="13"/>
       <c r="C865" s="13"/>
       <c r="D865" s="13"/>
@@ -28501,7 +28612,7 @@
       <c r="N865" s="13"/>
     </row>
     <row r="866" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A866" s="135"/>
+      <c r="A866" s="131"/>
       <c r="B866" s="13"/>
       <c r="C866" s="13"/>
       <c r="D866" s="13" t="s">
@@ -28527,7 +28638,7 @@
       <c r="N866" s="13"/>
     </row>
     <row r="867" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A867" s="135"/>
+      <c r="A867" s="131"/>
       <c r="B867" s="13"/>
       <c r="C867" s="13"/>
       <c r="D867" s="13"/>
@@ -28551,7 +28662,7 @@
       <c r="N867" s="13"/>
     </row>
     <row r="868" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A868" s="135"/>
+      <c r="A868" s="131"/>
       <c r="B868" s="13"/>
       <c r="C868" s="13"/>
       <c r="D868" s="13" t="s">
@@ -28577,7 +28688,7 @@
       <c r="N868" s="13"/>
     </row>
     <row r="869" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A869" s="135"/>
+      <c r="A869" s="131"/>
       <c r="B869" s="13"/>
       <c r="C869" s="13"/>
       <c r="D869" s="13"/>
@@ -28601,7 +28712,7 @@
       <c r="N869" s="13"/>
     </row>
     <row r="870" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A870" s="135"/>
+      <c r="A870" s="131"/>
       <c r="B870" s="13"/>
       <c r="C870" s="13"/>
       <c r="D870" s="13" t="s">
@@ -28627,7 +28738,7 @@
       <c r="N870" s="13"/>
     </row>
     <row r="871" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A871" s="135"/>
+      <c r="A871" s="131"/>
       <c r="B871" s="13"/>
       <c r="C871" s="13"/>
       <c r="D871" s="13"/>
@@ -28651,7 +28762,7 @@
       <c r="N871" s="13"/>
     </row>
     <row r="872" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A872" s="135"/>
+      <c r="A872" s="131"/>
       <c r="B872" s="13"/>
       <c r="C872" s="13"/>
       <c r="D872" s="13" t="s">
@@ -28677,7 +28788,7 @@
       <c r="N872" s="13"/>
     </row>
     <row r="873" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A873" s="136"/>
+      <c r="A873" s="132"/>
       <c r="B873" s="13"/>
       <c r="C873" s="13"/>
       <c r="D873" s="13"/>
@@ -28717,7 +28828,7 @@
       <c r="N874" s="13"/>
     </row>
     <row r="875" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A875" s="134">
+      <c r="A875" s="130">
         <v>166</v>
       </c>
       <c r="B875" s="13" t="s">
@@ -28747,7 +28858,7 @@
       <c r="N875" s="13"/>
     </row>
     <row r="876" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A876" s="135"/>
+      <c r="A876" s="131"/>
       <c r="B876" s="13"/>
       <c r="C876" s="13"/>
       <c r="D876" s="13"/>
@@ -28771,7 +28882,7 @@
       <c r="N876" s="13"/>
     </row>
     <row r="877" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A877" s="135"/>
+      <c r="A877" s="131"/>
       <c r="B877" s="13"/>
       <c r="C877" s="13"/>
       <c r="D877" s="13"/>
@@ -28795,7 +28906,7 @@
       <c r="N877" s="13"/>
     </row>
     <row r="878" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A878" s="135"/>
+      <c r="A878" s="131"/>
       <c r="B878" s="13"/>
       <c r="C878" s="13"/>
       <c r="D878" s="13"/>
@@ -28819,7 +28930,7 @@
       <c r="N878" s="13"/>
     </row>
     <row r="879" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A879" s="135"/>
+      <c r="A879" s="131"/>
       <c r="B879" s="13"/>
       <c r="C879" s="13"/>
       <c r="D879" s="13"/>
@@ -28843,7 +28954,7 @@
       <c r="N879" s="13"/>
     </row>
     <row r="880" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A880" s="135"/>
+      <c r="A880" s="131"/>
       <c r="B880" s="13"/>
       <c r="C880" s="13"/>
       <c r="D880" s="13" t="s">
@@ -28869,7 +28980,7 @@
       <c r="N880" s="13"/>
     </row>
     <row r="881" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A881" s="135"/>
+      <c r="A881" s="131"/>
       <c r="B881" s="13"/>
       <c r="C881" s="13"/>
       <c r="D881" s="13"/>
@@ -28893,7 +29004,7 @@
       <c r="N881" s="13"/>
     </row>
     <row r="882" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A882" s="135"/>
+      <c r="A882" s="131"/>
       <c r="B882" s="13"/>
       <c r="C882" s="13"/>
       <c r="D882" s="13"/>
@@ -28917,7 +29028,7 @@
       <c r="N882" s="13"/>
     </row>
     <row r="883" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A883" s="135"/>
+      <c r="A883" s="131"/>
       <c r="B883" s="13"/>
       <c r="C883" s="13"/>
       <c r="D883" s="13"/>
@@ -28941,7 +29052,7 @@
       <c r="N883" s="13"/>
     </row>
     <row r="884" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A884" s="135"/>
+      <c r="A884" s="131"/>
       <c r="B884" s="13"/>
       <c r="C884" s="13"/>
       <c r="D884" s="13"/>
@@ -28965,7 +29076,7 @@
       <c r="N884" s="13"/>
     </row>
     <row r="885" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A885" s="135"/>
+      <c r="A885" s="131"/>
       <c r="B885" s="13"/>
       <c r="C885" s="13"/>
       <c r="D885" s="13" t="s">
@@ -28991,7 +29102,7 @@
       <c r="N885" s="13"/>
     </row>
     <row r="886" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A886" s="135"/>
+      <c r="A886" s="131"/>
       <c r="B886" s="13"/>
       <c r="C886" s="13"/>
       <c r="D886" s="13"/>
@@ -29015,7 +29126,7 @@
       <c r="N886" s="13"/>
     </row>
     <row r="887" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A887" s="135"/>
+      <c r="A887" s="131"/>
       <c r="B887" s="13"/>
       <c r="C887" s="13"/>
       <c r="D887" s="13"/>
@@ -29039,7 +29150,7 @@
       <c r="N887" s="13"/>
     </row>
     <row r="888" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A888" s="135"/>
+      <c r="A888" s="131"/>
       <c r="B888" s="13"/>
       <c r="C888" s="13"/>
       <c r="D888" s="13"/>
@@ -29063,7 +29174,7 @@
       <c r="N888" s="13"/>
     </row>
     <row r="889" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A889" s="135"/>
+      <c r="A889" s="131"/>
       <c r="B889" s="13"/>
       <c r="C889" s="13"/>
       <c r="D889" s="13"/>
@@ -29087,7 +29198,7 @@
       <c r="N889" s="13"/>
     </row>
     <row r="890" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A890" s="135"/>
+      <c r="A890" s="131"/>
       <c r="B890" s="13"/>
       <c r="C890" s="13"/>
       <c r="D890" s="13" t="s">
@@ -29113,7 +29224,7 @@
       <c r="N890" s="13"/>
     </row>
     <row r="891" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A891" s="135"/>
+      <c r="A891" s="131"/>
       <c r="B891" s="13"/>
       <c r="C891" s="13"/>
       <c r="D891" s="13"/>
@@ -29137,7 +29248,7 @@
       <c r="N891" s="13"/>
     </row>
     <row r="892" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A892" s="135"/>
+      <c r="A892" s="131"/>
       <c r="B892" s="13"/>
       <c r="C892" s="13"/>
       <c r="D892" s="13"/>
@@ -29161,7 +29272,7 @@
       <c r="N892" s="13"/>
     </row>
     <row r="893" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A893" s="135"/>
+      <c r="A893" s="131"/>
       <c r="B893" s="13"/>
       <c r="C893" s="13"/>
       <c r="D893" s="13"/>
@@ -29185,7 +29296,7 @@
       <c r="N893" s="13"/>
     </row>
     <row r="894" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A894" s="135"/>
+      <c r="A894" s="131"/>
       <c r="B894" s="13"/>
       <c r="C894" s="13"/>
       <c r="D894" s="13"/>
@@ -29209,7 +29320,7 @@
       <c r="N894" s="13"/>
     </row>
     <row r="895" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A895" s="135"/>
+      <c r="A895" s="131"/>
       <c r="B895" s="13"/>
       <c r="C895" s="13"/>
       <c r="D895" s="13" t="s">
@@ -29235,7 +29346,7 @@
       <c r="N895" s="13"/>
     </row>
     <row r="896" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A896" s="135"/>
+      <c r="A896" s="131"/>
       <c r="B896" s="13"/>
       <c r="C896" s="13"/>
       <c r="D896" s="13"/>
@@ -29259,7 +29370,7 @@
       <c r="N896" s="13"/>
     </row>
     <row r="897" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A897" s="135"/>
+      <c r="A897" s="131"/>
       <c r="B897" s="13"/>
       <c r="C897" s="13"/>
       <c r="D897" s="13"/>
@@ -29283,7 +29394,7 @@
       <c r="N897" s="13"/>
     </row>
     <row r="898" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A898" s="135"/>
+      <c r="A898" s="131"/>
       <c r="B898" s="13"/>
       <c r="C898" s="13"/>
       <c r="D898" s="13"/>
@@ -29307,7 +29418,7 @@
       <c r="N898" s="13"/>
     </row>
     <row r="899" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A899" s="136"/>
+      <c r="A899" s="132"/>
       <c r="B899" s="13"/>
       <c r="C899" s="13"/>
       <c r="D899" s="13"/>
@@ -29347,7 +29458,7 @@
       <c r="N900" s="13"/>
     </row>
     <row r="901" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A901" s="134">
+      <c r="A901" s="130">
         <v>167</v>
       </c>
       <c r="B901" s="13" t="s">
@@ -29377,7 +29488,7 @@
       <c r="N901" s="13"/>
     </row>
     <row r="902" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A902" s="135"/>
+      <c r="A902" s="131"/>
       <c r="B902" s="13"/>
       <c r="C902" s="13"/>
       <c r="D902" s="13"/>
@@ -29401,7 +29512,7 @@
       <c r="N902" s="13"/>
     </row>
     <row r="903" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A903" s="135"/>
+      <c r="A903" s="131"/>
       <c r="B903" s="13"/>
       <c r="C903" s="13"/>
       <c r="D903" s="13"/>
@@ -29425,7 +29536,7 @@
       <c r="N903" s="13"/>
     </row>
     <row r="904" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A904" s="135"/>
+      <c r="A904" s="131"/>
       <c r="B904" s="13"/>
       <c r="C904" s="13"/>
       <c r="D904" s="13"/>
@@ -29449,7 +29560,7 @@
       <c r="N904" s="13"/>
     </row>
     <row r="905" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A905" s="135"/>
+      <c r="A905" s="131"/>
       <c r="B905" s="13"/>
       <c r="C905" s="13"/>
       <c r="D905" s="13"/>
@@ -29473,7 +29584,7 @@
       <c r="N905" s="13"/>
     </row>
     <row r="906" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A906" s="135"/>
+      <c r="A906" s="131"/>
       <c r="B906" s="13"/>
       <c r="C906" s="13"/>
       <c r="D906" s="13" t="s">
@@ -29499,7 +29610,7 @@
       <c r="N906" s="13"/>
     </row>
     <row r="907" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A907" s="135"/>
+      <c r="A907" s="131"/>
       <c r="B907" s="13"/>
       <c r="C907" s="13"/>
       <c r="D907" s="13"/>
@@ -29523,7 +29634,7 @@
       <c r="N907" s="13"/>
     </row>
     <row r="908" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A908" s="135"/>
+      <c r="A908" s="131"/>
       <c r="B908" s="13"/>
       <c r="C908" s="13"/>
       <c r="D908" s="13"/>
@@ -29547,7 +29658,7 @@
       <c r="N908" s="13"/>
     </row>
     <row r="909" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A909" s="135"/>
+      <c r="A909" s="131"/>
       <c r="B909" s="13"/>
       <c r="C909" s="13"/>
       <c r="D909" s="13"/>
@@ -29571,7 +29682,7 @@
       <c r="N909" s="13"/>
     </row>
     <row r="910" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A910" s="135"/>
+      <c r="A910" s="131"/>
       <c r="B910" s="13"/>
       <c r="C910" s="13"/>
       <c r="D910" s="13"/>
@@ -29595,7 +29706,7 @@
       <c r="N910" s="13"/>
     </row>
     <row r="911" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A911" s="135"/>
+      <c r="A911" s="131"/>
       <c r="B911" s="13"/>
       <c r="C911" s="13"/>
       <c r="D911" s="13" t="s">
@@ -29621,7 +29732,7 @@
       <c r="N911" s="13"/>
     </row>
     <row r="912" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A912" s="135"/>
+      <c r="A912" s="131"/>
       <c r="B912" s="13"/>
       <c r="C912" s="13"/>
       <c r="D912" s="13"/>
@@ -29645,7 +29756,7 @@
       <c r="N912" s="13"/>
     </row>
     <row r="913" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A913" s="135"/>
+      <c r="A913" s="131"/>
       <c r="B913" s="13"/>
       <c r="C913" s="13"/>
       <c r="D913" s="13"/>
@@ -29669,7 +29780,7 @@
       <c r="N913" s="13"/>
     </row>
     <row r="914" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A914" s="135"/>
+      <c r="A914" s="131"/>
       <c r="B914" s="13"/>
       <c r="C914" s="13"/>
       <c r="D914" s="13"/>
@@ -29693,7 +29804,7 @@
       <c r="N914" s="13"/>
     </row>
     <row r="915" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A915" s="135"/>
+      <c r="A915" s="131"/>
       <c r="B915" s="13"/>
       <c r="C915" s="13"/>
       <c r="D915" s="13"/>
@@ -29717,7 +29828,7 @@
       <c r="N915" s="13"/>
     </row>
     <row r="916" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A916" s="135"/>
+      <c r="A916" s="131"/>
       <c r="B916" s="13"/>
       <c r="C916" s="13"/>
       <c r="D916" s="13" t="s">
@@ -29743,7 +29854,7 @@
       <c r="N916" s="13"/>
     </row>
     <row r="917" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A917" s="135"/>
+      <c r="A917" s="131"/>
       <c r="B917" s="13"/>
       <c r="C917" s="13"/>
       <c r="D917" s="13"/>
@@ -29767,7 +29878,7 @@
       <c r="N917" s="13"/>
     </row>
     <row r="918" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A918" s="135"/>
+      <c r="A918" s="131"/>
       <c r="B918" s="13"/>
       <c r="C918" s="13"/>
       <c r="D918" s="13"/>
@@ -29791,7 +29902,7 @@
       <c r="N918" s="13"/>
     </row>
     <row r="919" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A919" s="135"/>
+      <c r="A919" s="131"/>
       <c r="B919" s="13"/>
       <c r="C919" s="13"/>
       <c r="D919" s="13"/>
@@ -29815,7 +29926,7 @@
       <c r="N919" s="13"/>
     </row>
     <row r="920" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A920" s="135"/>
+      <c r="A920" s="131"/>
       <c r="B920" s="13"/>
       <c r="C920" s="13"/>
       <c r="D920" s="13"/>
@@ -29839,7 +29950,7 @@
       <c r="N920" s="13"/>
     </row>
     <row r="921" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A921" s="135"/>
+      <c r="A921" s="131"/>
       <c r="B921" s="13"/>
       <c r="C921" s="13"/>
       <c r="D921" s="13" t="s">
@@ -29865,7 +29976,7 @@
       <c r="N921" s="13"/>
     </row>
     <row r="922" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A922" s="135"/>
+      <c r="A922" s="131"/>
       <c r="B922" s="13"/>
       <c r="C922" s="13"/>
       <c r="D922" s="13"/>
@@ -29889,7 +30000,7 @@
       <c r="N922" s="13"/>
     </row>
     <row r="923" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A923" s="135"/>
+      <c r="A923" s="131"/>
       <c r="B923" s="13"/>
       <c r="C923" s="13"/>
       <c r="D923" s="13"/>
@@ -29913,7 +30024,7 @@
       <c r="N923" s="13"/>
     </row>
     <row r="924" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A924" s="135"/>
+      <c r="A924" s="131"/>
       <c r="B924" s="13"/>
       <c r="C924" s="13"/>
       <c r="D924" s="13"/>
@@ -29937,7 +30048,7 @@
       <c r="N924" s="13"/>
     </row>
     <row r="925" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A925" s="136"/>
+      <c r="A925" s="132"/>
       <c r="B925" s="13"/>
       <c r="C925" s="13"/>
       <c r="D925" s="13"/>
@@ -29977,7 +30088,7 @@
       <c r="N926" s="13"/>
     </row>
     <row r="927" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A927" s="134">
+      <c r="A927" s="130">
         <v>168</v>
       </c>
       <c r="B927" s="13" t="s">
@@ -30007,7 +30118,7 @@
       <c r="N927" s="13"/>
     </row>
     <row r="928" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A928" s="136"/>
+      <c r="A928" s="132"/>
       <c r="B928" s="13"/>
       <c r="C928" s="13"/>
       <c r="D928" s="13"/>
@@ -30139,7 +30250,7 @@
       <c r="N933" s="13"/>
     </row>
     <row r="934" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A934" s="134">
+      <c r="A934" s="130">
         <v>171</v>
       </c>
       <c r="B934" s="13" t="s">
@@ -30169,7 +30280,7 @@
       <c r="N934" s="13"/>
     </row>
     <row r="935" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A935" s="136"/>
+      <c r="A935" s="132"/>
       <c r="B935" s="13"/>
       <c r="C935" s="13"/>
       <c r="D935" s="13"/>
@@ -30209,7 +30320,7 @@
       <c r="N936" s="13"/>
     </row>
     <row r="937" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A937" s="134">
+      <c r="A937" s="130">
         <v>172</v>
       </c>
       <c r="B937" s="13" t="s">
@@ -30239,7 +30350,7 @@
       <c r="N937" s="13"/>
     </row>
     <row r="938" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A938" s="135"/>
+      <c r="A938" s="131"/>
       <c r="B938" s="13"/>
       <c r="C938" s="13"/>
       <c r="D938" s="13"/>
@@ -30263,7 +30374,7 @@
       <c r="N938" s="13"/>
     </row>
     <row r="939" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A939" s="135"/>
+      <c r="A939" s="131"/>
       <c r="B939" s="13"/>
       <c r="C939" s="13"/>
       <c r="D939" s="13"/>
@@ -30287,7 +30398,7 @@
       <c r="N939" s="13"/>
     </row>
     <row r="940" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A940" s="135"/>
+      <c r="A940" s="131"/>
       <c r="B940" s="13"/>
       <c r="C940" s="13"/>
       <c r="D940" s="13"/>
@@ -30311,7 +30422,7 @@
       <c r="N940" s="13"/>
     </row>
     <row r="941" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A941" s="135"/>
+      <c r="A941" s="131"/>
       <c r="B941" s="13"/>
       <c r="C941" s="13"/>
       <c r="D941" s="13"/>
@@ -30335,7 +30446,7 @@
       <c r="N941" s="13"/>
     </row>
     <row r="942" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A942" s="135"/>
+      <c r="A942" s="131"/>
       <c r="B942" s="13"/>
       <c r="C942" s="13"/>
       <c r="D942" s="13" t="s">
@@ -30361,7 +30472,7 @@
       <c r="N942" s="13"/>
     </row>
     <row r="943" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A943" s="135"/>
+      <c r="A943" s="131"/>
       <c r="B943" s="13"/>
       <c r="C943" s="13"/>
       <c r="D943" s="13"/>
@@ -30385,7 +30496,7 @@
       <c r="N943" s="13"/>
     </row>
     <row r="944" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A944" s="135"/>
+      <c r="A944" s="131"/>
       <c r="B944" s="13"/>
       <c r="C944" s="13"/>
       <c r="D944" s="13"/>
@@ -30409,7 +30520,7 @@
       <c r="N944" s="13"/>
     </row>
     <row r="945" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A945" s="135"/>
+      <c r="A945" s="131"/>
       <c r="B945" s="13"/>
       <c r="C945" s="13"/>
       <c r="D945" s="13"/>
@@ -30433,7 +30544,7 @@
       <c r="N945" s="13"/>
     </row>
     <row r="946" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A946" s="135"/>
+      <c r="A946" s="131"/>
       <c r="B946" s="13"/>
       <c r="C946" s="13"/>
       <c r="D946" s="13"/>
@@ -30457,7 +30568,7 @@
       <c r="N946" s="13"/>
     </row>
     <row r="947" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A947" s="135"/>
+      <c r="A947" s="131"/>
       <c r="B947" s="13"/>
       <c r="C947" s="13"/>
       <c r="D947" s="13" t="s">
@@ -30483,7 +30594,7 @@
       <c r="N947" s="13"/>
     </row>
     <row r="948" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A948" s="135"/>
+      <c r="A948" s="131"/>
       <c r="B948" s="13"/>
       <c r="C948" s="13"/>
       <c r="D948" s="13"/>
@@ -30507,7 +30618,7 @@
       <c r="N948" s="13"/>
     </row>
     <row r="949" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A949" s="135"/>
+      <c r="A949" s="131"/>
       <c r="B949" s="13"/>
       <c r="C949" s="13"/>
       <c r="D949" s="13"/>
@@ -30531,7 +30642,7 @@
       <c r="N949" s="13"/>
     </row>
     <row r="950" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A950" s="135"/>
+      <c r="A950" s="131"/>
       <c r="B950" s="13"/>
       <c r="C950" s="13"/>
       <c r="D950" s="13"/>
@@ -30555,7 +30666,7 @@
       <c r="N950" s="13"/>
     </row>
     <row r="951" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A951" s="135"/>
+      <c r="A951" s="131"/>
       <c r="B951" s="13"/>
       <c r="C951" s="13"/>
       <c r="D951" s="13"/>
@@ -30579,7 +30690,7 @@
       <c r="N951" s="13"/>
     </row>
     <row r="952" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A952" s="135"/>
+      <c r="A952" s="131"/>
       <c r="B952" s="13"/>
       <c r="C952" s="13"/>
       <c r="D952" s="13" t="s">
@@ -30605,7 +30716,7 @@
       <c r="N952" s="13"/>
     </row>
     <row r="953" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A953" s="135"/>
+      <c r="A953" s="131"/>
       <c r="B953" s="13"/>
       <c r="C953" s="13"/>
       <c r="D953" s="13"/>
@@ -30629,7 +30740,7 @@
       <c r="N953" s="13"/>
     </row>
     <row r="954" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A954" s="135"/>
+      <c r="A954" s="131"/>
       <c r="B954" s="13"/>
       <c r="C954" s="13"/>
       <c r="D954" s="13"/>
@@ -30653,7 +30764,7 @@
       <c r="N954" s="13"/>
     </row>
     <row r="955" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A955" s="135"/>
+      <c r="A955" s="131"/>
       <c r="B955" s="13"/>
       <c r="C955" s="13"/>
       <c r="D955" s="13"/>
@@ -30677,7 +30788,7 @@
       <c r="N955" s="13"/>
     </row>
     <row r="956" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A956" s="136"/>
+      <c r="A956" s="132"/>
       <c r="B956" s="13"/>
       <c r="C956" s="13"/>
       <c r="D956" s="13"/>
@@ -30717,7 +30828,7 @@
       <c r="N957" s="13"/>
     </row>
     <row r="958" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A958" s="137">
+      <c r="A958" s="144">
         <v>173</v>
       </c>
       <c r="B958" s="13" t="s">
@@ -30749,7 +30860,7 @@
       </c>
     </row>
     <row r="959" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A959" s="136"/>
+      <c r="A959" s="132"/>
       <c r="B959" s="13"/>
       <c r="C959" s="13"/>
       <c r="D959" s="13"/>
@@ -30789,7 +30900,7 @@
       <c r="N960" s="13"/>
     </row>
     <row r="961" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A961" s="134">
+      <c r="A961" s="130">
         <v>174</v>
       </c>
       <c r="B961" s="13" t="s">
@@ -30821,7 +30932,7 @@
       </c>
     </row>
     <row r="962" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A962" s="136"/>
+      <c r="A962" s="132"/>
       <c r="B962" s="13"/>
       <c r="C962" s="13"/>
       <c r="D962" s="13"/>
@@ -30861,7 +30972,7 @@
       <c r="N963" s="13"/>
     </row>
     <row r="964" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A964" s="134">
+      <c r="A964" s="130">
         <v>175</v>
       </c>
       <c r="B964" s="13" t="s">
@@ -30891,7 +31002,7 @@
       <c r="N964" s="13"/>
     </row>
     <row r="965" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A965" s="135"/>
+      <c r="A965" s="131"/>
       <c r="B965" s="13"/>
       <c r="C965" s="13"/>
       <c r="D965" s="13"/>
@@ -30915,7 +31026,7 @@
       <c r="N965" s="13"/>
     </row>
     <row r="966" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A966" s="135"/>
+      <c r="A966" s="131"/>
       <c r="B966" s="13"/>
       <c r="C966" s="13"/>
       <c r="D966" s="13"/>
@@ -30939,7 +31050,7 @@
       <c r="N966" s="13"/>
     </row>
     <row r="967" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A967" s="135"/>
+      <c r="A967" s="131"/>
       <c r="B967" s="13"/>
       <c r="C967" s="13"/>
       <c r="D967" s="13"/>
@@ -30963,7 +31074,7 @@
       <c r="N967" s="13"/>
     </row>
     <row r="968" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A968" s="136"/>
+      <c r="A968" s="132"/>
       <c r="B968" s="13"/>
       <c r="C968" s="13"/>
       <c r="D968" s="13"/>
@@ -31003,7 +31114,7 @@
       <c r="N969" s="13"/>
     </row>
     <row r="970" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A970" s="134">
+      <c r="A970" s="130">
         <v>176</v>
       </c>
       <c r="B970" s="13" t="s">
@@ -31033,7 +31144,7 @@
       <c r="N970" s="13"/>
     </row>
     <row r="971" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A971" s="135"/>
+      <c r="A971" s="131"/>
       <c r="B971" s="13"/>
       <c r="C971" s="13"/>
       <c r="D971" s="13"/>
@@ -31057,7 +31168,7 @@
       <c r="N971" s="13"/>
     </row>
     <row r="972" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A972" s="135"/>
+      <c r="A972" s="131"/>
       <c r="B972" s="13"/>
       <c r="C972" s="13"/>
       <c r="D972" s="13"/>
@@ -31081,7 +31192,7 @@
       <c r="N972" s="13"/>
     </row>
     <row r="973" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A973" s="135"/>
+      <c r="A973" s="131"/>
       <c r="B973" s="13"/>
       <c r="C973" s="13"/>
       <c r="D973" s="13"/>
@@ -31105,7 +31216,7 @@
       <c r="N973" s="13"/>
     </row>
     <row r="974" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A974" s="136"/>
+      <c r="A974" s="132"/>
       <c r="B974" s="13"/>
       <c r="C974" s="13"/>
       <c r="D974" s="13"/>
@@ -31145,7 +31256,7 @@
       <c r="N975" s="13"/>
     </row>
     <row r="976" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A976" s="134">
+      <c r="A976" s="130">
         <v>177</v>
       </c>
       <c r="B976" s="13" t="s">
@@ -31175,7 +31286,7 @@
       <c r="N976" s="13"/>
     </row>
     <row r="977" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A977" s="136"/>
+      <c r="A977" s="132"/>
       <c r="B977" s="13"/>
       <c r="C977" s="13"/>
       <c r="D977" s="13" t="s">
@@ -31217,7 +31328,7 @@
       <c r="N978" s="13"/>
     </row>
     <row r="979" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A979" s="134">
+      <c r="A979" s="130">
         <v>178</v>
       </c>
       <c r="B979" s="13" t="s">
@@ -31247,7 +31358,7 @@
       <c r="N979" s="13"/>
     </row>
     <row r="980" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A980" s="135"/>
+      <c r="A980" s="131"/>
       <c r="B980" s="13"/>
       <c r="C980" s="13"/>
       <c r="D980" s="13"/>
@@ -31271,7 +31382,7 @@
       <c r="N980" s="13"/>
     </row>
     <row r="981" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A981" s="135"/>
+      <c r="A981" s="131"/>
       <c r="B981" s="13"/>
       <c r="C981" s="13"/>
       <c r="D981" s="13" t="s">
@@ -31297,7 +31408,7 @@
       <c r="N981" s="13"/>
     </row>
     <row r="982" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A982" s="136"/>
+      <c r="A982" s="132"/>
       <c r="B982" s="13"/>
       <c r="C982" s="13"/>
       <c r="D982" s="13"/>
@@ -31337,7 +31448,7 @@
       <c r="N983" s="13"/>
     </row>
     <row r="984" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A984" s="134">
+      <c r="A984" s="130">
         <v>179</v>
       </c>
       <c r="B984" s="13" t="s">
@@ -31367,7 +31478,7 @@
       <c r="N984" s="13"/>
     </row>
     <row r="985" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A985" s="135"/>
+      <c r="A985" s="131"/>
       <c r="B985" s="13"/>
       <c r="C985" s="13"/>
       <c r="D985" s="13"/>
@@ -31391,7 +31502,7 @@
       <c r="N985" s="13"/>
     </row>
     <row r="986" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A986" s="135"/>
+      <c r="A986" s="131"/>
       <c r="B986" s="13"/>
       <c r="C986" s="13"/>
       <c r="D986" s="13"/>
@@ -31415,7 +31526,7 @@
       <c r="N986" s="13"/>
     </row>
     <row r="987" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A987" s="135"/>
+      <c r="A987" s="131"/>
       <c r="B987" s="13"/>
       <c r="C987" s="13"/>
       <c r="D987" s="13"/>
@@ -31439,7 +31550,7 @@
       <c r="N987" s="13"/>
     </row>
     <row r="988" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A988" s="135"/>
+      <c r="A988" s="131"/>
       <c r="B988" s="13"/>
       <c r="C988" s="13"/>
       <c r="D988" s="13"/>
@@ -31463,7 +31574,7 @@
       <c r="N988" s="13"/>
     </row>
     <row r="989" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A989" s="135"/>
+      <c r="A989" s="131"/>
       <c r="B989" s="13"/>
       <c r="C989" s="13"/>
       <c r="D989" s="13" t="s">
@@ -31489,7 +31600,7 @@
       <c r="N989" s="13"/>
     </row>
     <row r="990" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A990" s="135"/>
+      <c r="A990" s="131"/>
       <c r="B990" s="13"/>
       <c r="C990" s="13"/>
       <c r="D990" s="13"/>
@@ -31513,7 +31624,7 @@
       <c r="N990" s="13"/>
     </row>
     <row r="991" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A991" s="135"/>
+      <c r="A991" s="131"/>
       <c r="B991" s="13"/>
       <c r="C991" s="13"/>
       <c r="D991" s="13"/>
@@ -31537,7 +31648,7 @@
       <c r="N991" s="13"/>
     </row>
     <row r="992" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A992" s="135"/>
+      <c r="A992" s="131"/>
       <c r="B992" s="13"/>
       <c r="C992" s="13"/>
       <c r="D992" s="13"/>
@@ -31561,7 +31672,7 @@
       <c r="N992" s="13"/>
     </row>
     <row r="993" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A993" s="136"/>
+      <c r="A993" s="132"/>
       <c r="B993" s="13"/>
       <c r="C993" s="13"/>
       <c r="D993" s="13"/>
@@ -31693,7 +31804,7 @@
       <c r="N998" s="13"/>
     </row>
     <row r="999" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A999" s="134">
+      <c r="A999" s="130">
         <v>182</v>
       </c>
       <c r="B999" s="13" t="s">
@@ -31723,7 +31834,7 @@
       <c r="N999" s="13"/>
     </row>
     <row r="1000" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1000" s="135"/>
+      <c r="A1000" s="131"/>
       <c r="B1000" s="13"/>
       <c r="C1000" s="13"/>
       <c r="D1000" s="13"/>
@@ -31747,7 +31858,7 @@
       <c r="N1000" s="13"/>
     </row>
     <row r="1001" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1001" s="135"/>
+      <c r="A1001" s="131"/>
       <c r="B1001" s="13"/>
       <c r="C1001" s="13"/>
       <c r="D1001" s="13"/>
@@ -31771,7 +31882,7 @@
       <c r="N1001" s="13"/>
     </row>
     <row r="1002" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1002" s="135"/>
+      <c r="A1002" s="131"/>
       <c r="B1002" s="13"/>
       <c r="C1002" s="13"/>
       <c r="D1002" s="13"/>
@@ -31795,7 +31906,7 @@
       <c r="N1002" s="13"/>
     </row>
     <row r="1003" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1003" s="135"/>
+      <c r="A1003" s="131"/>
       <c r="B1003" s="13"/>
       <c r="C1003" s="13"/>
       <c r="D1003" s="13"/>
@@ -31819,7 +31930,7 @@
       <c r="N1003" s="13"/>
     </row>
     <row r="1004" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1004" s="135"/>
+      <c r="A1004" s="131"/>
       <c r="B1004" s="117"/>
       <c r="C1004" s="117"/>
       <c r="D1004" s="117" t="s">
@@ -31845,7 +31956,7 @@
       <c r="N1004" s="117"/>
     </row>
     <row r="1005" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1005" s="135"/>
+      <c r="A1005" s="131"/>
       <c r="B1005" s="117"/>
       <c r="C1005" s="117"/>
       <c r="D1005" s="117"/>
@@ -31869,7 +31980,7 @@
       <c r="N1005" s="117"/>
     </row>
     <row r="1006" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1006" s="135"/>
+      <c r="A1006" s="131"/>
       <c r="B1006" s="117"/>
       <c r="C1006" s="117"/>
       <c r="D1006" s="117"/>
@@ -31893,7 +32004,7 @@
       <c r="N1006" s="117"/>
     </row>
     <row r="1007" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1007" s="135"/>
+      <c r="A1007" s="131"/>
       <c r="B1007" s="117"/>
       <c r="C1007" s="117"/>
       <c r="D1007" s="117"/>
@@ -31917,7 +32028,7 @@
       <c r="N1007" s="117"/>
     </row>
     <row r="1008" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1008" s="136"/>
+      <c r="A1008" s="132"/>
       <c r="B1008" s="117"/>
       <c r="C1008" s="117"/>
       <c r="D1008" s="117"/>
@@ -31957,7 +32068,7 @@
       <c r="N1009" s="13"/>
     </row>
     <row r="1010" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1010" s="134">
+      <c r="A1010" s="130">
         <v>183</v>
       </c>
       <c r="B1010" s="13" t="s">
@@ -31987,7 +32098,7 @@
       <c r="N1010" s="13"/>
     </row>
     <row r="1011" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1011" s="135"/>
+      <c r="A1011" s="131"/>
       <c r="B1011" s="13"/>
       <c r="C1011" s="13"/>
       <c r="D1011" s="13"/>
@@ -32011,7 +32122,7 @@
       <c r="N1011" s="13"/>
     </row>
     <row r="1012" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1012" s="135"/>
+      <c r="A1012" s="131"/>
       <c r="B1012" s="13"/>
       <c r="C1012" s="13"/>
       <c r="D1012" s="13"/>
@@ -32035,7 +32146,7 @@
       <c r="N1012" s="13"/>
     </row>
     <row r="1013" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1013" s="135"/>
+      <c r="A1013" s="131"/>
       <c r="B1013" s="13"/>
       <c r="C1013" s="13"/>
       <c r="D1013" s="13"/>
@@ -32059,7 +32170,7 @@
       <c r="N1013" s="13"/>
     </row>
     <row r="1014" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1014" s="135"/>
+      <c r="A1014" s="131"/>
       <c r="B1014" s="13"/>
       <c r="C1014" s="13"/>
       <c r="D1014" s="13"/>
@@ -32083,7 +32194,7 @@
       <c r="N1014" s="13"/>
     </row>
     <row r="1015" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1015" s="135"/>
+      <c r="A1015" s="131"/>
       <c r="B1015" s="13"/>
       <c r="C1015" s="13"/>
       <c r="D1015" s="13" t="s">
@@ -32109,7 +32220,7 @@
       <c r="N1015" s="13"/>
     </row>
     <row r="1016" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1016" s="135"/>
+      <c r="A1016" s="131"/>
       <c r="B1016" s="13"/>
       <c r="C1016" s="13"/>
       <c r="D1016" s="13"/>
@@ -32133,7 +32244,7 @@
       <c r="N1016" s="13"/>
     </row>
     <row r="1017" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1017" s="135"/>
+      <c r="A1017" s="131"/>
       <c r="B1017" s="13"/>
       <c r="C1017" s="13"/>
       <c r="D1017" s="13"/>
@@ -32157,7 +32268,7 @@
       <c r="N1017" s="13"/>
     </row>
     <row r="1018" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1018" s="135"/>
+      <c r="A1018" s="131"/>
       <c r="B1018" s="13"/>
       <c r="C1018" s="13"/>
       <c r="D1018" s="13"/>
@@ -32181,7 +32292,7 @@
       <c r="N1018" s="13"/>
     </row>
     <row r="1019" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1019" s="135"/>
+      <c r="A1019" s="131"/>
       <c r="B1019" s="13"/>
       <c r="C1019" s="13"/>
       <c r="D1019" s="13"/>
@@ -32205,7 +32316,7 @@
       <c r="N1019" s="13"/>
     </row>
     <row r="1020" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1020" s="135"/>
+      <c r="A1020" s="131"/>
       <c r="B1020" s="13"/>
       <c r="C1020" s="13"/>
       <c r="D1020" s="13" t="s">
@@ -32231,7 +32342,7 @@
       <c r="N1020" s="13"/>
     </row>
     <row r="1021" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1021" s="135"/>
+      <c r="A1021" s="131"/>
       <c r="B1021" s="13"/>
       <c r="C1021" s="13"/>
       <c r="D1021" s="13"/>
@@ -32255,7 +32366,7 @@
       <c r="N1021" s="13"/>
     </row>
     <row r="1022" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1022" s="135"/>
+      <c r="A1022" s="131"/>
       <c r="B1022" s="13"/>
       <c r="C1022" s="13"/>
       <c r="D1022" s="13"/>
@@ -32279,7 +32390,7 @@
       <c r="N1022" s="13"/>
     </row>
     <row r="1023" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1023" s="135"/>
+      <c r="A1023" s="131"/>
       <c r="B1023" s="13"/>
       <c r="C1023" s="13"/>
       <c r="D1023" s="13"/>
@@ -32303,7 +32414,7 @@
       <c r="N1023" s="13"/>
     </row>
     <row r="1024" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1024" s="135"/>
+      <c r="A1024" s="131"/>
       <c r="B1024" s="13"/>
       <c r="C1024" s="13"/>
       <c r="D1024" s="13"/>
@@ -32327,7 +32438,7 @@
       <c r="N1024" s="13"/>
     </row>
     <row r="1025" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1025" s="135"/>
+      <c r="A1025" s="131"/>
       <c r="B1025" s="13"/>
       <c r="C1025" s="13"/>
       <c r="D1025" s="13" t="s">
@@ -32353,7 +32464,7 @@
       <c r="N1025" s="13"/>
     </row>
     <row r="1026" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1026" s="135"/>
+      <c r="A1026" s="131"/>
       <c r="B1026" s="13"/>
       <c r="C1026" s="13"/>
       <c r="D1026" s="13"/>
@@ -32377,7 +32488,7 @@
       <c r="N1026" s="13"/>
     </row>
     <row r="1027" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1027" s="135"/>
+      <c r="A1027" s="131"/>
       <c r="B1027" s="13"/>
       <c r="C1027" s="13"/>
       <c r="D1027" s="13"/>
@@ -32401,7 +32512,7 @@
       <c r="N1027" s="13"/>
     </row>
     <row r="1028" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1028" s="135"/>
+      <c r="A1028" s="131"/>
       <c r="B1028" s="13"/>
       <c r="C1028" s="13"/>
       <c r="D1028" s="13"/>
@@ -32425,7 +32536,7 @@
       <c r="N1028" s="13"/>
     </row>
     <row r="1029" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1029" s="136"/>
+      <c r="A1029" s="132"/>
       <c r="B1029" s="13"/>
       <c r="C1029" s="13"/>
       <c r="D1029" s="13"/>
@@ -32465,7 +32576,7 @@
       <c r="N1030" s="13"/>
     </row>
     <row r="1031" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1031" s="134">
+      <c r="A1031" s="130">
         <v>184</v>
       </c>
       <c r="B1031" s="13" t="s">
@@ -32495,7 +32606,7 @@
       <c r="N1031" s="13"/>
     </row>
     <row r="1032" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1032" s="135"/>
+      <c r="A1032" s="131"/>
       <c r="B1032" s="13"/>
       <c r="C1032" s="13"/>
       <c r="D1032" s="13"/>
@@ -32519,7 +32630,7 @@
       <c r="N1032" s="13"/>
     </row>
     <row r="1033" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1033" s="135"/>
+      <c r="A1033" s="131"/>
       <c r="B1033" s="13"/>
       <c r="C1033" s="13"/>
       <c r="D1033" s="13"/>
@@ -32543,7 +32654,7 @@
       <c r="N1033" s="13"/>
     </row>
     <row r="1034" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1034" s="135"/>
+      <c r="A1034" s="131"/>
       <c r="B1034" s="13"/>
       <c r="C1034" s="13"/>
       <c r="D1034" s="13"/>
@@ -32567,7 +32678,7 @@
       <c r="N1034" s="13"/>
     </row>
     <row r="1035" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1035" s="135"/>
+      <c r="A1035" s="131"/>
       <c r="B1035" s="13"/>
       <c r="C1035" s="13"/>
       <c r="D1035" s="13"/>
@@ -32591,7 +32702,7 @@
       <c r="N1035" s="13"/>
     </row>
     <row r="1036" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1036" s="135"/>
+      <c r="A1036" s="131"/>
       <c r="B1036" s="13"/>
       <c r="C1036" s="13"/>
       <c r="D1036" s="13" t="s">
@@ -32617,7 +32728,7 @@
       <c r="N1036" s="13"/>
     </row>
     <row r="1037" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1037" s="135"/>
+      <c r="A1037" s="131"/>
       <c r="B1037" s="13"/>
       <c r="C1037" s="13"/>
       <c r="D1037" s="13"/>
@@ -32641,7 +32752,7 @@
       <c r="N1037" s="13"/>
     </row>
     <row r="1038" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1038" s="135"/>
+      <c r="A1038" s="131"/>
       <c r="B1038" s="13"/>
       <c r="C1038" s="13"/>
       <c r="D1038" s="13"/>
@@ -32665,7 +32776,7 @@
       <c r="N1038" s="13"/>
     </row>
     <row r="1039" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1039" s="135"/>
+      <c r="A1039" s="131"/>
       <c r="B1039" s="13"/>
       <c r="C1039" s="13"/>
       <c r="D1039" s="13"/>
@@ -32689,7 +32800,7 @@
       <c r="N1039" s="13"/>
     </row>
     <row r="1040" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1040" s="135"/>
+      <c r="A1040" s="131"/>
       <c r="B1040" s="13"/>
       <c r="C1040" s="13"/>
       <c r="D1040" s="13"/>
@@ -32713,7 +32824,7 @@
       <c r="N1040" s="13"/>
     </row>
     <row r="1041" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1041" s="135"/>
+      <c r="A1041" s="131"/>
       <c r="B1041" s="13"/>
       <c r="C1041" s="13"/>
       <c r="D1041" s="13" t="s">
@@ -32739,7 +32850,7 @@
       <c r="N1041" s="13"/>
     </row>
     <row r="1042" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1042" s="135"/>
+      <c r="A1042" s="131"/>
       <c r="B1042" s="13"/>
       <c r="C1042" s="13"/>
       <c r="D1042" s="13"/>
@@ -32763,7 +32874,7 @@
       <c r="N1042" s="13"/>
     </row>
     <row r="1043" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1043" s="135"/>
+      <c r="A1043" s="131"/>
       <c r="B1043" s="13"/>
       <c r="C1043" s="13"/>
       <c r="D1043" s="13"/>
@@ -32787,7 +32898,7 @@
       <c r="N1043" s="13"/>
     </row>
     <row r="1044" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1044" s="135"/>
+      <c r="A1044" s="131"/>
       <c r="B1044" s="13"/>
       <c r="C1044" s="13"/>
       <c r="D1044" s="13"/>
@@ -32811,7 +32922,7 @@
       <c r="N1044" s="13"/>
     </row>
     <row r="1045" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1045" s="135"/>
+      <c r="A1045" s="131"/>
       <c r="B1045" s="13"/>
       <c r="C1045" s="13"/>
       <c r="D1045" s="13"/>
@@ -32835,7 +32946,7 @@
       <c r="N1045" s="13"/>
     </row>
     <row r="1046" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1046" s="135"/>
+      <c r="A1046" s="131"/>
       <c r="B1046" s="13"/>
       <c r="C1046" s="13"/>
       <c r="D1046" s="13" t="s">
@@ -32861,7 +32972,7 @@
       <c r="N1046" s="13"/>
     </row>
     <row r="1047" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1047" s="135"/>
+      <c r="A1047" s="131"/>
       <c r="B1047" s="13"/>
       <c r="C1047" s="13"/>
       <c r="D1047" s="13"/>
@@ -32885,7 +32996,7 @@
       <c r="N1047" s="13"/>
     </row>
     <row r="1048" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1048" s="135"/>
+      <c r="A1048" s="131"/>
       <c r="B1048" s="13"/>
       <c r="C1048" s="13"/>
       <c r="D1048" s="13"/>
@@ -32909,7 +33020,7 @@
       <c r="N1048" s="13"/>
     </row>
     <row r="1049" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1049" s="135"/>
+      <c r="A1049" s="131"/>
       <c r="B1049" s="13"/>
       <c r="C1049" s="13"/>
       <c r="D1049" s="13"/>
@@ -32933,7 +33044,7 @@
       <c r="N1049" s="13"/>
     </row>
     <row r="1050" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1050" s="136"/>
+      <c r="A1050" s="132"/>
       <c r="B1050" s="13"/>
       <c r="C1050" s="13"/>
       <c r="D1050" s="13"/>
@@ -32973,7 +33084,7 @@
       <c r="N1051" s="13"/>
     </row>
     <row r="1052" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1052" s="134">
+      <c r="A1052" s="130">
         <v>185</v>
       </c>
       <c r="B1052" s="13" t="s">
@@ -33003,7 +33114,7 @@
       <c r="N1052" s="13"/>
     </row>
     <row r="1053" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1053" s="136"/>
+      <c r="A1053" s="132"/>
       <c r="B1053" s="13"/>
       <c r="C1053" s="13"/>
       <c r="D1053" s="13"/>
@@ -33043,7 +33154,7 @@
       <c r="N1054" s="13"/>
     </row>
     <row r="1055" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1055" s="134">
+      <c r="A1055" s="130">
         <v>186</v>
       </c>
       <c r="B1055" s="13" t="s">
@@ -33073,7 +33184,7 @@
       <c r="N1055" s="13"/>
     </row>
     <row r="1056" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1056" s="136"/>
+      <c r="A1056" s="132"/>
       <c r="B1056" s="13"/>
       <c r="C1056" s="13"/>
       <c r="D1056" s="13"/>
@@ -33113,7 +33224,7 @@
       <c r="N1057" s="13"/>
     </row>
     <row r="1058" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1058" s="134">
+      <c r="A1058" s="130">
         <v>187</v>
       </c>
       <c r="B1058" s="13" t="s">
@@ -33143,7 +33254,7 @@
       <c r="N1058" s="13"/>
     </row>
     <row r="1059" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1059" s="135"/>
+      <c r="A1059" s="131"/>
       <c r="B1059" s="13"/>
       <c r="C1059" s="13"/>
       <c r="D1059" s="13"/>
@@ -33167,7 +33278,7 @@
       <c r="N1059" s="13"/>
     </row>
     <row r="1060" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1060" s="135"/>
+      <c r="A1060" s="131"/>
       <c r="B1060" s="13"/>
       <c r="C1060" s="13"/>
       <c r="D1060" s="13" t="s">
@@ -33193,7 +33304,7 @@
       <c r="N1060" s="13"/>
     </row>
     <row r="1061" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1061" s="135"/>
+      <c r="A1061" s="131"/>
       <c r="B1061" s="13"/>
       <c r="C1061" s="13"/>
       <c r="D1061" s="13"/>
@@ -33217,7 +33328,7 @@
       <c r="N1061" s="13"/>
     </row>
     <row r="1062" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1062" s="135"/>
+      <c r="A1062" s="131"/>
       <c r="B1062" s="13"/>
       <c r="C1062" s="13"/>
       <c r="D1062" s="13" t="s">
@@ -33243,7 +33354,7 @@
       <c r="N1062" s="13"/>
     </row>
     <row r="1063" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1063" s="135"/>
+      <c r="A1063" s="131"/>
       <c r="B1063" s="13"/>
       <c r="C1063" s="13"/>
       <c r="D1063" s="13"/>
@@ -33267,7 +33378,7 @@
       <c r="N1063" s="13"/>
     </row>
     <row r="1064" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1064" s="135"/>
+      <c r="A1064" s="131"/>
       <c r="B1064" s="13"/>
       <c r="C1064" s="13"/>
       <c r="D1064" s="13" t="s">
@@ -33293,7 +33404,7 @@
       <c r="N1064" s="13"/>
     </row>
     <row r="1065" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1065" s="136"/>
+      <c r="A1065" s="132"/>
       <c r="B1065" s="13"/>
       <c r="C1065" s="13"/>
       <c r="D1065" s="13"/>
@@ -33333,14 +33444,14 @@
       <c r="N1066" s="13"/>
     </row>
     <row r="1067" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1067" s="134">
+      <c r="A1067" s="130">
         <v>188</v>
       </c>
       <c r="B1067" s="13" t="s">
         <v>511</v>
       </c>
       <c r="C1067" s="13"/>
-      <c r="D1067" s="149" t="s">
+      <c r="D1067" s="128" t="s">
         <v>512</v>
       </c>
       <c r="E1067" s="100" t="s">
@@ -33363,7 +33474,7 @@
       <c r="N1067" s="13"/>
     </row>
     <row r="1068" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1068" s="135"/>
+      <c r="A1068" s="131"/>
       <c r="B1068" s="13"/>
       <c r="C1068" s="13"/>
       <c r="D1068" s="13"/>
@@ -33387,10 +33498,10 @@
       <c r="N1068" s="13"/>
     </row>
     <row r="1069" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1069" s="135"/>
+      <c r="A1069" s="131"/>
       <c r="B1069" s="13"/>
       <c r="C1069" s="13"/>
-      <c r="D1069" s="149" t="s">
+      <c r="D1069" s="128" t="s">
         <v>513</v>
       </c>
       <c r="E1069" s="100" t="s">
@@ -33413,7 +33524,7 @@
       <c r="N1069" s="13"/>
     </row>
     <row r="1070" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1070" s="135"/>
+      <c r="A1070" s="131"/>
       <c r="B1070" s="13"/>
       <c r="C1070" s="13"/>
       <c r="D1070" s="13"/>
@@ -33437,10 +33548,10 @@
       <c r="N1070" s="13"/>
     </row>
     <row r="1071" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1071" s="135"/>
+      <c r="A1071" s="131"/>
       <c r="B1071" s="13"/>
       <c r="C1071" s="13"/>
-      <c r="D1071" s="149" t="s">
+      <c r="D1071" s="128" t="s">
         <v>514</v>
       </c>
       <c r="E1071" s="100" t="s">
@@ -33463,7 +33574,7 @@
       <c r="N1071" s="13"/>
     </row>
     <row r="1072" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1072" s="135"/>
+      <c r="A1072" s="131"/>
       <c r="B1072" s="13"/>
       <c r="C1072" s="13"/>
       <c r="D1072" s="13"/>
@@ -33487,10 +33598,10 @@
       <c r="N1072" s="13"/>
     </row>
     <row r="1073" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1073" s="135"/>
+      <c r="A1073" s="131"/>
       <c r="B1073" s="13"/>
       <c r="C1073" s="13"/>
-      <c r="D1073" s="149" t="s">
+      <c r="D1073" s="128" t="s">
         <v>515</v>
       </c>
       <c r="E1073" s="100" t="s">
@@ -33513,7 +33624,7 @@
       <c r="N1073" s="13"/>
     </row>
     <row r="1074" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1074" s="136"/>
+      <c r="A1074" s="132"/>
       <c r="B1074" s="13"/>
       <c r="C1074" s="13"/>
       <c r="D1074" s="13"/>
@@ -33553,14 +33664,14 @@
       <c r="N1075" s="13"/>
     </row>
     <row r="1076" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1076" s="134">
+      <c r="A1076" s="130">
         <v>189</v>
       </c>
       <c r="B1076" s="13" t="s">
         <v>516</v>
       </c>
       <c r="C1076" s="13"/>
-      <c r="D1076" s="149" t="s">
+      <c r="D1076" s="128" t="s">
         <v>517</v>
       </c>
       <c r="E1076" s="100" t="s">
@@ -33585,7 +33696,7 @@
       </c>
     </row>
     <row r="1077" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1077" s="135"/>
+      <c r="A1077" s="131"/>
       <c r="B1077" s="13"/>
       <c r="C1077" s="13"/>
       <c r="D1077" s="13"/>
@@ -33609,7 +33720,7 @@
       <c r="N1077" s="13"/>
     </row>
     <row r="1078" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1078" s="135"/>
+      <c r="A1078" s="131"/>
       <c r="B1078" s="13"/>
       <c r="C1078" s="13"/>
       <c r="D1078" s="13"/>
@@ -33633,7 +33744,7 @@
       <c r="N1078" s="13"/>
     </row>
     <row r="1079" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1079" s="135"/>
+      <c r="A1079" s="131"/>
       <c r="B1079" s="13"/>
       <c r="C1079" s="13"/>
       <c r="D1079" s="13"/>
@@ -33657,7 +33768,7 @@
       <c r="N1079" s="13"/>
     </row>
     <row r="1080" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1080" s="135"/>
+      <c r="A1080" s="131"/>
       <c r="B1080" s="13"/>
       <c r="C1080" s="13"/>
       <c r="D1080" s="13"/>
@@ -33681,10 +33792,10 @@
       <c r="N1080" s="13"/>
     </row>
     <row r="1081" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1081" s="135"/>
+      <c r="A1081" s="131"/>
       <c r="B1081" s="13"/>
       <c r="C1081" s="13"/>
-      <c r="D1081" s="148" t="s">
+      <c r="D1081" s="127" t="s">
         <v>519</v>
       </c>
       <c r="E1081" s="100" t="s">
@@ -33707,7 +33818,7 @@
       <c r="N1081" s="13"/>
     </row>
     <row r="1082" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1082" s="135"/>
+      <c r="A1082" s="131"/>
       <c r="B1082" s="13"/>
       <c r="C1082" s="13"/>
       <c r="D1082" s="13"/>
@@ -33731,7 +33842,7 @@
       <c r="N1082" s="13"/>
     </row>
     <row r="1083" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1083" s="135"/>
+      <c r="A1083" s="131"/>
       <c r="B1083" s="13"/>
       <c r="C1083" s="13"/>
       <c r="D1083" s="13"/>
@@ -33755,7 +33866,7 @@
       <c r="N1083" s="13"/>
     </row>
     <row r="1084" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1084" s="135"/>
+      <c r="A1084" s="131"/>
       <c r="B1084" s="13"/>
       <c r="C1084" s="13"/>
       <c r="D1084" s="13"/>
@@ -33779,7 +33890,7 @@
       <c r="N1084" s="13"/>
     </row>
     <row r="1085" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1085" s="136"/>
+      <c r="A1085" s="132"/>
       <c r="B1085" s="13"/>
       <c r="C1085" s="13"/>
       <c r="D1085" s="13"/>
@@ -33819,7 +33930,7 @@
       <c r="N1086" s="13"/>
     </row>
     <row r="1087" spans="1:14" ht="15" customHeight="1">
-      <c r="A1087" s="134">
+      <c r="A1087" s="130">
         <v>190</v>
       </c>
       <c r="B1087" s="13" t="s">
@@ -33849,7 +33960,7 @@
       <c r="N1087" s="13"/>
     </row>
     <row r="1088" spans="1:14" ht="15" customHeight="1">
-      <c r="A1088" s="135"/>
+      <c r="A1088" s="131"/>
       <c r="B1088" s="13"/>
       <c r="C1088" s="13"/>
       <c r="D1088" s="13"/>
@@ -33873,7 +33984,7 @@
       <c r="N1088" s="13"/>
     </row>
     <row r="1089" spans="1:14" ht="15" customHeight="1">
-      <c r="A1089" s="135"/>
+      <c r="A1089" s="131"/>
       <c r="B1089" s="13"/>
       <c r="C1089" s="13"/>
       <c r="D1089" s="13" t="s">
@@ -33899,7 +34010,7 @@
       <c r="N1089" s="13"/>
     </row>
     <row r="1090" spans="1:14" ht="15" customHeight="1">
-      <c r="A1090" s="136"/>
+      <c r="A1090" s="132"/>
       <c r="B1090" s="13"/>
       <c r="C1090" s="13"/>
       <c r="D1090" s="13"/>
@@ -33939,7 +34050,7 @@
       <c r="N1091" s="13"/>
     </row>
     <row r="1092" spans="1:14" ht="15" customHeight="1">
-      <c r="A1092" s="134">
+      <c r="A1092" s="130">
         <v>191</v>
       </c>
       <c r="B1092" s="13" t="s">
@@ -33969,7 +34080,7 @@
       <c r="N1092" s="13"/>
     </row>
     <row r="1093" spans="1:14" ht="15" customHeight="1">
-      <c r="A1093" s="136"/>
+      <c r="A1093" s="132"/>
       <c r="B1093" s="13"/>
       <c r="C1093" s="13"/>
       <c r="D1093" s="13"/>
@@ -34099,7 +34210,7 @@
       <c r="N1098" s="13"/>
     </row>
     <row r="1099" spans="1:14" ht="15" customHeight="1">
-      <c r="A1099" s="134">
+      <c r="A1099" s="130">
         <v>194</v>
       </c>
       <c r="B1099" s="13"/>
@@ -34127,7 +34238,7 @@
       <c r="N1099" s="13"/>
     </row>
     <row r="1100" spans="1:14" ht="15" customHeight="1">
-      <c r="A1100" s="135"/>
+      <c r="A1100" s="131"/>
       <c r="B1100" s="13"/>
       <c r="C1100" s="13"/>
       <c r="D1100" s="13" t="s">
@@ -34153,7 +34264,7 @@
       <c r="N1100" s="13"/>
     </row>
     <row r="1101" spans="1:14" ht="15" customHeight="1">
-      <c r="A1101" s="135"/>
+      <c r="A1101" s="131"/>
       <c r="B1101" s="13"/>
       <c r="C1101" s="13"/>
       <c r="D1101" s="13" t="s">
@@ -34179,7 +34290,7 @@
       <c r="N1101" s="13"/>
     </row>
     <row r="1102" spans="1:14" ht="15" customHeight="1">
-      <c r="A1102" s="136"/>
+      <c r="A1102" s="132"/>
       <c r="B1102" s="13"/>
       <c r="C1102" s="13"/>
       <c r="D1102" s="13" t="s">
@@ -34221,7 +34332,7 @@
       <c r="N1103" s="13"/>
     </row>
     <row r="1104" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1104" s="134">
+      <c r="A1104" s="130">
         <v>195</v>
       </c>
       <c r="B1104" s="13"/>
@@ -34249,7 +34360,7 @@
       <c r="N1104" s="13"/>
     </row>
     <row r="1105" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1105" s="135"/>
+      <c r="A1105" s="131"/>
       <c r="B1105" s="13"/>
       <c r="C1105" s="13"/>
       <c r="D1105" s="13" t="s">
@@ -34275,7 +34386,7 @@
       <c r="N1105" s="13"/>
     </row>
     <row r="1106" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1106" s="135"/>
+      <c r="A1106" s="131"/>
       <c r="B1106" s="13"/>
       <c r="C1106" s="13"/>
       <c r="D1106" s="13" t="s">
@@ -34301,7 +34412,7 @@
       <c r="N1106" s="13"/>
     </row>
     <row r="1107" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1107" s="135"/>
+      <c r="A1107" s="131"/>
       <c r="B1107" s="13"/>
       <c r="C1107" s="13"/>
       <c r="D1107" s="13" t="s">
@@ -34327,7 +34438,7 @@
       <c r="N1107" s="13"/>
     </row>
     <row r="1108" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1108" s="135"/>
+      <c r="A1108" s="131"/>
       <c r="B1108" s="13"/>
       <c r="C1108" s="13"/>
       <c r="D1108" s="13" t="s">
@@ -34353,7 +34464,7 @@
       <c r="N1108" s="13"/>
     </row>
     <row r="1109" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1109" s="135"/>
+      <c r="A1109" s="131"/>
       <c r="B1109" s="13"/>
       <c r="C1109" s="13"/>
       <c r="D1109" s="13" t="s">
@@ -34379,7 +34490,7 @@
       <c r="N1109" s="13"/>
     </row>
     <row r="1110" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1110" s="135"/>
+      <c r="A1110" s="131"/>
       <c r="B1110" s="13"/>
       <c r="C1110" s="13"/>
       <c r="D1110" s="13" t="s">
@@ -34405,7 +34516,7 @@
       <c r="N1110" s="13"/>
     </row>
     <row r="1111" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1111" s="135"/>
+      <c r="A1111" s="131"/>
       <c r="B1111" s="13"/>
       <c r="C1111" s="13"/>
       <c r="D1111" s="13" t="s">
@@ -34431,7 +34542,7 @@
       <c r="N1111" s="13"/>
     </row>
     <row r="1112" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1112" s="135"/>
+      <c r="A1112" s="131"/>
       <c r="B1112" s="13"/>
       <c r="C1112" s="13"/>
       <c r="D1112" s="13" t="s">
@@ -34457,7 +34568,7 @@
       <c r="N1112" s="13"/>
     </row>
     <row r="1113" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1113" s="135"/>
+      <c r="A1113" s="131"/>
       <c r="B1113" s="13"/>
       <c r="C1113" s="13"/>
       <c r="D1113" s="13" t="s">
@@ -34483,7 +34594,7 @@
       <c r="N1113" s="13"/>
     </row>
     <row r="1114" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1114" s="135"/>
+      <c r="A1114" s="131"/>
       <c r="B1114" s="13"/>
       <c r="C1114" s="13"/>
       <c r="D1114" s="13" t="s">
@@ -34509,7 +34620,7 @@
       <c r="N1114" s="13"/>
     </row>
     <row r="1115" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1115" s="135"/>
+      <c r="A1115" s="131"/>
       <c r="B1115" s="13"/>
       <c r="C1115" s="13"/>
       <c r="D1115" s="13" t="s">
@@ -34535,7 +34646,7 @@
       <c r="N1115" s="13"/>
     </row>
     <row r="1116" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1116" s="135"/>
+      <c r="A1116" s="131"/>
       <c r="B1116" s="13"/>
       <c r="C1116" s="13"/>
       <c r="D1116" s="13" t="s">
@@ -34561,7 +34672,7 @@
       <c r="N1116" s="13"/>
     </row>
     <row r="1117" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1117" s="135"/>
+      <c r="A1117" s="131"/>
       <c r="B1117" s="13"/>
       <c r="C1117" s="13"/>
       <c r="D1117" s="13" t="s">
@@ -34587,7 +34698,7 @@
       <c r="N1117" s="13"/>
     </row>
     <row r="1118" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1118" s="135"/>
+      <c r="A1118" s="131"/>
       <c r="B1118" s="13"/>
       <c r="C1118" s="13"/>
       <c r="D1118" s="13" t="s">
@@ -34613,7 +34724,7 @@
       <c r="N1118" s="13"/>
     </row>
     <row r="1119" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1119" s="135"/>
+      <c r="A1119" s="131"/>
       <c r="B1119" s="13"/>
       <c r="C1119" s="13"/>
       <c r="D1119" s="13" t="s">
@@ -34639,7 +34750,7 @@
       <c r="N1119" s="13"/>
     </row>
     <row r="1120" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1120" s="135"/>
+      <c r="A1120" s="131"/>
       <c r="B1120" s="13"/>
       <c r="C1120" s="13"/>
       <c r="D1120" s="13" t="s">
@@ -34665,7 +34776,7 @@
       <c r="N1120" s="13"/>
     </row>
     <row r="1121" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1121" s="135"/>
+      <c r="A1121" s="131"/>
       <c r="B1121" s="13"/>
       <c r="C1121" s="13"/>
       <c r="D1121" s="13" t="s">
@@ -34691,7 +34802,7 @@
       <c r="N1121" s="13"/>
     </row>
     <row r="1122" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1122" s="135"/>
+      <c r="A1122" s="131"/>
       <c r="B1122" s="13"/>
       <c r="C1122" s="13"/>
       <c r="D1122" s="13" t="s">
@@ -34717,7 +34828,7 @@
       <c r="N1122" s="13"/>
     </row>
     <row r="1123" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1123" s="135"/>
+      <c r="A1123" s="131"/>
       <c r="B1123" s="13"/>
       <c r="C1123" s="13"/>
       <c r="D1123" s="13" t="s">
@@ -34743,7 +34854,7 @@
       <c r="N1123" s="13"/>
     </row>
     <row r="1124" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1124" s="135"/>
+      <c r="A1124" s="131"/>
       <c r="B1124" s="13"/>
       <c r="C1124" s="13"/>
       <c r="D1124" s="13" t="s">
@@ -34769,7 +34880,7 @@
       <c r="N1124" s="13"/>
     </row>
     <row r="1125" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1125" s="135"/>
+      <c r="A1125" s="131"/>
       <c r="B1125" s="13"/>
       <c r="C1125" s="13"/>
       <c r="D1125" s="13" t="s">
@@ -34795,7 +34906,7 @@
       <c r="N1125" s="13"/>
     </row>
     <row r="1126" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1126" s="135"/>
+      <c r="A1126" s="131"/>
       <c r="B1126" s="13"/>
       <c r="C1126" s="13"/>
       <c r="D1126" s="13" t="s">
@@ -34821,7 +34932,7 @@
       <c r="N1126" s="13"/>
     </row>
     <row r="1127" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1127" s="136"/>
+      <c r="A1127" s="132"/>
       <c r="B1127" s="13"/>
       <c r="C1127" s="13"/>
       <c r="D1127" s="13" t="s">
@@ -34907,7 +35018,7 @@
       <c r="N1130" s="13"/>
     </row>
     <row r="1131" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1131" s="134">
+      <c r="A1131" s="130">
         <v>197</v>
       </c>
       <c r="B1131" s="72" t="s">
@@ -34937,7 +35048,7 @@
       <c r="N1131" s="13"/>
     </row>
     <row r="1132" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1132" s="135"/>
+      <c r="A1132" s="131"/>
       <c r="B1132" s="72" t="s">
         <v>557</v>
       </c>
@@ -34965,7 +35076,7 @@
       <c r="N1132" s="13"/>
     </row>
     <row r="1133" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1133" s="135"/>
+      <c r="A1133" s="131"/>
       <c r="B1133" s="72" t="s">
         <v>557</v>
       </c>
@@ -34993,7 +35104,7 @@
       <c r="N1133" s="13"/>
     </row>
     <row r="1134" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1134" s="136"/>
+      <c r="A1134" s="132"/>
       <c r="B1134" s="72" t="s">
         <v>557</v>
       </c>
@@ -35037,7 +35148,7 @@
       <c r="N1135" s="13"/>
     </row>
     <row r="1136" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1136" s="134">
+      <c r="A1136" s="130">
         <v>202</v>
       </c>
       <c r="B1136" s="72">
@@ -35067,7 +35178,7 @@
       <c r="N1136" s="13"/>
     </row>
     <row r="1137" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1137" s="135"/>
+      <c r="A1137" s="131"/>
       <c r="B1137" s="72">
         <v>59</v>
       </c>
@@ -35095,7 +35206,7 @@
       <c r="N1137" s="13"/>
     </row>
     <row r="1138" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1138" s="135"/>
+      <c r="A1138" s="131"/>
       <c r="B1138" s="72">
         <v>59</v>
       </c>
@@ -35123,7 +35234,7 @@
       <c r="N1138" s="13"/>
     </row>
     <row r="1139" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1139" s="136"/>
+      <c r="A1139" s="132"/>
       <c r="B1139" s="72">
         <v>59</v>
       </c>
@@ -35167,7 +35278,7 @@
       <c r="N1140" s="13"/>
     </row>
     <row r="1141" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1141" s="134">
+      <c r="A1141" s="130">
         <v>203</v>
       </c>
       <c r="B1141" s="72" t="s">
@@ -35197,7 +35308,7 @@
       <c r="N1141" s="13"/>
     </row>
     <row r="1142" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1142" s="135"/>
+      <c r="A1142" s="131"/>
       <c r="B1142" s="72" t="s">
         <v>560</v>
       </c>
@@ -35225,7 +35336,7 @@
       <c r="N1142" s="13"/>
     </row>
     <row r="1143" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1143" s="135"/>
+      <c r="A1143" s="131"/>
       <c r="B1143" s="72" t="s">
         <v>560</v>
       </c>
@@ -35253,7 +35364,7 @@
       <c r="N1143" s="13"/>
     </row>
     <row r="1144" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1144" s="136"/>
+      <c r="A1144" s="132"/>
       <c r="B1144" s="72" t="s">
         <v>560</v>
       </c>
@@ -35297,7 +35408,7 @@
       <c r="N1145" s="13"/>
     </row>
     <row r="1146" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1146" s="134">
+      <c r="A1146" s="130">
         <v>204</v>
       </c>
       <c r="B1146" s="72">
@@ -35327,7 +35438,7 @@
       <c r="N1146" s="13"/>
     </row>
     <row r="1147" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1147" s="135"/>
+      <c r="A1147" s="131"/>
       <c r="B1147" s="72">
         <v>27</v>
       </c>
@@ -35355,7 +35466,7 @@
       <c r="N1147" s="13"/>
     </row>
     <row r="1148" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1148" s="135"/>
+      <c r="A1148" s="131"/>
       <c r="B1148" s="72">
         <v>27</v>
       </c>
@@ -35383,7 +35494,7 @@
       <c r="N1148" s="13"/>
     </row>
     <row r="1149" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1149" s="136"/>
+      <c r="A1149" s="132"/>
       <c r="B1149" s="72">
         <v>27</v>
       </c>
@@ -35427,7 +35538,7 @@
       <c r="N1150" s="13"/>
     </row>
     <row r="1151" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1151" s="134">
+      <c r="A1151" s="130">
         <v>205</v>
       </c>
       <c r="B1151" s="72" t="s">
@@ -35457,7 +35568,7 @@
       <c r="N1151" s="13"/>
     </row>
     <row r="1152" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1152" s="135"/>
+      <c r="A1152" s="131"/>
       <c r="B1152" s="72" t="s">
         <v>563</v>
       </c>
@@ -35485,7 +35596,7 @@
       <c r="N1152" s="13"/>
     </row>
     <row r="1153" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1153" s="135"/>
+      <c r="A1153" s="131"/>
       <c r="B1153" s="72" t="s">
         <v>563</v>
       </c>
@@ -35513,7 +35624,7 @@
       <c r="N1153" s="13"/>
     </row>
     <row r="1154" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1154" s="136"/>
+      <c r="A1154" s="132"/>
       <c r="B1154" s="72" t="s">
         <v>563</v>
       </c>
@@ -35557,7 +35668,7 @@
       <c r="N1155" s="13"/>
     </row>
     <row r="1156" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1156" s="134">
+      <c r="A1156" s="130">
         <v>206</v>
       </c>
       <c r="B1156" s="72">
@@ -35587,7 +35698,7 @@
       <c r="N1156" s="13"/>
     </row>
     <row r="1157" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1157" s="135"/>
+      <c r="A1157" s="131"/>
       <c r="B1157" s="72">
         <v>40</v>
       </c>
@@ -35615,7 +35726,7 @@
       <c r="N1157" s="13"/>
     </row>
     <row r="1158" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1158" s="135"/>
+      <c r="A1158" s="131"/>
       <c r="B1158" s="72">
         <v>40</v>
       </c>
@@ -35643,7 +35754,7 @@
       <c r="N1158" s="13"/>
     </row>
     <row r="1159" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1159" s="136"/>
+      <c r="A1159" s="132"/>
       <c r="B1159" s="72">
         <v>40</v>
       </c>
@@ -35687,7 +35798,7 @@
       <c r="N1160" s="13"/>
     </row>
     <row r="1161" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1161" s="134">
+      <c r="A1161" s="130">
         <v>207</v>
       </c>
       <c r="B1161" s="72" t="s">
@@ -35717,7 +35828,7 @@
       <c r="N1161" s="13"/>
     </row>
     <row r="1162" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1162" s="135"/>
+      <c r="A1162" s="131"/>
       <c r="B1162" s="72" t="s">
         <v>566</v>
       </c>
@@ -35745,7 +35856,7 @@
       <c r="N1162" s="13"/>
     </row>
     <row r="1163" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1163" s="135"/>
+      <c r="A1163" s="131"/>
       <c r="B1163" s="72" t="s">
         <v>566</v>
       </c>
@@ -35773,7 +35884,7 @@
       <c r="N1163" s="13"/>
     </row>
     <row r="1164" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1164" s="136"/>
+      <c r="A1164" s="132"/>
       <c r="B1164" s="72" t="s">
         <v>566</v>
       </c>
@@ -35817,7 +35928,7 @@
       <c r="N1165" s="13"/>
     </row>
     <row r="1166" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1166" s="134">
+      <c r="A1166" s="130">
         <v>208</v>
       </c>
       <c r="B1166" s="72">
@@ -35847,7 +35958,7 @@
       <c r="N1166" s="13"/>
     </row>
     <row r="1167" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1167" s="135"/>
+      <c r="A1167" s="131"/>
       <c r="B1167" s="72">
         <v>81</v>
       </c>
@@ -35875,7 +35986,7 @@
       <c r="N1167" s="13"/>
     </row>
     <row r="1168" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1168" s="135"/>
+      <c r="A1168" s="131"/>
       <c r="B1168" s="72">
         <v>81</v>
       </c>
@@ -35903,7 +36014,7 @@
       <c r="N1168" s="13"/>
     </row>
     <row r="1169" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1169" s="136"/>
+      <c r="A1169" s="132"/>
       <c r="B1169" s="72">
         <v>81</v>
       </c>
@@ -35947,7 +36058,7 @@
       <c r="N1170" s="13"/>
     </row>
     <row r="1171" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1171" s="134">
+      <c r="A1171" s="130">
         <v>209</v>
       </c>
       <c r="B1171" s="72">
@@ -35977,7 +36088,7 @@
       <c r="N1171" s="13"/>
     </row>
     <row r="1172" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1172" s="135"/>
+      <c r="A1172" s="131"/>
       <c r="B1172" s="72">
         <v>46</v>
       </c>
@@ -36005,7 +36116,7 @@
       <c r="N1172" s="13"/>
     </row>
     <row r="1173" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1173" s="135"/>
+      <c r="A1173" s="131"/>
       <c r="B1173" s="72">
         <v>46</v>
       </c>
@@ -36033,7 +36144,7 @@
       <c r="N1173" s="13"/>
     </row>
     <row r="1174" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1174" s="136"/>
+      <c r="A1174" s="132"/>
       <c r="B1174" s="72">
         <v>46</v>
       </c>
@@ -36077,7 +36188,7 @@
       <c r="N1175" s="13"/>
     </row>
     <row r="1176" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1176" s="134">
+      <c r="A1176" s="130">
         <v>210</v>
       </c>
       <c r="B1176" s="72">
@@ -36107,7 +36218,7 @@
       <c r="N1176" s="13"/>
     </row>
     <row r="1177" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1177" s="135"/>
+      <c r="A1177" s="131"/>
       <c r="B1177" s="72">
         <v>86</v>
       </c>
@@ -36135,7 +36246,7 @@
       <c r="N1177" s="13"/>
     </row>
     <row r="1178" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1178" s="135"/>
+      <c r="A1178" s="131"/>
       <c r="B1178" s="72">
         <v>86</v>
       </c>
@@ -36163,7 +36274,7 @@
       <c r="N1178" s="13"/>
     </row>
     <row r="1179" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1179" s="136"/>
+      <c r="A1179" s="132"/>
       <c r="B1179" s="72">
         <v>86</v>
       </c>
@@ -36339,7 +36450,7 @@
       <c r="N1186" s="13"/>
     </row>
     <row r="1187" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1187" s="131">
+      <c r="A1187" s="143">
         <v>214</v>
       </c>
       <c r="B1187" s="7" t="s">
@@ -36371,7 +36482,7 @@
       <c r="N1187" s="16"/>
     </row>
     <row r="1188" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1188" s="132"/>
+      <c r="A1188" s="138"/>
       <c r="B1188" s="7" t="s">
         <v>49</v>
       </c>
@@ -36401,7 +36512,7 @@
       <c r="N1188" s="16"/>
     </row>
     <row r="1189" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1189" s="132"/>
+      <c r="A1189" s="138"/>
       <c r="B1189" s="7" t="s">
         <v>49</v>
       </c>
@@ -36431,7 +36542,7 @@
       <c r="N1189" s="16"/>
     </row>
     <row r="1190" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1190" s="125"/>
+      <c r="A1190" s="139"/>
       <c r="B1190" s="7" t="s">
         <v>49</v>
       </c>
@@ -38538,76 +38649,96 @@
     </row>
   </sheetData>
   <mergeCells count="184">
-    <mergeCell ref="A760:A769"/>
-    <mergeCell ref="A771:A790"/>
-    <mergeCell ref="A792:A801"/>
-    <mergeCell ref="A803:A812"/>
-    <mergeCell ref="A814:A823"/>
-    <mergeCell ref="A825:A834"/>
-    <mergeCell ref="A836:A845"/>
-    <mergeCell ref="A679:A682"/>
-    <mergeCell ref="A684:A687"/>
-    <mergeCell ref="A689:A692"/>
-    <mergeCell ref="A694:A697"/>
-    <mergeCell ref="A699:A702"/>
-    <mergeCell ref="A704:A707"/>
-    <mergeCell ref="A709:A712"/>
-    <mergeCell ref="A714:A729"/>
-    <mergeCell ref="A731:A758"/>
-    <mergeCell ref="A626:A629"/>
-    <mergeCell ref="A631:A634"/>
-    <mergeCell ref="A636:A639"/>
-    <mergeCell ref="A641:A652"/>
-    <mergeCell ref="A654:A657"/>
-    <mergeCell ref="A659:A662"/>
-    <mergeCell ref="A664:A667"/>
-    <mergeCell ref="A669:A672"/>
-    <mergeCell ref="A674:A677"/>
-    <mergeCell ref="A573:A576"/>
-    <mergeCell ref="A578:A581"/>
-    <mergeCell ref="A583:A586"/>
-    <mergeCell ref="A588:A591"/>
-    <mergeCell ref="A595:A598"/>
-    <mergeCell ref="A600:A603"/>
-    <mergeCell ref="A605:A608"/>
-    <mergeCell ref="A610:A613"/>
-    <mergeCell ref="A619:A622"/>
-    <mergeCell ref="A1176:A1179"/>
-    <mergeCell ref="A1187:A1190"/>
-    <mergeCell ref="A1141:A1144"/>
-    <mergeCell ref="A1146:A1149"/>
-    <mergeCell ref="A1151:A1154"/>
-    <mergeCell ref="A1156:A1159"/>
-    <mergeCell ref="A1161:A1164"/>
-    <mergeCell ref="A1166:A1169"/>
-    <mergeCell ref="A1171:A1174"/>
-    <mergeCell ref="A1058:A1065"/>
-    <mergeCell ref="A1067:A1074"/>
-    <mergeCell ref="A1076:A1085"/>
-    <mergeCell ref="A1087:A1090"/>
-    <mergeCell ref="A1092:A1093"/>
-    <mergeCell ref="A1099:A1102"/>
-    <mergeCell ref="A1104:A1127"/>
-    <mergeCell ref="A1131:A1134"/>
-    <mergeCell ref="A1136:A1139"/>
-    <mergeCell ref="A970:A974"/>
-    <mergeCell ref="A976:A977"/>
-    <mergeCell ref="A979:A982"/>
-    <mergeCell ref="A984:A993"/>
-    <mergeCell ref="A999:A1008"/>
-    <mergeCell ref="A1010:A1029"/>
-    <mergeCell ref="A1031:A1050"/>
-    <mergeCell ref="A1052:A1053"/>
-    <mergeCell ref="A1055:A1056"/>
-    <mergeCell ref="A858:A873"/>
-    <mergeCell ref="A875:A899"/>
-    <mergeCell ref="A901:A925"/>
-    <mergeCell ref="A927:A928"/>
-    <mergeCell ref="A934:A935"/>
-    <mergeCell ref="A937:A956"/>
-    <mergeCell ref="A958:A959"/>
-    <mergeCell ref="A961:A962"/>
-    <mergeCell ref="A964:A968"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="A48:A51"/>
+    <mergeCell ref="A53:A56"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A63:A66"/>
+    <mergeCell ref="A68:A71"/>
+    <mergeCell ref="A73:A76"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="A83:A86"/>
+    <mergeCell ref="A88:A91"/>
+    <mergeCell ref="A93:A96"/>
+    <mergeCell ref="A98:A101"/>
+    <mergeCell ref="A103:A106"/>
+    <mergeCell ref="A113:A116"/>
+    <mergeCell ref="A118:A121"/>
+    <mergeCell ref="A123:A126"/>
+    <mergeCell ref="A128:A131"/>
+    <mergeCell ref="A133:A136"/>
+    <mergeCell ref="A138:A141"/>
+    <mergeCell ref="A143:A146"/>
+    <mergeCell ref="A148:A151"/>
+    <mergeCell ref="A153:A156"/>
+    <mergeCell ref="A158:A161"/>
+    <mergeCell ref="A163:A166"/>
+    <mergeCell ref="A168:A170"/>
+    <mergeCell ref="A172:A174"/>
+    <mergeCell ref="A176:A179"/>
+    <mergeCell ref="A181:A184"/>
+    <mergeCell ref="A186:A189"/>
+    <mergeCell ref="A191:A194"/>
+    <mergeCell ref="A196:A199"/>
+    <mergeCell ref="A201:A204"/>
+    <mergeCell ref="A206:A209"/>
+    <mergeCell ref="A211:A214"/>
+    <mergeCell ref="A216:A219"/>
+    <mergeCell ref="A221:A224"/>
+    <mergeCell ref="A226:A229"/>
+    <mergeCell ref="A231:A234"/>
+    <mergeCell ref="A236:A239"/>
+    <mergeCell ref="A241:A244"/>
+    <mergeCell ref="A246:A249"/>
+    <mergeCell ref="A251:A254"/>
+    <mergeCell ref="A256:A259"/>
+    <mergeCell ref="A261:A264"/>
+    <mergeCell ref="A266:A269"/>
+    <mergeCell ref="A271:A274"/>
+    <mergeCell ref="A276:A279"/>
+    <mergeCell ref="A283:A286"/>
+    <mergeCell ref="A288:A291"/>
+    <mergeCell ref="A293:A296"/>
+    <mergeCell ref="A298:A301"/>
+    <mergeCell ref="A308:A311"/>
+    <mergeCell ref="A313:A316"/>
+    <mergeCell ref="A318:A321"/>
+    <mergeCell ref="A323:A326"/>
+    <mergeCell ref="A328:A331"/>
+    <mergeCell ref="A333:A336"/>
+    <mergeCell ref="A338:A341"/>
+    <mergeCell ref="A343:A346"/>
+    <mergeCell ref="A348:A351"/>
+    <mergeCell ref="A353:A356"/>
+    <mergeCell ref="A358:A361"/>
+    <mergeCell ref="A363:A366"/>
+    <mergeCell ref="A368:A371"/>
+    <mergeCell ref="A373:A376"/>
+    <mergeCell ref="A378:A381"/>
+    <mergeCell ref="A383:A386"/>
+    <mergeCell ref="A388:A391"/>
+    <mergeCell ref="A393:A396"/>
+    <mergeCell ref="A398:A401"/>
+    <mergeCell ref="A403:A406"/>
+    <mergeCell ref="A408:A411"/>
+    <mergeCell ref="A413:A416"/>
+    <mergeCell ref="A418:A421"/>
+    <mergeCell ref="A423:A426"/>
     <mergeCell ref="A428:A431"/>
     <mergeCell ref="A433:A436"/>
     <mergeCell ref="A438:A441"/>
@@ -38632,99 +38763,373 @@
     <mergeCell ref="A530:A533"/>
     <mergeCell ref="A551:A558"/>
     <mergeCell ref="A560:A567"/>
-    <mergeCell ref="A383:A386"/>
-    <mergeCell ref="A388:A391"/>
-    <mergeCell ref="A393:A396"/>
-    <mergeCell ref="A398:A401"/>
-    <mergeCell ref="A403:A406"/>
-    <mergeCell ref="A408:A411"/>
-    <mergeCell ref="A413:A416"/>
-    <mergeCell ref="A418:A421"/>
-    <mergeCell ref="A423:A426"/>
-    <mergeCell ref="A338:A341"/>
-    <mergeCell ref="A343:A346"/>
-    <mergeCell ref="A348:A351"/>
-    <mergeCell ref="A353:A356"/>
-    <mergeCell ref="A358:A361"/>
-    <mergeCell ref="A363:A366"/>
-    <mergeCell ref="A368:A371"/>
-    <mergeCell ref="A373:A376"/>
-    <mergeCell ref="A378:A381"/>
-    <mergeCell ref="A288:A291"/>
-    <mergeCell ref="A293:A296"/>
-    <mergeCell ref="A298:A301"/>
-    <mergeCell ref="A308:A311"/>
-    <mergeCell ref="A313:A316"/>
-    <mergeCell ref="A318:A321"/>
-    <mergeCell ref="A323:A326"/>
-    <mergeCell ref="A328:A331"/>
-    <mergeCell ref="A333:A336"/>
-    <mergeCell ref="A241:A244"/>
-    <mergeCell ref="A246:A249"/>
-    <mergeCell ref="A251:A254"/>
-    <mergeCell ref="A256:A259"/>
-    <mergeCell ref="A261:A264"/>
-    <mergeCell ref="A266:A269"/>
-    <mergeCell ref="A271:A274"/>
-    <mergeCell ref="A276:A279"/>
-    <mergeCell ref="A283:A286"/>
-    <mergeCell ref="A196:A199"/>
-    <mergeCell ref="A201:A204"/>
-    <mergeCell ref="A206:A209"/>
-    <mergeCell ref="A211:A214"/>
-    <mergeCell ref="A216:A219"/>
-    <mergeCell ref="A221:A224"/>
-    <mergeCell ref="A226:A229"/>
-    <mergeCell ref="A231:A234"/>
-    <mergeCell ref="A236:A239"/>
-    <mergeCell ref="A153:A156"/>
-    <mergeCell ref="A158:A161"/>
-    <mergeCell ref="A163:A166"/>
-    <mergeCell ref="A168:A170"/>
-    <mergeCell ref="A172:A174"/>
-    <mergeCell ref="A176:A179"/>
-    <mergeCell ref="A181:A184"/>
-    <mergeCell ref="A186:A189"/>
-    <mergeCell ref="A191:A194"/>
-    <mergeCell ref="A103:A106"/>
-    <mergeCell ref="A113:A116"/>
-    <mergeCell ref="A118:A121"/>
-    <mergeCell ref="A123:A126"/>
-    <mergeCell ref="A128:A131"/>
-    <mergeCell ref="A133:A136"/>
-    <mergeCell ref="A138:A141"/>
-    <mergeCell ref="A143:A146"/>
-    <mergeCell ref="A148:A151"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="A63:A66"/>
-    <mergeCell ref="A68:A71"/>
-    <mergeCell ref="A73:A76"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A83:A86"/>
-    <mergeCell ref="A88:A91"/>
-    <mergeCell ref="A93:A96"/>
-    <mergeCell ref="A98:A101"/>
-    <mergeCell ref="A13:A16"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="A28:A31"/>
-    <mergeCell ref="A33:A36"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A43:A46"/>
-    <mergeCell ref="A48:A51"/>
-    <mergeCell ref="A53:A56"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A858:A873"/>
+    <mergeCell ref="A875:A899"/>
+    <mergeCell ref="A901:A925"/>
+    <mergeCell ref="A927:A928"/>
+    <mergeCell ref="A934:A935"/>
+    <mergeCell ref="A937:A956"/>
+    <mergeCell ref="A958:A959"/>
+    <mergeCell ref="A961:A962"/>
+    <mergeCell ref="A964:A968"/>
+    <mergeCell ref="A970:A974"/>
+    <mergeCell ref="A976:A977"/>
+    <mergeCell ref="A979:A982"/>
+    <mergeCell ref="A984:A993"/>
+    <mergeCell ref="A999:A1008"/>
+    <mergeCell ref="A1010:A1029"/>
+    <mergeCell ref="A1031:A1050"/>
+    <mergeCell ref="A1052:A1053"/>
+    <mergeCell ref="A1055:A1056"/>
+    <mergeCell ref="A1058:A1065"/>
+    <mergeCell ref="A1067:A1074"/>
+    <mergeCell ref="A1076:A1085"/>
+    <mergeCell ref="A1087:A1090"/>
+    <mergeCell ref="A1092:A1093"/>
+    <mergeCell ref="A1099:A1102"/>
+    <mergeCell ref="A1104:A1127"/>
+    <mergeCell ref="A1131:A1134"/>
+    <mergeCell ref="A1136:A1139"/>
+    <mergeCell ref="A1176:A1179"/>
+    <mergeCell ref="A1187:A1190"/>
+    <mergeCell ref="A1141:A1144"/>
+    <mergeCell ref="A1146:A1149"/>
+    <mergeCell ref="A1151:A1154"/>
+    <mergeCell ref="A1156:A1159"/>
+    <mergeCell ref="A1161:A1164"/>
+    <mergeCell ref="A1166:A1169"/>
+    <mergeCell ref="A1171:A1174"/>
+    <mergeCell ref="A573:A576"/>
+    <mergeCell ref="A578:A581"/>
+    <mergeCell ref="A583:A586"/>
+    <mergeCell ref="A588:A591"/>
+    <mergeCell ref="A595:A598"/>
+    <mergeCell ref="A600:A603"/>
+    <mergeCell ref="A605:A608"/>
+    <mergeCell ref="A610:A613"/>
+    <mergeCell ref="A619:A622"/>
+    <mergeCell ref="A626:A629"/>
+    <mergeCell ref="A631:A634"/>
+    <mergeCell ref="A636:A639"/>
+    <mergeCell ref="A641:A652"/>
+    <mergeCell ref="A654:A657"/>
+    <mergeCell ref="A659:A662"/>
+    <mergeCell ref="A664:A667"/>
+    <mergeCell ref="A669:A672"/>
+    <mergeCell ref="A674:A677"/>
+    <mergeCell ref="A760:A769"/>
+    <mergeCell ref="A771:A790"/>
+    <mergeCell ref="A792:A801"/>
+    <mergeCell ref="A803:A812"/>
+    <mergeCell ref="A814:A823"/>
+    <mergeCell ref="A825:A834"/>
+    <mergeCell ref="A836:A845"/>
+    <mergeCell ref="A679:A682"/>
+    <mergeCell ref="A684:A687"/>
+    <mergeCell ref="A689:A692"/>
+    <mergeCell ref="A694:A697"/>
+    <mergeCell ref="A699:A702"/>
+    <mergeCell ref="A704:A707"/>
+    <mergeCell ref="A709:A712"/>
+    <mergeCell ref="A714:A729"/>
+    <mergeCell ref="A731:A758"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="8" fitToHeight="0" orientation="landscape"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F16041B-08CB-4EC6-9E47-CBC37F9DFA6A}">
+  <dimension ref="A1:B35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>580</v>
+      </c>
+      <c r="B2">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>581</v>
+      </c>
+      <c r="B3">
+        <v>10002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>582</v>
+      </c>
+      <c r="B4">
+        <v>10003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>583</v>
+      </c>
+      <c r="B5">
+        <v>10004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>584</v>
+      </c>
+      <c r="B6">
+        <v>10005</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>585</v>
+      </c>
+      <c r="B7">
+        <v>10006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>586</v>
+      </c>
+      <c r="B8">
+        <v>10007</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>587</v>
+      </c>
+      <c r="B9">
+        <v>10008</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>588</v>
+      </c>
+      <c r="B10">
+        <v>10009</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>589</v>
+      </c>
+      <c r="B11">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>590</v>
+      </c>
+      <c r="B12">
+        <v>10011</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>591</v>
+      </c>
+      <c r="B13">
+        <v>10012</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>592</v>
+      </c>
+      <c r="B14">
+        <v>10013</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>593</v>
+      </c>
+      <c r="B15">
+        <v>10014</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>594</v>
+      </c>
+      <c r="B16">
+        <v>10015</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>595</v>
+      </c>
+      <c r="B17">
+        <v>10016</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>596</v>
+      </c>
+      <c r="B18">
+        <v>10017</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>597</v>
+      </c>
+      <c r="B19">
+        <v>10018</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>598</v>
+      </c>
+      <c r="B20">
+        <v>10019</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>599</v>
+      </c>
+      <c r="B21">
+        <v>10020</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>600</v>
+      </c>
+      <c r="B22">
+        <v>10021</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>601</v>
+      </c>
+      <c r="B23">
+        <v>10022</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>602</v>
+      </c>
+      <c r="B24">
+        <v>10023</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>603</v>
+      </c>
+      <c r="B25">
+        <v>10024</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>604</v>
+      </c>
+      <c r="B26">
+        <v>10025</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>605</v>
+      </c>
+      <c r="B27">
+        <v>10026</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>606</v>
+      </c>
+      <c r="B28">
+        <v>10027</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>607</v>
+      </c>
+      <c r="B29">
+        <v>10028</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>608</v>
+      </c>
+      <c r="B30">
+        <v>10029</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>609</v>
+      </c>
+      <c r="B31">
+        <v>10030</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>610</v>
+      </c>
+      <c r="B32">
+        <v>10031</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>611</v>
+      </c>
+      <c r="B33">
+        <v>10032</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>612</v>
+      </c>
+      <c r="B34">
+        <v>10033</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>613</v>
+      </c>
+      <c r="B35">
+        <v>10034</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>